--- a/data/標案資料庫.xlsx
+++ b/data/標案資料庫.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="標案資料庫" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月份統計" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="說明" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="標案資料庫" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="月份統計" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="說明" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'標案資料庫'!$A$1:$M$98</definedName>
@@ -6779,7 +6779,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4184</v>
+        <v>4195</v>
       </c>
       <c r="C2" t="n">
         <v>97</v>
@@ -6815,7 +6815,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>產生時間：2026-10-16 15:42　資料庫共 97 筆</t>
+          <t>產生時間：2026-10-17 08:24　資料庫共 97 筆</t>
         </is>
       </c>
     </row>

--- a/data/標案資料庫.xlsx
+++ b/data/標案資料庫.xlsx
@@ -6815,7 +6815,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>產生時間：2026-10-17 08:24　資料庫共 97 筆</t>
+          <t>產生時間：2026-10-18 07:59　資料庫共 97 筆</t>
         </is>
       </c>
     </row>

--- a/data/標案資料庫.xlsx
+++ b/data/標案資料庫.xlsx
@@ -12,7 +12,7 @@
     <sheet name="說明" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'標案資料庫'!$A$1:$M$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'標案資料庫'!$A$1:$M$114</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M98"/>
+  <dimension ref="A1:M114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -524,25 +524,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>桃園市政府藝文設施管理中心</t>
+          <t>國家人權博物館</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>「2027桃園鐵玫瑰藝術節活動執行統籌及行銷」委託專業服務採購案</t>
+          <t>「解嚴40週年國際論壇暨紀念專書籌劃」委託專業服務案</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9000000</v>
+        <v>2200000</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -552,22 +552,22 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>115AFMC-017</t>
+          <t>11590Z</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>活動執行、藝術節、行銷</t>
+          <t>國際論壇、論壇</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,32 +580,32 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>屏東縣獅子鄉公所</t>
+          <t>南投縣政府</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>屏東縣獅子鄉115年度慶祝重陽節聯合表揚暨族語文化推廣與文化健康站成果展活動勞務採購案</t>
+          <t>「2026南投花卉嘉年華－草屯展區系列活動」勞務採購案</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1162700</v>
+        <v>1000000</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -620,17 +620,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1151001AA</t>
+          <t>1150602018G</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>成果展、活動、推廣</t>
+          <t>嘉年華、系列活動</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -643,37 +643,35 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>勞動部勞動力發展署雲嘉南分署</t>
+          <t>臺南市政府農業局</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116年度社群平台整合行銷委託計畫</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>2000000</v>
-      </c>
+          <t>日本地區臺南市農漁產推廣暨行銷活動策畫與執行委託專業服務案</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -683,21 +681,21 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>yctrb1150129</t>
+          <t>115AGR080</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>整合行銷、社群平台</t>
+          <t>活動、行銷、推廣</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -706,32 +704,32 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>內政部</t>
+          <t>桃園市政府環境管理處</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>116年第84屆兵役節慶祝大會暨頒獎典禮委外服務案</t>
+          <t>115年度職業安全衛生業務標竿學習宣導活動計畫</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1230000</v>
+        <v>1300000</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -741,26 +739,26 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>115YJ-ST15</t>
+          <t>1150036916</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>國際會議論壇/活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>大會、頒獎典禮</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -769,32 +767,32 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>桃園市八德區公所</t>
+          <t>南投縣政府社會及勞動局</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>116年度桃園市元旦升旗典禮活動規劃與執行</t>
+          <t>南投縣115年度國際身心障礙者日宣導活動</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1600000</v>
+        <v>2500000</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -809,17 +807,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>BB1151015</t>
+          <t>115-10-10-005-E</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>活動規劃、典禮</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -832,37 +830,37 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>國立臺中教育大學</t>
+          <t>財團法人蘭陽農業發展基金會</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>數位內容充實與推廣總計畫成果紀錄影片製作採購案</t>
+          <t>2027宜蘭綠色博覽會－海洋館委託專業服務案</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>465000</v>
+        <v>7000000</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -872,21 +870,21 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>115-C063</t>
+          <t>115101305</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>影片製作、推廣</t>
+          <t>博覽會</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -895,32 +893,32 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>文化部</t>
+          <t>財團法人蘭陽農業發展基金會</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>文化部「蒙藏文化情境展示及體驗活動」展場設計製作布卸展及活動執行藝文採購案</t>
+          <t>2027宜蘭綠色博覽會－森林館委託專業服務案</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>3350000</v>
+        <v>3950000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -935,21 +933,21 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>11510159</t>
+          <t>115101301</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>博覽會</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -958,32 +956,32 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>國立雲林科技大學</t>
+          <t>雲林縣政府</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026研發成果展場地佈置案</t>
+          <t>「2026雲林文創聯合徵選暨雲林設計獎」頒獎典禮委託規劃執行案</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>840000</v>
+        <v>500000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -993,12 +991,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>HTL115040</t>
+          <t>1152H10116</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1008,7 +1006,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>成果展</t>
+          <t>頒獎典禮</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1021,32 +1019,32 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>桃園市政府觀光旅遊局</t>
+          <t>臺北市教師研習中心</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>116年桃園觀光旅遊局輿情蒐集及通報服務勞務採購案</t>
+          <t>116年度優質學校頒獎典禮、杏壇芬芳獎表揚典禮、臺北教育111標竿學校頒獎典禮採購案</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>247008</v>
+        <v>869500</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1061,21 +1059,21 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1151015-AA1</t>
+          <t>11605</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>政策溝通</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>輿情</t>
+          <t>頒獎典禮</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -1084,32 +1082,32 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>臺中市立圖書館</t>
+          <t>臺中市政府數位發展局</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026臺中市立圖書館羅布森圖書館展覽委託專業服務採購案</t>
+          <t>台中通特店消費推廣暨抽獎活動案</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1120000</v>
+        <v>950000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1124,21 +1122,21 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>115058</t>
+          <t>115B-10</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>展覽</t>
+          <t>活動、推廣</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -1147,37 +1145,37 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>桃園市政府客家事務局</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>115年客家記憶共創計畫-客家文化中心古契約展覽策劃執行</t>
+          <t>「桃園市客家文化館開館系列活動」勞務採購案</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>850000</v>
+        <v>5500000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1187,7 +1185,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>A132-1151015-1</t>
+          <t>115-021</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1197,11 +1195,11 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>展覽</t>
+          <t>系列活動</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
@@ -1210,37 +1208,37 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>廣亞學校財團法人育達科技大學</t>
+          <t>嘉義市政府</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>研究發展處創新創業輔導暨育成中心115年青年創業工作坊專案管理計畫青年遴選活動頒獎典禮暨成果展評選採購</t>
+          <t>嘉義市政府116年家庭暴力暨性侵害防治中心宣導行銷計畫</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>350000</v>
+        <v>1800000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1250,21 +1248,21 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>115J-04</t>
+          <t>115266</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>頒獎典禮、成果展、活動、工作坊</t>
+          <t>宣導、行銷</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
@@ -1273,32 +1271,32 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>苗栗縣政府衛生局</t>
+          <t>國家科學及技術委員會南部科學園區管理局</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>115年衛生教育之媒體廣告行銷推廣</t>
+          <t>國家科學及技術委員會116年度科學園區滿意度調查計畫</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>770000</v>
+        <v>1236708</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1313,21 +1311,21 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>11535</t>
+          <t>115660D01151</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>政策溝通</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>行銷推廣、廣告、媒體</t>
+          <t>滿意度調查</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
@@ -1336,32 +1334,32 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>新竹市政府</t>
+          <t>農業部林業及自然保育署阿里山林業鐵路及文化資產管理處</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>116年新竹市政府城市行銷處社群網站管理</t>
+          <t>116-117年「阿里山林鐵行動學校」跨館際展覽委託專業服務案</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1900000</v>
+        <v>2800000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1376,21 +1374,21 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1150300</t>
+          <t>116-EDU-001</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>城市行銷、社群網站</t>
+          <t>展覽</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
@@ -1399,32 +1397,32 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>高雄市政府地政局</t>
+          <t>新北市政府觀光旅遊局</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>115年度不動產防詐暨交易安全宣導活動委外服務案</t>
+          <t>115年新北市平日住宿及生日券獎助活動專案管理委託專業服務案</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>400000</v>
+        <v>700000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1439,21 +1437,21 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>115019</t>
+          <t>1152038719</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
@@ -1462,37 +1460,37 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>桃園市政府環境保護局</t>
+          <t>中華郵政股份有限公司</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>116年社群網路環境教育推廣維運計畫</t>
+          <t>「羊來了-生肖郵票特展」策、布展及開幕活動委託服務</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>3800000</v>
+        <v>1480000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1502,21 +1500,21 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1150085608</t>
+          <t>115-3-167</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>推廣、社群</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
@@ -1525,61 +1523,61 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>嘉義縣表演藝術中心</t>
+          <t>桃園市政府藝文設施管理中心</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>嘉義縣表演藝術中心115年表演節目整合傳播委託專業服務案</t>
+          <t>「2027桃園鐵玫瑰藝術節活動執行統籌及行銷」委託專業服務採購案</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>800000</v>
+        <v>9000000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1150002654</t>
+          <t>115AFMC-017</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>整合傳播</t>
+          <t>活動執行、藝術節、行銷</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
@@ -1588,32 +1586,32 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>南投縣水里鄉公所</t>
+          <t>屏東縣獅子鄉公所</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>「2026水里觀光行銷暨農特產品推廣系列活動—煙火設計及施放勞務採購案」</t>
+          <t>屏東縣獅子鄉115年度慶祝重陽節聯合表揚暨族語文化推廣與文化健康站成果展活動勞務採購案</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1000000</v>
+        <v>1162700</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1623,12 +1621,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>115SHTS07</t>
+          <t>1151001AA</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1638,11 +1636,11 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>系列活動、觀光行銷、推廣</t>
+          <t>成果展、活動、推廣</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
@@ -1651,37 +1649,37 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>國立臺灣大學</t>
+          <t>勞動部勞動力發展署雲嘉南分署</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2027年臺大杜鵑花節學系博覽會場佈</t>
+          <t>116年度社群平台整合行銷委託計畫</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1250000</v>
+        <v>2000000</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1691,21 +1689,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1150963</t>
+          <t>yctrb1150129</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>博覽會</t>
+          <t>整合行銷、社群平台</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
@@ -1714,32 +1712,32 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>高雄市政府運動發展局</t>
+          <t>內政部</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>企業22年甲級排球聯賽高雄台電女子排球隊主場賽事行銷活動案</t>
+          <t>116年第84屆兵役節慶祝大會暨頒獎典禮委外服務案</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>590000</v>
+        <v>1230000</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1749,26 +1747,26 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>115-B-76</t>
+          <t>115YJ-ST15</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>國際會議論壇/活動執行</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>活動、行銷</t>
+          <t>大會、頒獎典禮</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
@@ -1777,32 +1775,32 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>桃園市八德區公所</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>115年度管路灌溉成果推廣活動</t>
+          <t>116年度桃園市元旦升旗典禮活動規劃與執行</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>4000000</v>
+        <v>1600000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1817,21 +1815,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>TY115B030</t>
+          <t>BB1151015</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>活動、推廣</t>
+          <t>活動規劃、典禮</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
@@ -1840,28 +1838,28 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>臺北市政府工務局</t>
+          <t>國立臺中教育大學</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>116年全國大專院校運動會開閉幕典禮活動</t>
+          <t>數位內容充實與推廣總計畫成果紀錄影片製作採購案</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>10000000</v>
+        <v>465000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1870,31 +1868,31 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1150826S0096</t>
+          <t>115-C063</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>活動、典禮</t>
+          <t>影片製作、推廣</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
@@ -1903,37 +1901,37 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>臺中市政府環境保護局</t>
+          <t>文化部</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>115年度環保英雄歲末嘉年華活動採購案</t>
+          <t>文化部「蒙藏文化情境展示及體驗活動」展場設計製作布卸展及活動執行藝文採購案</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>1105000</v>
+        <v>3350000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1943,7 +1941,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>N1151013101</t>
+          <t>11510159</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1953,7 +1951,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>嘉年華</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1966,37 +1964,37 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>新北市政府環境保護局</t>
+          <t>國立雲林科技大學</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>116年度資源回收推動及形象改造計畫</t>
+          <t>2026研發成果展場地佈置案</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>9670000</v>
+        <v>840000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2006,17 +2004,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>115-177</t>
+          <t>HTL115040</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>形象改造</t>
+          <t>成果展</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -2029,37 +2027,37 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>原住民族委員會原住民族文化發展中心</t>
+          <t>桃園市政府觀光旅遊局</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>116年公益彩券回饋金計畫-文化觀光行銷專業人才勞務採購案</t>
+          <t>116年桃園觀光旅遊局輿情蒐集及通報服務勞務採購案</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>4681825</v>
+        <v>247008</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2069,21 +2067,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1150006860</t>
+          <t>1151015-AA1</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>政策溝通</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>觀光行銷</t>
+          <t>輿情</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
@@ -2092,32 +2090,32 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>勞動部</t>
+          <t>臺中市立圖書館</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>115年度「勞工自願提繳退休金影片製作案」</t>
+          <t>2026臺中市立圖書館羅布森圖書館展覽委託專業服務採購案</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>997920</v>
+        <v>1120000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2132,21 +2130,21 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>03-11509091</t>
+          <t>115058</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>影片製作</t>
+          <t>展覽</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
@@ -2155,32 +2153,32 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>桃園市政府捷運工程局</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>桃園市八德區德和路一段第2階段通車活動委託服務案</t>
+          <t>115年客家記憶共創計畫-客家文化中心古契約展覽策劃執行</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>1000000</v>
+        <v>850000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2190,12 +2188,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1151006</t>
+          <t>A132-1151015-1</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2205,7 +2203,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>展覽</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2218,37 +2216,37 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>中華郵政股份有限公司</t>
+          <t>廣亞學校財團法人育達科技大學</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>115年度郵政形象廣告電視託播</t>
+          <t>研究發展處創新創業輔導暨育成中心115年青年創業工作坊專案管理計畫青年遴選活動頒獎典禮暨成果展評選採購</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>6000000</v>
+        <v>350000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>公開招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2258,21 +2256,21 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>115-5-294</t>
+          <t>115J-04</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>電視託播、形象廣告</t>
+          <t>頒獎典禮、成果展、活動、工作坊</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
@@ -2288,30 +2286,30 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>臺銀人壽保險股份有限公司</t>
+          <t>苗栗縣政府衛生局</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>115年壽險行銷研討會-理財激勵專案</t>
+          <t>115年衛生教育之媒體廣告行銷推廣</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>8330000</v>
+        <v>770000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2321,21 +2319,21 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>115-005-106-CL-1-798</t>
+          <t>11535</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>研討會</t>
+          <t>行銷推廣、廣告、媒體</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
@@ -2351,28 +2349,30 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>國立臺南大學</t>
+          <t>新竹市政府</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>幼兒美感教育社群與國際交流影音紀錄</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr"/>
+          <t>116年新竹市政府城市行銷處社群網站管理</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>1900000</v>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2382,21 +2382,21 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1151065-TL</t>
+          <t>1150300</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>國際會議論壇/宣導行銷</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>國際交流、社群</t>
+          <t>城市行銷、社群網站</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
@@ -2412,25 +2412,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>臺東縣鹿野鄉公所</t>
+          <t>高雄市政府地政局</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026鹿野馬拉松系列活動賽事勞務採購案</t>
+          <t>115年度不動產防詐暨交易安全宣導活動委外服務案</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1460000</v>
+        <v>400000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2445,21 +2445,21 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1150929</t>
+          <t>115019</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>系列活動</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
@@ -2475,30 +2475,30 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>臺中市大里區公所</t>
+          <t>桃園市政府環境保護局</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>115年大里區運動會暨里鄰長健行活動規劃執行委託專業服務採購</t>
+          <t>116年社群網路環境教育推廣維運計畫</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>400000</v>
+        <v>3800000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2508,17 +2508,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>115dali032</t>
+          <t>1150085608</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>活動規劃</t>
+          <t>推廣、社群</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2538,25 +2538,25 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>桃園市復興區公所</t>
+          <t>嘉義縣表演藝術中心</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>桃園市復興區115年度甜柿推廣活動好柿發聲勞務採購案</t>
+          <t>嘉義縣表演藝術中心115年表演節目整合傳播委託專業服務案</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>766500</v>
+        <v>800000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2571,17 +2571,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>115D52</t>
+          <t>1150002654</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>活動、推廣</t>
+          <t>整合傳播</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2601,25 +2601,25 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>南投縣政府</t>
+          <t>南投縣水里鄉公所</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>115年度南投拍片好所在影視音協拍多元媒體宣傳採購案</t>
+          <t>「2026水里觀光行銷暨農特產品推廣系列活動—煙火設計及施放勞務採購案」</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>1100000</v>
+        <v>1000000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2634,21 +2634,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1150707005G</t>
+          <t>115SHTS07</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>媒體宣傳</t>
+          <t>系列活動、觀光行銷、推廣</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
@@ -2664,54 +2664,54 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>農業部林業及自然保育署阿里山林業鐵路及文化資產管理處</t>
+          <t>國立臺灣大學</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>阿里山林鐵服務中心小葉子館之展覽、賣店、服務設施規劃暨製作案</t>
+          <t>2027年臺大杜鵑花節學系博覽會場佈</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>2500000</v>
+        <v>1250000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>115-ALI-001</t>
+          <t>1150963</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>展覽</t>
+          <t>博覽會</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
@@ -2727,21 +2727,21 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>苗栗縣政府</t>
+          <t>高雄市政府運動發展局</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>苗栗縣政府115年度短影音攝製暨電視宣傳委託專業服務案</t>
+          <t>企業22年甲級排球聯賽高雄台電女子排球隊主場賽事行銷活動案</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>650000</v>
+        <v>590000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2760,21 +2760,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>115147f</t>
+          <t>115-B-76</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>宣傳</t>
+          <t>活動、行銷</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
@@ -2790,30 +2790,30 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>花蓮縣豐濱鄉公所</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>115年「點亮豐濱！族語詩歌高聲唱耶誕嘉年華暨文化健康站成果展」勞務採購案</t>
+          <t>115年度管路灌溉成果推廣活動</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>1100000</v>
+        <v>4000000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2823,21 +2823,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>FB1151218</t>
+          <t>TY115B030</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>嘉年華、成果展</t>
+          <t>活動、推廣</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
@@ -2853,25 +2853,25 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>臺中市政府研究發展考核委員會</t>
+          <t>臺北市政府工務局</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>「115年度臺中市經濟發展與城市行銷推廣案」委託專業服務案</t>
+          <t>116年全國大專院校運動會開閉幕典禮活動</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>2520000</v>
+        <v>10000000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2881,26 +2881,26 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>115RCP16</t>
+          <t>1150826S0096</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>行銷推廣、城市行銷</t>
+          <t>活動、典禮</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
@@ -2916,25 +2916,25 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>高雄市政府經濟發展局</t>
+          <t>臺中市政府環境保護局</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>「2027高雄過好年聯合記者會」委託專業服務案</t>
+          <t>115年度環保英雄歲末嘉年華活動採購案</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>500000</v>
+        <v>1105000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>115090</t>
+          <t>N1151013101</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>記者會</t>
+          <t>嘉年華</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2979,40 +2979,40 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>內政部</t>
+          <t>新北市政府環境保護局</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>115年度合作社制度宣導短片託播案</t>
+          <t>116年度資源回收推動及形象改造計畫</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>800000</v>
+        <v>9670000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>115HT-NH090806</t>
+          <t>115-177</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>宣導短片</t>
+          <t>形象改造</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -3042,30 +3042,30 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>花蓮縣議會</t>
+          <t>原住民族委員會原住民族文化發展中心</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>花蓮縣議會「第21屆議員宣誓就職典禮暨正副議長選舉」委託專業服務案</t>
+          <t>116年公益彩券回饋金計畫-文化觀光行銷專業人才勞務採購案</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>360000</v>
+        <v>4681825</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3075,21 +3075,21 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>115GA31</t>
+          <t>1150006860</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>典禮</t>
+          <t>觀光行銷</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
@@ -3105,30 +3105,30 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>南投縣水里鄉公所</t>
+          <t>勞動部</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>「2026水里觀光行銷暨農特產推廣系列活動」勞務採購案</t>
+          <t>115年度「勞工自願提繳退休金影片製作案」</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>4300000</v>
+        <v>997920</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3138,21 +3138,21 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>115SHTS06</t>
+          <t>03-11509091</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>系列活動、觀光行銷、推廣</t>
+          <t>影片製作</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
@@ -3168,25 +3168,25 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>花蓮縣政府</t>
+          <t>桃園市政府捷運工程局</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>115年花蓮縣長青大學結業典禮暨成果展活動</t>
+          <t>桃園市八德區德和路一段第2階段通車活動委託服務案</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>1150000</v>
+        <v>1000000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>SC1150020901</t>
+          <t>1151006</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3211,11 +3211,11 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>成果展、活動、典禮</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
@@ -3231,30 +3231,30 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>臺南市政府經濟發展局</t>
+          <t>中華郵政股份有限公司</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>「116年永康迎春嘉年華」活動規劃執行服務</t>
+          <t>115年度郵政形象廣告電視託播</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>600000</v>
+        <v>6000000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>公開招標公告</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3264,17 +3264,17 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>115ECON71S1</t>
+          <t>115-5-294</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>嘉年華、活動規劃</t>
+          <t>電視託播、形象廣告</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3294,25 +3294,25 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>臺北表演藝術中心</t>
+          <t>臺銀人壽保險股份有限公司</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>第三屆臺北戲劇獎頒獎典禮暨系列活動製作執行勞務採購案</t>
+          <t>115年壽險行銷研討會-理財激勵專案</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>15000000</v>
+        <v>8330000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3327,21 +3327,21 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>TPACRD1150141</t>
+          <t>115-005-106-CL-1-798</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>頒獎典禮、系列活動</t>
+          <t>研討會</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
@@ -3357,25 +3357,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>屏東縣獅子鄉公所</t>
+          <t>國立臺南大學</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>屏東縣獅子鄉115年度慶祝重陽節聯合表揚暨族語文化推廣與文化健康站成果展活動勞務採購案</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="n">
-        <v>1162700</v>
-      </c>
+          <t>幼兒美感教育社群與國際交流影音紀錄</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3390,21 +3388,21 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1151001AA</t>
+          <t>1151065-TL</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>國際會議論壇/宣導行銷</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>成果展、活動、推廣</t>
+          <t>國際交流、社群</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
@@ -3420,21 +3418,21 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>宜蘭縣政府</t>
+          <t>臺東縣鹿野鄉公所</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>「宜蘭縣115年國際移民嘉年華」活動規劃執行委託案</t>
+          <t>2026鹿野馬拉松系列活動賽事勞務採購案</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>400000</v>
+        <v>1460000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -3453,7 +3451,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>CVSL115019</t>
+          <t>1150929</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3463,11 +3461,11 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>嘉年華、活動規劃</t>
+          <t>系列活動</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
@@ -3483,25 +3481,25 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>財政部高雄國稅局</t>
+          <t>臺中市大里區公所</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>115年度結合統一發票推行暨「來稅局找碴-觀察力培養計畫」租稅宣導活動委外服務案</t>
+          <t>115年大里區運動會暨里鄰長健行活動規劃執行委託專業服務採購</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>445000</v>
+        <v>400000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3516,21 +3514,21 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1150042</t>
+          <t>115dali032</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>活動規劃</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
@@ -3546,25 +3544,25 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>國立臺中教育大學</t>
+          <t>桃園市復興區公所</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>115年原住民族教育論壇暨原住民族教育資源中心成果交流會</t>
+          <t>桃園市復興區115年度甜柿推廣活動好柿發聲勞務採購案</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>1450000</v>
+        <v>766500</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3579,21 +3577,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>115-C062</t>
+          <t>115D52</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>論壇</t>
+          <t>活動、推廣</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
@@ -3609,25 +3607,25 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>衛生福利部疾病管制署</t>
+          <t>南投縣政府</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>「115年度防疫績優獎頒獎典禮專業服務」採購案</t>
+          <t>115年度南投拍片好所在影視音協拍多元媒體宣傳採購案</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>950000</v>
+        <v>1100000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3642,17 +3640,17 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>LA115028</t>
+          <t>1150707005G</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>頒獎典禮</t>
+          <t>媒體宣傳</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -3672,21 +3670,21 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>花蓮縣政府</t>
+          <t>農業部林業及自然保育署阿里山林業鐵路及文化資產管理處</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>115年花蓮縣精品咖啡行銷推廣計畫</t>
+          <t>阿里山林鐵服務中心小葉子館之展覽、賣店、服務設施規劃暨製作案</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>1100000</v>
+        <v>2500000</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -3695,31 +3693,31 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>AG1150018061</t>
+          <t>115-ALI-001</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>行銷推廣</t>
+          <t>展覽</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
@@ -3735,21 +3733,21 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>社團法人花蓮縣基督教會花蓮靈糧堂宣教協會</t>
+          <t>苗栗縣政府</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026花蓮幸福聖誕城行銷宣傳及城市聯合宣傳規劃案</t>
+          <t>苗栗縣政府115年度短影音攝製暨電視宣傳委託專業服務案</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>6789600</v>
+        <v>650000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -3758,7 +3756,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3768,7 +3766,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-2HLLC</t>
+          <t>115147f</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3778,11 +3776,11 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>行銷宣傳</t>
+          <t>宣傳</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
@@ -3798,21 +3796,21 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>社團法人花蓮縣基督教會花蓮靈糧堂宣教協會</t>
+          <t>花蓮縣豐濱鄉公所</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026花蓮幸福聖誕城活動執行案</t>
+          <t>115年「點亮豐濱！族語詩歌高聲唱耶誕嘉年華暨文化健康站成果展」勞務採購案</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>9950000</v>
+        <v>1100000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -3821,7 +3819,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3831,7 +3829,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-1HLLC</t>
+          <t>FB1151218</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3841,11 +3839,11 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>嘉年華、成果展</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
@@ -3861,30 +3859,30 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>桃園市平鎮區公所</t>
+          <t>臺中市政府研究發展考核委員會</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>116年桃園市平鎮區元旦升旗典禮活動</t>
+          <t>「115年度臺中市經濟發展與城市行銷推廣案」委託專業服務案</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>450000</v>
+        <v>2520000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3894,21 +3892,21 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1151005A01</t>
+          <t>115RCP16</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>活動、典禮</t>
+          <t>行銷推廣、城市行銷</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
@@ -3924,25 +3922,25 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>彰化縣田中鎮公所</t>
+          <t>高雄市政府經濟發展局</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026田中藝術節–愛閱田中・藝起嗨劇場委託專業服務採購案</t>
+          <t>「2027高雄過好年聯合記者會」委託專業服務案</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>700000</v>
+        <v>500000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3952,12 +3950,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>115-081</t>
+          <t>115090</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3967,7 +3965,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>藝術節</t>
+          <t>記者會</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -3987,40 +3985,40 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>內政部</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>116年屏東縣政府社會處網路媒體行銷維運案</t>
+          <t>115年度合作社制度宣導短片託播案</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>2000000</v>
+        <v>800000</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>A058-1151007-2</t>
+          <t>115HT-NH090806</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4030,7 +4028,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>媒體行銷</t>
+          <t>宣導短片</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -4050,25 +4048,25 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>南投縣政府</t>
+          <t>花蓮縣議會</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>115年縣政成果及重大活動影音攝製行銷案</t>
+          <t>花蓮縣議會「第21屆議員宣誓就職典禮暨正副議長選舉」委託專業服務案</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>1400000</v>
+        <v>360000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4083,21 +4081,21 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>115-07-06-011E</t>
+          <t>115GA31</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>活動、行銷</t>
+          <t>典禮</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
@@ -4118,25 +4116,25 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>苗栗縣政府</t>
+          <t>南投縣水里鄉公所</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>「2027台灣燈會在苗栗」廣播錄製暨執行委託專業服務案</t>
+          <t>「2026水里觀光行銷暨農特產推廣系列活動」勞務採購案</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>500000</v>
+        <v>4300000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4146,21 +4144,21 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>115141f</t>
+          <t>115SHTS06</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>燈會</t>
+          <t>系列活動、觀光行銷、推廣</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
@@ -4181,20 +4179,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>臺南市政府經濟發展局</t>
+          <t>花蓮縣政府</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>「2027新化年貨大街」活動委託服務案</t>
+          <t>115年花蓮縣長青大學結業典禮暨成果展活動</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1100000</v>
+        <v>1150000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4209,7 +4207,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>115ECON72S1</t>
+          <t>SC1150020901</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4219,11 +4217,11 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>成果展、活動、典禮</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
@@ -4239,30 +4237,30 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>花蓮縣政府</t>
+          <t>臺南市政府經濟發展局</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026花蓮星潮原聲系列活動規劃執行案</t>
+          <t>「116年永康迎春嘉年華」活動規劃執行服務</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>40000000</v>
+        <v>600000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4272,7 +4270,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>AB1150007224</t>
+          <t>115ECON71S1</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4282,7 +4280,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>系列活動、活動規劃</t>
+          <t>嘉年華、活動規劃</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -4302,30 +4300,30 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>南投縣政府</t>
+          <t>臺北表演藝術中心</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>「2026南投花卉嘉年華－草屯展區系列活動」勞務採購案</t>
+          <t>第三屆臺北戲劇獎頒獎典禮暨系列活動製作執行勞務採購案</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>1000000</v>
+        <v>15000000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4335,7 +4333,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>1150602018G</t>
+          <t>TPACRD1150141</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4345,7 +4343,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>嘉年華、系列活動</t>
+          <t>頒獎典禮、系列活動</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -4365,25 +4363,25 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>內政部</t>
+          <t>屏東縣獅子鄉公所</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>116年第84屆兵役節慶祝大會暨頒獎典禮委外服務案</t>
+          <t>屏東縣獅子鄉115年度慶祝重陽節聯合表揚暨族語文化推廣與文化健康站成果展活動勞務採購案</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>1230000</v>
+        <v>1162700</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4398,21 +4396,21 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>115YJ-ST15</t>
+          <t>1151001AA</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>國際會議論壇/活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>大會、頒獎典禮</t>
+          <t>成果展、活動、推廣</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
@@ -4428,25 +4426,25 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>國立臺灣美術館</t>
+          <t>宜蘭縣政府</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">國家珍藏作品之線上藝廊推廣影片製作採購案 </t>
+          <t>「宜蘭縣115年國際移民嘉年華」活動規劃執行委託案</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>600000</v>
+        <v>400000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4461,21 +4459,21 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>115118</t>
+          <t>CVSL115019</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>影片製作、推廣</t>
+          <t>嘉年華、活動規劃</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
@@ -4491,30 +4489,30 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>苗栗縣苗栗市公所</t>
+          <t>財政部高雄國稅局</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>苗栗市2026冬迎璀璨歲末藝文嘉年華</t>
+          <t>115年度結合統一發票推行暨「來稅局找碴-觀察力培養計畫」租稅宣導活動委外服務案</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>2440000</v>
+        <v>445000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4524,21 +4522,21 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>C548</t>
+          <t>1150042</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>嘉年華</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
@@ -4554,25 +4552,25 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>苗栗縣苗栗市公所</t>
+          <t>國立臺中教育大學</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>115年度苗栗市親子蘿蔔節活動執行委託專業服務採購案</t>
+          <t>115年原住民族教育論壇暨原住民族教育資源中心成果交流會</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>1000000</v>
+        <v>1450000</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4587,21 +4585,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>B1600</t>
+          <t>115-C062</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>論壇</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
@@ -4617,30 +4615,30 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>桃園市政府工務局</t>
+          <t>衛生福利部疾病管制署</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>115年桃園市食農教育執行成果展委託專業服務案</t>
+          <t>「115年度防疫績優獎頒獎典禮專業服務」採購案</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>2000000</v>
+        <v>950000</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4650,7 +4648,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1151005-3</t>
+          <t>LA115028</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4660,7 +4658,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>成果展</t>
+          <t>頒獎典禮</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -4680,25 +4678,25 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>新竹縣尖石鄉公所</t>
+          <t>花蓮縣政府</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>新竹縣尖石鄉115年尖石鄉鄉長盃第二屆傳統路跑嘉年華暨傳統擲矛、傳統狩獵活動勞務採購案</t>
+          <t>115年花蓮縣精品咖啡行銷推廣計畫</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>950000</v>
+        <v>1100000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4713,17 +4711,17 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1159226</t>
+          <t>AG1150018061</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>嘉年華</t>
+          <t>行銷推廣</t>
         </is>
       </c>
       <c r="K68" t="n">
@@ -4743,21 +4741,21 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>嘉義縣文化觀光局</t>
+          <t>社團法人花蓮縣基督教會花蓮靈糧堂宣教協會</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>「116年度嘉義縣觀光旅遊數位整合行銷」委託專業服務案</t>
+          <t>2026花蓮幸福聖誕城行銷宣傳及城市聯合宣傳規劃案</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>2000000</v>
+        <v>6789600</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -4776,7 +4774,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1150011120</t>
+          <t>2026-2HLLC</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4786,7 +4784,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>整合行銷</t>
+          <t>行銷宣傳</t>
         </is>
       </c>
       <c r="K69" t="n">
@@ -4806,54 +4804,54 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>台灣中油股份有限公司探採事業部</t>
+          <t>社團法人花蓮縣基督教會花蓮靈糧堂宣教協會</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>碳封存監測資料彙整分析及社會溝通顧問服務</t>
+          <t>2026花蓮幸福聖誕城活動執行案</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>1490000</v>
+        <v>9950000</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>BEA1500013</t>
+          <t>2026-1HLLC</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>政策溝通</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>社會溝通</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="K70" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
@@ -4869,21 +4867,21 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>中央選舉委員會</t>
+          <t>桃園市平鎮區公所</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>115年地方公職人員選舉及公民投票選務滿意度民意調查採購案</t>
+          <t>116年桃園市平鎮區元旦升旗典禮活動</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>500000</v>
+        <v>450000</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -4902,21 +4900,21 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1150909</t>
+          <t>1151005A01</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>政策溝通</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>民意調查</t>
+          <t>活動、典禮</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
@@ -4932,25 +4930,25 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>桃園市政府捷運工程局</t>
+          <t>彰化縣田中鎮公所</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>桃園市八德區德和路一段第2階段通車活動委託服務案</t>
+          <t>2026田中藝術節–愛閱田中・藝起嗨劇場委託專業服務採購案</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>1000000</v>
+        <v>700000</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4960,12 +4958,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1151006</t>
+          <t>115-081</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4975,11 +4973,11 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>藝術節</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
@@ -4995,17 +4993,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>國防部</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>國軍招募宣傳電視廣告託播</t>
+          <t>116年屏東縣政府社會處網路媒體行銷維運案</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
@@ -5013,12 +5011,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>公開招標公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5028,7 +5026,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>CC15003L050</t>
+          <t>A058-1151007-2</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5038,11 +5036,11 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>廣告託播、宣傳</t>
+          <t>媒體行銷</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
@@ -5058,30 +5056,30 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>衛生福利部社會及家庭署</t>
+          <t>南投縣政府</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>116年度強化社會安全網績優人員及團體獎項品牌識別系統專業服務案</t>
+          <t>115年縣政成果及重大活動影音攝製行銷案</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>2550000</v>
+        <v>1400000</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5091,17 +5089,17 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>C116001</t>
+          <t>115-07-06-011E</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>品牌識別</t>
+          <t>活動、行銷</t>
         </is>
       </c>
       <c r="K74" t="n">
@@ -5121,30 +5119,30 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>臺北市政府觀光傳播局</t>
+          <t>苗栗縣政府</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>116年度臺北開齋節暨穆斯林友善城市推廣活動案</t>
+          <t>「2027台灣燈會在苗栗」廣播錄製暨執行委託專業服務案</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>4000000</v>
+        <v>500000</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5154,21 +5152,21 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>1150075</t>
+          <t>115141f</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>活動、推廣</t>
+          <t>燈會</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
@@ -5184,25 +5182,25 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>國立歷史博物館</t>
+          <t>臺南市政府經濟發展局</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>常設展手語導覽影片製作案</t>
+          <t>「2027新化年貨大街」活動委託服務案</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>950000</v>
+        <v>1100000</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5217,21 +5215,21 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>115046</t>
+          <t>115ECON72S1</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>影片製作</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
@@ -5247,25 +5245,25 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>內政部國土管理署</t>
+          <t>花蓮縣政府</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>116年度住宅政策推廣影音及多媒體製作案</t>
+          <t>2026花蓮星潮原聲系列活動規劃執行案</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>9950000</v>
+        <v>40000000</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5280,21 +5278,21 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>115A-066</t>
+          <t>AB1150007224</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>推廣、媒體</t>
+          <t>系列活動、活動規劃</t>
         </is>
       </c>
       <c r="K77" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
@@ -5310,30 +5308,30 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>高雄市政府勞工局訓練就業中心</t>
+          <t>南投縣政府</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>「116年度鳳山、岡山就業服務站現場徵才活動」委託服務案</t>
+          <t>「2026南投花卉嘉年華－草屯展區系列活動」勞務採購案</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>2892100</v>
+        <v>1000000</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5343,7 +5341,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>116F002</t>
+          <t>1150602018G</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5353,11 +5351,11 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>嘉年華、系列活動</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
@@ -5373,25 +5371,25 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>新北市政府勞工局</t>
+          <t>內政部</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>新北市政府116年度外國人文化與休閒活動計畫-越南、印尼活動委託專業服務採購案</t>
+          <t>116年第84屆兵役節慶祝大會暨頒獎典禮委外服務案</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>1300000</v>
+        <v>1230000</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5401,26 +5399,26 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>TPLAB115013</t>
+          <t>115YJ-ST15</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>國際會議論壇/活動執行</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>大會、頒獎典禮</t>
         </is>
       </c>
       <c r="K79" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
@@ -5436,25 +5434,25 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>臺中市石岡區公所</t>
+          <t>國立臺灣美術館</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>115年石岡童樂會暨水資源宣導活動</t>
+          <t xml:space="preserve">國家珍藏作品之線上藝廊推廣影片製作採購案 </t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>800000</v>
+        <v>600000</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5469,17 +5467,17 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>115SK20</t>
+          <t>115118</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>影片製作、推廣</t>
         </is>
       </c>
       <c r="K80" t="n">
@@ -5499,30 +5497,30 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>臺中市石岡區公所</t>
+          <t>苗栗縣苗栗市公所</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026臺中市民野餐日（石岡區）暨觀光活化水資源宣導活動</t>
+          <t>苗栗市2026冬迎璀璨歲末藝文嘉年華</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>920000</v>
+        <v>2440000</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5532,21 +5530,21 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>115SK19</t>
+          <t>C548</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>嘉年華</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
@@ -5562,30 +5560,30 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>新竹縣芎林鄉公所</t>
+          <t>苗栗縣苗栗市公所</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2027芎林路跑嘉年華活動計畫委託專業服務案</t>
+          <t>115年度苗栗市親子蘿蔔節活動執行委託專業服務採購案</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>2400000</v>
+        <v>1000000</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5595,7 +5593,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>1160001P</t>
+          <t>B1600</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5605,11 +5603,11 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>嘉年華、活動</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="K82" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
@@ -5625,25 +5623,25 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>海洋委員會</t>
+          <t>桃園市政府工務局</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>海洋博覽會整體規劃暨先期策略研析委託專業服務案</t>
+          <t>115年桃園市食農教育執行成果展委託專業服務案</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5658,21 +5656,21 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>OAC115044</t>
+          <t>1151005-3</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>博覽會</t>
+          <t>成果展</t>
         </is>
       </c>
       <c r="K83" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
@@ -5688,21 +5686,21 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>花蓮縣政府</t>
+          <t>新竹縣尖石鄉公所</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>115年花蓮宜居城市行銷採購案(開口契約)</t>
+          <t>新竹縣尖石鄉115年尖石鄉鄉長盃第二屆傳統路跑嘉年華暨傳統擲矛、傳統狩獵活動勞務採購案</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>9450000</v>
+        <v>950000</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -5711,7 +5709,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5721,17 +5719,17 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>SK1150005862</t>
+          <t>1159226</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>城市行銷</t>
+          <t>嘉年華</t>
         </is>
       </c>
       <c r="K84" t="n">
@@ -5751,30 +5749,30 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>花蓮縣政府</t>
+          <t>嘉義縣文化觀光局</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>115年花蓮縣社區照顧關懷據點及社區長照站成果展</t>
+          <t>「116年度嘉義縣觀光旅遊數位整合行銷」委託專業服務案</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>1250000</v>
+        <v>2000000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5784,17 +5782,17 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>SC1150020073</t>
+          <t>1150011120</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>成果展</t>
+          <t>整合行銷</t>
         </is>
       </c>
       <c r="K85" t="n">
@@ -5814,25 +5812,25 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>桃園市政府文化局</t>
+          <t>台灣中油股份有限公司探採事業部</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026桃園仙草花節系列活動-民歌演唱會委託專業服務案</t>
+          <t>碳封存監測資料彙整分析及社會溝通顧問服務</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>500000</v>
+        <v>1490000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5842,26 +5840,26 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>TYC115-39</t>
+          <t>BEA1500013</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>政策溝通</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>系列活動</t>
+          <t>社會溝通</t>
         </is>
       </c>
       <c r="K86" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
@@ -5877,30 +5875,30 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>宜蘭縣政府</t>
+          <t>中央選舉委員會</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>宜蘭縣115年度原有住宅無障礙設施補助委託辦理推廣宣導評估案</t>
+          <t>115年地方公職人員選舉及公民投票選務滿意度民意調查採購案</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>1210000</v>
+        <v>500000</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5910,21 +5908,21 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>CNSL115032</t>
+          <t>1150909</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>政策溝通</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>宣導、推廣</t>
+          <t>民意調查</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L87" s="3" t="inlineStr">
         <is>
@@ -5940,30 +5938,30 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>財團法人嘉義市文化基金會</t>
+          <t>桃園市政府捷運工程局</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026嘉義市管樂節晚會舞台暨表演節目規畫執行委託服務案</t>
+          <t>桃園市八德區德和路一段第2階段通車活動委託服務案</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>15000000</v>
+        <v>1000000</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5973,7 +5971,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>115A001</t>
+          <t>1151006</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5983,7 +5981,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>晚會</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K88" t="n">
@@ -6003,30 +6001,30 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>新竹市政府</t>
+          <t>國防部</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>「2026客家藝文活動」委託專業服務案</t>
+          <t>國軍招募宣傳電視廣告託播</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>2400000</v>
+        <v>2000000</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開招標公告</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6036,21 +6034,21 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>1150292</t>
+          <t>CC15003L050</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>廣告託播、宣傳</t>
         </is>
       </c>
       <c r="K89" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L89" s="3" t="inlineStr">
         <is>
@@ -6066,25 +6064,25 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>新北市政府觀光旅遊局</t>
+          <t>衛生福利部社會及家庭署</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>116年度跨媒體整合傳播採購案</t>
+          <t>116年度強化社會安全網績優人員及團體獎項品牌識別系統專業服務案</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>7350000</v>
+        <v>2550000</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -6099,7 +6097,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1151911877</t>
+          <t>C116001</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6109,11 +6107,11 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>整合傳播、跨媒體</t>
+          <t>品牌識別</t>
         </is>
       </c>
       <c r="K90" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
@@ -6129,25 +6127,25 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>司法院</t>
+          <t>臺北市政府觀光傳播局</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>司法院115年司法博物館主題活動規劃執行採購案</t>
+          <t>116年度臺北開齋節暨穆斯林友善城市推廣活動案</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>3400000</v>
+        <v>4000000</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6162,21 +6160,21 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>1151400844</t>
+          <t>1150075</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>活動規劃、主題活動</t>
+          <t>活動、推廣</t>
         </is>
       </c>
       <c r="K91" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L91" s="3" t="inlineStr">
         <is>
@@ -6192,25 +6190,25 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>彰化縣伸港鄉公所</t>
+          <t>國立歷史博物館</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2027年伸港飛揚-元旦升旗健行齊步走暨節能減碳宣導活動委託服務案</t>
+          <t>常設展手語導覽影片製作案</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>1152300</v>
+        <v>950000</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -6220,26 +6218,26 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1152006</t>
+          <t>115046</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>影片製作</t>
         </is>
       </c>
       <c r="K92" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
@@ -6255,30 +6253,30 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>臺東縣政府</t>
+          <t>內政部國土管理署</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>興隆國小--臺東縣115年度環境變遷與藍碳發展論壇暨體驗學習活動</t>
+          <t>116年度住宅政策推廣影音及多媒體製作案</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>420000</v>
+        <v>9950000</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6288,21 +6286,21 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>115310130545</t>
+          <t>115A-066</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>論壇</t>
+          <t>推廣、媒體</t>
         </is>
       </c>
       <c r="K93" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L93" s="3" t="inlineStr">
         <is>
@@ -6318,25 +6316,25 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>桃園市政府文化局</t>
+          <t>高雄市政府勞工局訓練就業中心</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026桃園社造博覽會規劃執行案</t>
+          <t>「116年度鳳山、岡山就業服務站現場徵才活動」委託服務案</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>2000000</v>
+        <v>2892100</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6351,21 +6349,21 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1150276</t>
+          <t>116F002</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>博覽會</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K94" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
@@ -6381,25 +6379,25 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>新北市政府水利局</t>
+          <t>新北市政府勞工局</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>新北市治水、清水、親水水環境治理成果影片製作案</t>
+          <t>新北市政府116年度外國人文化與休閒活動計畫-越南、印尼活動委託專業服務採購案</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>1200000</v>
+        <v>1300000</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -6409,26 +6407,26 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1150930A</t>
+          <t>TPLAB115013</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>影片製作</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K95" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L95" s="3" t="inlineStr">
         <is>
@@ -6444,25 +6442,25 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>彰化縣田中鎮公所</t>
+          <t>臺中市石岡區公所</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026田中藝術節–愛閱田中・藝起嗨劇場委託專業服務採購案</t>
+          <t>115年石岡童樂會暨水資源宣導活動</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>700000</v>
+        <v>800000</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -6477,21 +6475,21 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>115-081</t>
+          <t>115SK20</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>藝術節</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K96" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
@@ -6507,25 +6505,25 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>外交部領事事務局</t>
+          <t>臺中市石岡區公所</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>115年度推廣外交部領事事務局「LINE官方帳號」靜態貼圖廣告方案</t>
+          <t>2026臺中市民野餐日（石岡區）暨觀光活化水資源宣導活動</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>630000</v>
+        <v>920000</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -6540,21 +6538,21 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>T115027CB</t>
+          <t>115SK19</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>廣告、推廣</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K97" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L97" s="3" t="inlineStr">
         <is>
@@ -6570,68 +6568,1076 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>新竹縣芎林鄉公所</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2027芎林路跑嘉年華活動計畫委託專業服務案</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>1160001P</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>活動執行</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>嘉年華、活動</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>12</v>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>海洋委員會</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>海洋博覽會整體規劃暨先期策略研析委託專業服務案</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>OAC115044</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>國際會議論壇</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>博覽會</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>10</v>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>花蓮縣政府</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>115年花蓮宜居城市行銷採購案(開口契約)</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>9450000</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>SK1150005862</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>宣導行銷</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>城市行銷</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>8</v>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>花蓮縣政府</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>115年花蓮縣社區照顧關懷據點及社區長照站成果展</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>1250000</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>公開取得報價單或企劃書公告</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>SC1150020073</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>活動執行</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>成果展</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>8</v>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>桃園市政府文化局</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026桃園仙草花節系列活動-民歌演唱會委託專業服務案</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>500000</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>公開取得報價單或企劃書公告</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>TYC115-39</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>活動執行</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>系列活動</t>
+        </is>
+      </c>
+      <c r="K102" t="n">
+        <v>8</v>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>宜蘭縣政府</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>宜蘭縣115年度原有住宅無障礙設施補助委託辦理推廣宣導評估案</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>1210000</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>CNSL115032</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>宣導行銷</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>宣導、推廣</t>
+        </is>
+      </c>
+      <c r="K103" t="n">
+        <v>8</v>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>財團法人嘉義市文化基金會</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026嘉義市管樂節晚會舞台暨表演節目規畫執行委託服務案</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>115A001</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>活動執行</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>晚會</t>
+        </is>
+      </c>
+      <c r="K104" t="n">
+        <v>4</v>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>新竹市政府</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>「2026客家藝文活動」委託專業服務案</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>1150292</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>活動執行</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>活動</t>
+        </is>
+      </c>
+      <c r="K105" t="n">
+        <v>4</v>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>新北市政府觀光旅遊局</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>116年度跨媒體整合傳播採購案</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>7350000</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>1151911877</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>宣導行銷</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>整合傳播、跨媒體</t>
+        </is>
+      </c>
+      <c r="K106" t="n">
+        <v>16</v>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>司法院</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>司法院115年司法博物館主題活動規劃執行採購案</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>1151400844</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>活動執行</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>活動規劃、主題活動</t>
+        </is>
+      </c>
+      <c r="K107" t="n">
+        <v>16</v>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>彰化縣伸港鄉公所</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2027年伸港飛揚-元旦升旗健行齊步走暨節能減碳宣導活動委託服務案</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>1152300</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>公開取得報價單或企劃書公告</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>1152006</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>活動執行/宣導行銷</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>活動、宣導活動</t>
+        </is>
+      </c>
+      <c r="K108" t="n">
+        <v>12</v>
+      </c>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>臺東縣政府</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>興隆國小--臺東縣115年度環境變遷與藍碳發展論壇暨體驗學習活動</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>420000</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>公開取得報價單或企劃書公告</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>115310130545</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>國際會議論壇</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>論壇</t>
+        </is>
+      </c>
+      <c r="K109" t="n">
+        <v>10</v>
+      </c>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>桃園市政府文化局</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026桃園社造博覽會規劃執行案</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>1150276</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>國際會議論壇</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>博覽會</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
+        <v>10</v>
+      </c>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>新北市政府水利局</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>新北市治水、清水、親水水環境治理成果影片製作案</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>公開取得報價單或企劃書公告</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>1150930A</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>宣導行銷</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>影片製作</t>
+        </is>
+      </c>
+      <c r="K111" t="n">
+        <v>8</v>
+      </c>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>彰化縣田中鎮公所</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026田中藝術節–愛閱田中・藝起嗨劇場委託專業服務採購案</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>700000</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>公開取得報價單或企劃書公告</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>115-081</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>活動執行</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>藝術節</t>
+        </is>
+      </c>
+      <c r="K112" t="n">
+        <v>8</v>
+      </c>
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>外交部領事事務局</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>115年度推廣外交部領事事務局「LINE官方帳號」靜態貼圖廣告方案</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>630000</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>公開取得報價單或企劃書公告</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>T115027CB</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>宣導行銷</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>廣告、推廣</t>
+        </is>
+      </c>
+      <c r="K113" t="n">
+        <v>8</v>
+      </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
         <is>
           <t>勞動部勞動力發展署桃竹苗分署</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>116年機關整合行銷勞務採購案</t>
         </is>
       </c>
-      <c r="D98" s="2" t="n">
+      <c r="D114" s="2" t="n">
         <v>1330000</v>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="E114" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F114" t="inlineStr">
         <is>
           <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
         <is>
           <t>116Y020</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="I114" t="inlineStr">
         <is>
           <t>宣導行銷</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="J114" t="inlineStr">
         <is>
           <t>整合行銷</t>
         </is>
       </c>
-      <c r="K98" t="n">
+      <c r="K114" t="n">
         <v>8</v>
       </c>
-      <c r="L98" s="3" t="inlineStr">
-        <is>
-          <t>開啟</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
         <is>
           <t>2026-10-15 08:34</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M98"/>
+  <autoFilter ref="A1:M114"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -6730,6 +7736,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" r:id="rId95"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L97" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L114" r:id="rId113"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6779,13 +7801,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4195</v>
+        <v>4550</v>
       </c>
       <c r="C2" t="n">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>273077653</v>
+        <v>306863861</v>
       </c>
     </row>
   </sheetData>
@@ -6815,7 +7837,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>產生時間：2026-10-18 07:59　資料庫共 97 筆</t>
+          <t>產生時間：2026-10-19 08:10　資料庫共 113 筆</t>
         </is>
       </c>
     </row>

--- a/data/標案資料庫.xlsx
+++ b/data/標案資料庫.xlsx
@@ -12,7 +12,7 @@
     <sheet name="說明" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'標案資料庫'!$A$1:$M$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'標案資料庫'!$A$1:$M$124</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M114"/>
+  <dimension ref="A1:M124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -524,25 +524,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>國家人權博物館</t>
+          <t>衛生福利部</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>「解嚴40週年國際論壇暨紀念專書籌劃」委託專業服務案</t>
+          <t>116年度「社會工作專業人員表揚典禮暨宣導活動」</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2200000</v>
+        <v>2600000</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -557,21 +557,21 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>11590Z</t>
+          <t>M1604017</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>國際論壇、論壇</t>
+          <t>活動、典禮、宣導活動</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -580,28 +580,28 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>南投縣政府</t>
+          <t>高雄市政府新聞局</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>「2026南投花卉嘉年華－草屯展區系列活動」勞務採購案</t>
+          <t>施政成果暨大型活動平面整合行銷案</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1000000</v>
+        <v>1100000</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -615,26 +615,26 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1150602018G</t>
+          <t>1151015B</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>嘉年華、系列活動</t>
+          <t>活動、整合行銷</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -643,35 +643,37 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>臺南市政府農業局</t>
+          <t>高雄市政府工務局公園處</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>日本地區臺南市農漁產推廣暨行銷活動策畫與執行委託專業服務案</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr"/>
+          <t>115-116年度工務建設宣導活動案(開口契約)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>2445109</v>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -681,7 +683,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>115AGR080</t>
+          <t>11504SB012</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -691,7 +693,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>活動、行銷、推廣</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -704,32 +706,32 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>桃園市政府環境管理處</t>
+          <t>苗栗縣政府衛生局</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>115年度職業安全衛生業務標竿學習宣導活動計畫</t>
+          <t>115年預防保健業務之戶外廣告行銷推廣</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1300000</v>
+        <v>580000</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -739,22 +741,22 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1150036916</t>
+          <t>11532</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>行銷推廣、廣告</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -767,37 +769,37 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>南投縣政府社會及勞動局</t>
+          <t>臺北市立美術館</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>南投縣115年度國際身心障礙者日宣導活動</t>
+          <t>「當代藝術與技術論壇」錄影案</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2500000</v>
+        <v>220000</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -807,21 +809,21 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>115-10-10-005-E</t>
+          <t>115RE0118</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>論壇</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -830,32 +832,32 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>財團法人蘭陽農業發展基金會</t>
+          <t>桃園市政府客家事務局</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2027宜蘭綠色博覽會－海洋館委託專業服務案</t>
+          <t>桃園市政府客家事務局115-116年桃園市客家文化館展覽活動等營運管理勞務採購案</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7000000</v>
+        <v>5100000</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -870,21 +872,21 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>115101305</t>
+          <t>115-022</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>博覽會</t>
+          <t>活動、展覽</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -893,37 +895,37 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>財團法人蘭陽農業發展基金會</t>
+          <t>南投縣政府</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2027宜蘭綠色博覽會－森林館委託專業服務案</t>
+          <t>115年度幸福南投短影音行銷宣傳採購案</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>3950000</v>
+        <v>1400000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -933,21 +935,21 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>115101301</t>
+          <t>115-07-07-006G</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>博覽會</t>
+          <t>行銷宣傳</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -956,47 +958,47 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>雲林縣政府</t>
+          <t>農業部林業及自然保育署花蓮分署</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>「2026雲林文創聯合徵選暨雲林設計獎」頒獎典禮委託規劃執行案</t>
+          <t>林田山遊客中心佈展(含活動駐館)委託專業服務</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>500000</v>
+        <v>5900000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1152H10116</t>
+          <t>115m011</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1006,11 +1008,11 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>頒獎典禮</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -1019,37 +1021,37 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>臺北市教師研習中心</t>
+          <t>臺中市神岡區公所</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>116年度優質學校頒獎典禮、杏壇芬芳獎表揚典禮、臺北教育111標竿學校頒獎典禮採購案</t>
+          <t>【2026臺中市民野餐日(神岡區)雙場地活動】委託專業服務採購案</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>869500</v>
+        <v>1920000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1059,7 +1061,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>11605</t>
+          <t>115-LS37</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1069,11 +1071,11 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>頒獎典禮</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -1082,37 +1084,37 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>臺中市政府數位發展局</t>
+          <t>臺中市政府客家事務委員會</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>台中通特店消費推廣暨抽獎活動案</t>
+          <t>2027臺中東勢新丁粄節-文宣暨會場佈置委託專業服務勞務採購案</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>950000</v>
+        <v>1750000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1122,21 +1124,21 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>115B-10</t>
+          <t>1151102</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>活動、推廣</t>
+          <t>文宣</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1147,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
@@ -1157,16 +1159,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>桃園市政府客家事務局</t>
+          <t>國家人權博物館</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>「桃園市客家文化館開館系列活動」勞務採購案</t>
+          <t>「解嚴40週年國際論壇暨紀念專書籌劃」委託專業服務案</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>5500000</v>
+        <v>2200000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1185,21 +1187,21 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>115-021</t>
+          <t>11590Z</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>系列活動</t>
+          <t>國際論壇、論壇</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
@@ -1220,49 +1222,49 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>嘉義市政府</t>
+          <t>南投縣政府</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>嘉義市政府116年家庭暴力暨性侵害防治中心宣導行銷計畫</t>
+          <t>「2026南投花卉嘉年華－草屯展區系列活動」勞務採購案</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1800000</v>
+        <v>1000000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>115266</t>
+          <t>1150602018G</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>宣導、行銷</t>
+          <t>嘉年華、系列活動</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
@@ -1283,17 +1285,15 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>國家科學及技術委員會南部科學園區管理局</t>
+          <t>臺南市政府農業局</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>國家科學及技術委員會116年度科學園區滿意度調查計畫</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>1236708</v>
-      </c>
+          <t>日本地區臺南市農漁產推廣暨行銷活動策畫與執行委託專業服務案</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>2026-10-23</t>
@@ -1311,21 +1311,21 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>115660D01151</t>
+          <t>115AGR080</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>政策溝通</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>滿意度調查</t>
+          <t>活動、行銷、推廣</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
@@ -1346,25 +1346,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>農業部林業及自然保育署阿里山林業鐵路及文化資產管理處</t>
+          <t>桃園市政府環境管理處</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>116-117年「阿里山林鐵行動學校」跨館際展覽委託專業服務案</t>
+          <t>115年度職業安全衛生業務標竿學習宣導活動計畫</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>2800000</v>
+        <v>1300000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1374,21 +1374,21 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>116-EDU-001</t>
+          <t>1150036916</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>展覽</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
@@ -1409,16 +1409,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>新北市政府觀光旅遊局</t>
+          <t>南投縣政府社會及勞動局</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>115年新北市平日住宿及生日券獎助活動專案管理委託專業服務案</t>
+          <t>南投縣115年度國際身心障礙者日宣導活動</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>700000</v>
+        <v>2500000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1437,21 +1437,21 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1152038719</t>
+          <t>115-10-10-005-E</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
@@ -1472,25 +1472,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>中華郵政股份有限公司</t>
+          <t>財團法人蘭陽農業發展基金會</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>「羊來了-生肖郵票特展」策、布展及開幕活動委託服務</t>
+          <t>2027宜蘭綠色博覽會－海洋館委託專業服務案</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1480000</v>
+        <v>7000000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1500,21 +1500,21 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>115-3-167</t>
+          <t>115101305</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>博覽會</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
@@ -1530,25 +1530,25 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>桃園市政府藝文設施管理中心</t>
+          <t>財團法人蘭陽農業發展基金會</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>「2027桃園鐵玫瑰藝術節活動執行統籌及行銷」委託專業服務採購案</t>
+          <t>2027宜蘭綠色博覽會－森林館委託專業服務案</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>9000000</v>
+        <v>3950000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1558,26 +1558,26 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>115AFMC-017</t>
+          <t>115101301</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>活動執行、藝術節、行銷</t>
+          <t>博覽會</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
@@ -1586,32 +1586,32 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>屏東縣獅子鄉公所</t>
+          <t>雲林縣政府</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>屏東縣獅子鄉115年度慶祝重陽節聯合表揚暨族語文化推廣與文化健康站成果展活動勞務採購案</t>
+          <t>「2026雲林文創聯合徵選暨雲林設計獎」頒獎典禮委託規劃執行案</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1162700</v>
+        <v>500000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1626,21 +1626,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1151001AA</t>
+          <t>1152H10116</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>成果展、活動、推廣</t>
+          <t>頒獎典禮</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
@@ -1649,37 +1649,37 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>勞動部勞動力發展署雲嘉南分署</t>
+          <t>臺北市教師研習中心</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>116年度社群平台整合行銷委託計畫</t>
+          <t>116年度優質學校頒獎典禮、杏壇芬芳獎表揚典禮、臺北教育111標竿學校頒獎典禮採購案</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>2000000</v>
+        <v>869500</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1689,21 +1689,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>yctrb1150129</t>
+          <t>11605</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>整合行銷、社群平台</t>
+          <t>頒獎典禮</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
@@ -1712,32 +1712,32 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>內政部</t>
+          <t>臺中市政府數位發展局</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>116年第84屆兵役節慶祝大會暨頒獎典禮委外服務案</t>
+          <t>台中通特店消費推廣暨抽獎活動案</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1230000</v>
+        <v>950000</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1747,26 +1747,26 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>115YJ-ST15</t>
+          <t>115B-10</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>國際會議論壇/活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>大會、頒獎典禮</t>
+          <t>活動、推廣</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
@@ -1775,32 +1775,32 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>桃園市八德區公所</t>
+          <t>桃園市政府客家事務局</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>116年度桃園市元旦升旗典禮活動規劃與執行</t>
+          <t>「桃園市客家文化館開館系列活動」勞務採購案</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>1600000</v>
+        <v>5500000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>BB1151015</t>
+          <t>115-021</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1825,11 +1825,11 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>活動規劃、典禮</t>
+          <t>系列活動</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
@@ -1838,37 +1838,37 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>國立臺中教育大學</t>
+          <t>嘉義市政府</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>數位內容充實與推廣總計畫成果紀錄影片製作採購案</t>
+          <t>嘉義市政府116年家庭暴力暨性侵害防治中心宣導行銷計畫</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>465000</v>
+        <v>1800000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>115-C063</t>
+          <t>115266</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1888,11 +1888,11 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>影片製作、推廣</t>
+          <t>宣導、行銷</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
@@ -1901,37 +1901,37 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>文化部</t>
+          <t>國家科學及技術委員會南部科學園區管理局</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>文化部「蒙藏文化情境展示及體驗活動」展場設計製作布卸展及活動執行藝文採購案</t>
+          <t>國家科學及技術委員會116年度科學園區滿意度調查計畫</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>3350000</v>
+        <v>1236708</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1941,21 +1941,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>11510159</t>
+          <t>115660D01151</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>政策溝通</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>滿意度調查</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
@@ -1964,37 +1964,37 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>國立雲林科技大學</t>
+          <t>農業部林業及自然保育署阿里山林業鐵路及文化資產管理處</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026研發成果展場地佈置案</t>
+          <t>116-117年「阿里山林鐵行動學校」跨館際展覽委託專業服務案</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>840000</v>
+        <v>2800000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>HTL115040</t>
+          <t>116-EDU-001</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2014,11 +2014,11 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>成果展</t>
+          <t>展覽</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
@@ -2027,32 +2027,32 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>桃園市政府觀光旅遊局</t>
+          <t>新北市政府觀光旅遊局</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>116年桃園觀光旅遊局輿情蒐集及通報服務勞務採購案</t>
+          <t>115年新北市平日住宿及生日券獎助活動專案管理委託專業服務案</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>247008</v>
+        <v>700000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2067,21 +2067,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1151015-AA1</t>
+          <t>1152038719</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>政策溝通</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>輿情</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
@@ -2090,28 +2090,28 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>臺中市立圖書館</t>
+          <t>中華郵政股份有限公司</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026臺中市立圖書館羅布森圖書館展覽委託專業服務採購案</t>
+          <t>「羊來了-生肖郵票特展」策、布展及開幕活動委託服務</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1120000</v>
+        <v>1480000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>115058</t>
+          <t>115-3-167</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>展覽</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
@@ -2165,49 +2165,49 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>桃園市政府藝文設施管理中心</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>115年客家記憶共創計畫-客家文化中心古契約展覽策劃執行</t>
+          <t>「2027桃園鐵玫瑰藝術節活動執行統籌及行銷」委託專業服務採購案</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>850000</v>
+        <v>9000000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>A132-1151015-1</t>
+          <t>115AFMC-017</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>展覽</t>
+          <t>活動執行、藝術節、行銷</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
@@ -2223,21 +2223,21 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>廣亞學校財團法人育達科技大學</t>
+          <t>屏東縣獅子鄉公所</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>研究發展處創新創業輔導暨育成中心115年青年創業工作坊專案管理計畫青年遴選活動頒獎典禮暨成果展評選採購</t>
+          <t>屏東縣獅子鄉115年度慶祝重陽節聯合表揚暨族語文化推廣與文化健康站成果展活動勞務採購案</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>350000</v>
+        <v>1162700</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2251,26 +2251,26 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>115J-04</t>
+          <t>1151001AA</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>頒獎典禮、成果展、活動、工作坊</t>
+          <t>成果展、活動、推廣</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
@@ -2279,37 +2279,37 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>苗栗縣政府衛生局</t>
+          <t>勞動部勞動力發展署雲嘉南分署</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>115年衛生教育之媒體廣告行銷推廣</t>
+          <t>116年度社群平台整合行銷委託計畫</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>770000</v>
+        <v>2000000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>11535</t>
+          <t>yctrb1150129</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>行銷推廣、廣告、媒體</t>
+          <t>整合行銷、社群平台</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2342,61 +2342,61 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>新竹市政府</t>
+          <t>內政部</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>116年新竹市政府城市行銷處社群網站管理</t>
+          <t>116年第84屆兵役節慶祝大會暨頒獎典禮委外服務案</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1900000</v>
+        <v>1230000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1150300</t>
+          <t>115YJ-ST15</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>國際會議論壇/活動執行</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>城市行銷、社群網站</t>
+          <t>大會、頒獎典禮</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
@@ -2405,37 +2405,37 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>高雄市政府地政局</t>
+          <t>桃園市八德區公所</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>115年度不動產防詐暨交易安全宣導活動委外服務案</t>
+          <t>116年度桃園市元旦升旗典禮活動規劃與執行</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>400000</v>
+        <v>1600000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2445,17 +2445,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>115019</t>
+          <t>BB1151015</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>活動規劃、典禮</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2468,37 +2468,37 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>桃園市政府環境保護局</t>
+          <t>國立臺中教育大學</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>116年社群網路環境教育推廣維運計畫</t>
+          <t>數位內容充實與推廣總計畫成果紀錄影片製作採購案</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>3800000</v>
+        <v>465000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1150085608</t>
+          <t>115-C063</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2518,11 +2518,11 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>推廣、社群</t>
+          <t>影片製作、推廣</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
@@ -2531,37 +2531,37 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>嘉義縣表演藝術中心</t>
+          <t>文化部</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>嘉義縣表演藝術中心115年表演節目整合傳播委託專業服務案</t>
+          <t>文化部「蒙藏文化情境展示及體驗活動」展場設計製作布卸展及活動執行藝文採購案</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>800000</v>
+        <v>3350000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2571,17 +2571,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1150002654</t>
+          <t>11510159</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>整合傳播</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2594,32 +2594,32 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>南投縣水里鄉公所</t>
+          <t>國立雲林科技大學</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>「2026水里觀光行銷暨農特產品推廣系列活動—煙火設計及施放勞務採購案」</t>
+          <t>2026研發成果展場地佈置案</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>1000000</v>
+        <v>840000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2634,21 +2634,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>115SHTS07</t>
+          <t>HTL115040</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>系列活動、觀光行銷、推廣</t>
+          <t>成果展</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
@@ -2657,32 +2657,32 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>國立臺灣大學</t>
+          <t>桃園市政府觀光旅遊局</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2027年臺大杜鵑花節學系博覽會場佈</t>
+          <t>116年桃園觀光旅遊局輿情蒐集及通報服務勞務採購案</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1250000</v>
+        <v>247008</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2697,21 +2697,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1150963</t>
+          <t>1151015-AA1</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>政策溝通</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>博覽會</t>
+          <t>輿情</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
@@ -2720,32 +2720,32 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>高雄市政府運動發展局</t>
+          <t>臺中市立圖書館</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>企業22年甲級排球聯賽高雄台電女子排球隊主場賽事行銷活動案</t>
+          <t>2026臺中市立圖書館羅布森圖書館展覽委託專業服務採購案</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>590000</v>
+        <v>1120000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2760,21 +2760,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>115-B-76</t>
+          <t>115058</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>活動、行銷</t>
+          <t>展覽</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
@@ -2783,37 +2783,37 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>115年度管路灌溉成果推廣活動</t>
+          <t>115年客家記憶共創計畫-客家文化中心古契約展覽策劃執行</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>4000000</v>
+        <v>850000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2823,21 +2823,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>TY115B030</t>
+          <t>A132-1151015-1</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>活動、推廣</t>
+          <t>展覽</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
@@ -2846,28 +2846,28 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>臺北市政府工務局</t>
+          <t>廣亞學校財團法人育達科技大學</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>116年全國大專院校運動會開閉幕典禮活動</t>
+          <t>研究發展處創新創業輔導暨育成中心115年青年創業工作坊專案管理計畫青年遴選活動頒獎典禮暨成果展評選採購</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>10000000</v>
+        <v>350000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2876,17 +2876,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1150826S0096</t>
+          <t>115J-04</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2896,11 +2896,11 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>活動、典禮</t>
+          <t>頒獎典禮、成果展、活動、工作坊</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
@@ -2916,25 +2916,25 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>臺中市政府環境保護局</t>
+          <t>苗栗縣政府衛生局</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>115年度環保英雄歲末嘉年華活動採購案</t>
+          <t>115年衛生教育之媒體廣告行銷推廣</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>1105000</v>
+        <v>770000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2949,21 +2949,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>N1151013101</t>
+          <t>11535</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>嘉年華</t>
+          <t>行銷推廣、廣告、媒體</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
@@ -2979,25 +2979,25 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>新北市政府環境保護局</t>
+          <t>新竹市政府</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>116年度資源回收推動及形象改造計畫</t>
+          <t>116年新竹市政府城市行銷處社群網站管理</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>9670000</v>
+        <v>1900000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>115-177</t>
+          <t>1150300</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3022,11 +3022,11 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>形象改造</t>
+          <t>城市行銷、社群網站</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
@@ -3042,30 +3042,30 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>原住民族委員會原住民族文化發展中心</t>
+          <t>高雄市政府地政局</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>116年公益彩券回饋金計畫-文化觀光行銷專業人才勞務採購案</t>
+          <t>115年度不動產防詐暨交易安全宣導活動委外服務案</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>4681825</v>
+        <v>400000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3075,21 +3075,21 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1150006860</t>
+          <t>115019</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>觀光行銷</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
@@ -3105,30 +3105,30 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>勞動部</t>
+          <t>桃園市政府環境保護局</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>115年度「勞工自願提繳退休金影片製作案」</t>
+          <t>116年社群網路環境教育推廣維運計畫</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>997920</v>
+        <v>3800000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>03-11509091</t>
+          <t>1150085608</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>影片製作</t>
+          <t>推廣、社群</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3168,25 +3168,25 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>桃園市政府捷運工程局</t>
+          <t>嘉義縣表演藝術中心</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>桃園市八德區德和路一段第2階段通車活動委託服務案</t>
+          <t>嘉義縣表演藝術中心115年表演節目整合傳播委託專業服務案</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>1000000</v>
+        <v>800000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3196,26 +3196,26 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1151006</t>
+          <t>1150002654</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>整合傳播</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
@@ -3231,30 +3231,30 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>中華郵政股份有限公司</t>
+          <t>南投縣水里鄉公所</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>115年度郵政形象廣告電視託播</t>
+          <t>「2026水里觀光行銷暨農特產品推廣系列活動—煙火設計及施放勞務採購案」</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>公開招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3264,21 +3264,21 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>115-5-294</t>
+          <t>115SHTS07</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>電視託播、形象廣告</t>
+          <t>系列活動、觀光行銷、推廣</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
@@ -3294,30 +3294,30 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>臺銀人壽保險股份有限公司</t>
+          <t>國立臺灣大學</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>115年壽險行銷研討會-理財激勵專案</t>
+          <t>2027年臺大杜鵑花節學系博覽會場佈</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>8330000</v>
+        <v>1250000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>115-005-106-CL-1-798</t>
+          <t>1150963</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>研討會</t>
+          <t>博覽會</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -3357,23 +3357,25 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>國立臺南大學</t>
+          <t>高雄市政府運動發展局</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>幼兒美感教育社群與國際交流影音紀錄</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr"/>
+          <t>企業22年甲級排球聯賽高雄台電女子排球隊主場賽事行銷活動案</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>590000</v>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3388,21 +3390,21 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1151065-TL</t>
+          <t>115-B-76</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>國際會議論壇/宣導行銷</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>國際交流、社群</t>
+          <t>活動、行銷</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
@@ -3418,30 +3420,30 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>臺東縣鹿野鄉公所</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026鹿野馬拉松系列活動賽事勞務採購案</t>
+          <t>115年度管路灌溉成果推廣活動</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>1460000</v>
+        <v>4000000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3451,17 +3453,17 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1150929</t>
+          <t>TY115B030</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>系列活動</t>
+          <t>活動、推廣</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -3481,40 +3483,40 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>臺中市大里區公所</t>
+          <t>臺北市政府工務局</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>115年大里區運動會暨里鄰長健行活動規劃執行委託專業服務採購</t>
+          <t>116年全國大專院校運動會開閉幕典禮活動</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>400000</v>
+        <v>10000000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>115dali032</t>
+          <t>1150826S0096</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3524,7 +3526,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>活動規劃</t>
+          <t>活動、典禮</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3544,25 +3546,25 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>桃園市復興區公所</t>
+          <t>臺中市政府環境保護局</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>桃園市復興區115年度甜柿推廣活動好柿發聲勞務採購案</t>
+          <t>115年度環保英雄歲末嘉年華活動採購案</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>766500</v>
+        <v>1105000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3577,17 +3579,17 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>115D52</t>
+          <t>N1151013101</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>活動、推廣</t>
+          <t>嘉年華</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -3607,30 +3609,30 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>南投縣政府</t>
+          <t>新北市政府環境保護局</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>115年度南投拍片好所在影視音協拍多元媒體宣傳採購案</t>
+          <t>116年度資源回收推動及形象改造計畫</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>1100000</v>
+        <v>9670000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3640,7 +3642,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1150707005G</t>
+          <t>115-177</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3650,7 +3652,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>媒體宣傳</t>
+          <t>形象改造</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -3670,21 +3672,21 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>農業部林業及自然保育署阿里山林業鐵路及文化資產管理處</t>
+          <t>原住民族委員會原住民族文化發展中心</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>阿里山林鐵服務中心小葉子館之展覽、賣店、服務設施規劃暨製作案</t>
+          <t>116年公益彩券回饋金計畫-文化觀光行銷專業人才勞務採購案</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>2500000</v>
+        <v>4681825</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -3698,26 +3700,26 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>115-ALI-001</t>
+          <t>1150006860</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>展覽</t>
+          <t>觀光行銷</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
@@ -3733,25 +3735,25 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>苗栗縣政府</t>
+          <t>勞動部</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>苗栗縣政府115年度短影音攝製暨電視宣傳委託專業服務案</t>
+          <t>115年度「勞工自願提繳退休金影片製作案」</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>650000</v>
+        <v>997920</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3766,7 +3768,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>115147f</t>
+          <t>03-11509091</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3776,11 +3778,11 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>宣傳</t>
+          <t>影片製作</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
@@ -3796,21 +3798,21 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>花蓮縣豐濱鄉公所</t>
+          <t>桃園市政府捷運工程局</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>115年「點亮豐濱！族語詩歌高聲唱耶誕嘉年華暨文化健康站成果展」勞務採購案</t>
+          <t>桃園市八德區德和路一段第2階段通車活動委託服務案</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1100000</v>
+        <v>1000000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -3824,12 +3826,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>FB1151218</t>
+          <t>1151006</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3839,11 +3841,11 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>嘉年華、成果展</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
@@ -3859,30 +3861,30 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>臺中市政府研究發展考核委員會</t>
+          <t>中華郵政股份有限公司</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>「115年度臺中市經濟發展與城市行銷推廣案」委託專業服務案</t>
+          <t>115年度郵政形象廣告電視託播</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>2520000</v>
+        <v>6000000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開招標公告</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3892,7 +3894,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>115RCP16</t>
+          <t>115-5-294</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3902,7 +3904,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>行銷推廣、城市行銷</t>
+          <t>電視託播、形象廣告</t>
         </is>
       </c>
       <c r="K55" t="n">
@@ -3922,30 +3924,30 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>高雄市政府經濟發展局</t>
+          <t>臺銀人壽保險股份有限公司</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>「2027高雄過好年聯合記者會」委託專業服務案</t>
+          <t>115年壽險行銷研討會-理財激勵專案</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>500000</v>
+        <v>8330000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3955,21 +3957,21 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>115090</t>
+          <t>115-005-106-CL-1-798</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>記者會</t>
+          <t>研討會</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
@@ -3985,25 +3987,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>內政部</t>
+          <t>國立臺南大學</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>115年度合作社制度宣導短片託播案</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="n">
-        <v>800000</v>
-      </c>
+          <t>幼兒美感教育社群與國際交流影音紀錄</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4013,26 +4013,26 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>115HT-NH090806</t>
+          <t>1151065-TL</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>國際會議論壇/宣導行銷</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>宣導短片</t>
+          <t>國際交流、社群</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
@@ -4048,21 +4048,21 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>花蓮縣議會</t>
+          <t>臺東縣鹿野鄉公所</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>花蓮縣議會「第21屆議員宣誓就職典禮暨正副議長選舉」委託專業服務案</t>
+          <t>2026鹿野馬拉松系列活動賽事勞務採購案</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>360000</v>
+        <v>1460000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>115GA31</t>
+          <t>1150929</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4091,11 +4091,11 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>典禮</t>
+          <t>系列活動</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
@@ -4111,30 +4111,30 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>南投縣水里鄉公所</t>
+          <t>臺中市大里區公所</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>「2026水里觀光行銷暨農特產推廣系列活動」勞務採購案</t>
+          <t>115年大里區運動會暨里鄰長健行活動規劃執行委託專業服務採購</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>4300000</v>
+        <v>400000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4144,21 +4144,21 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>115SHTS06</t>
+          <t>115dali032</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>系列活動、觀光行銷、推廣</t>
+          <t>活動規劃</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
@@ -4174,25 +4174,25 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>花蓮縣政府</t>
+          <t>桃園市復興區公所</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>115年花蓮縣長青大學結業典禮暨成果展活動</t>
+          <t>桃園市復興區115年度甜柿推廣活動好柿發聲勞務採購案</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1150000</v>
+        <v>766500</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4207,21 +4207,21 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>SC1150020901</t>
+          <t>115D52</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>成果展、活動、典禮</t>
+          <t>活動、推廣</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
@@ -4237,25 +4237,25 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>臺南市政府經濟發展局</t>
+          <t>南投縣政府</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>「116年永康迎春嘉年華」活動規劃執行服務</t>
+          <t>115年度南投拍片好所在影視音協拍多元媒體宣傳採購案</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>600000</v>
+        <v>1100000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4270,21 +4270,21 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>115ECON71S1</t>
+          <t>1150707005G</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>嘉年華、活動規劃</t>
+          <t>媒體宣傳</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
@@ -4300,25 +4300,25 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>臺北表演藝術中心</t>
+          <t>農業部林業及自然保育署阿里山林業鐵路及文化資產管理處</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>第三屆臺北戲劇獎頒獎典禮暨系列活動製作執行勞務採購案</t>
+          <t>阿里山林鐵服務中心小葉子館之展覽、賣店、服務設施規劃暨製作案</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>15000000</v>
+        <v>2500000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4328,12 +4328,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>TPACRD1150141</t>
+          <t>115-ALI-001</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4343,11 +4343,11 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>頒獎典禮、系列活動</t>
+          <t>展覽</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
@@ -4363,25 +4363,25 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>屏東縣獅子鄉公所</t>
+          <t>苗栗縣政府</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>屏東縣獅子鄉115年度慶祝重陽節聯合表揚暨族語文化推廣與文化健康站成果展活動勞務採購案</t>
+          <t>苗栗縣政府115年度短影音攝製暨電視宣傳委託專業服務案</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>1162700</v>
+        <v>650000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4396,21 +4396,21 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>1151001AA</t>
+          <t>115147f</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>成果展、活動、推廣</t>
+          <t>宣傳</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
@@ -4426,21 +4426,21 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>宜蘭縣政府</t>
+          <t>花蓮縣豐濱鄉公所</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>「宜蘭縣115年國際移民嘉年華」活動規劃執行委託案</t>
+          <t>115年「點亮豐濱！族語詩歌高聲唱耶誕嘉年華暨文化健康站成果展」勞務採購案</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>400000</v>
+        <v>1100000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>CVSL115019</t>
+          <t>FB1151218</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>嘉年華、活動規劃</t>
+          <t>嘉年華、成果展</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -4489,30 +4489,30 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>財政部高雄國稅局</t>
+          <t>臺中市政府研究發展考核委員會</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>115年度結合統一發票推行暨「來稅局找碴-觀察力培養計畫」租稅宣導活動委外服務案</t>
+          <t>「115年度臺中市經濟發展與城市行銷推廣案」委託專業服務案</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>445000</v>
+        <v>2520000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4522,21 +4522,21 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1150042</t>
+          <t>115RCP16</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>行銷推廣、城市行銷</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
@@ -4552,25 +4552,25 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>國立臺中教育大學</t>
+          <t>高雄市政府經濟發展局</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>115年原住民族教育論壇暨原住民族教育資源中心成果交流會</t>
+          <t>「2027高雄過好年聯合記者會」委託專業服務案</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>1450000</v>
+        <v>500000</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4585,21 +4585,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>115-C062</t>
+          <t>115090</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>論壇</t>
+          <t>記者會</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
@@ -4615,25 +4615,25 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>衛生福利部疾病管制署</t>
+          <t>內政部</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>「115年度防疫績優獎頒獎典禮專業服務」採購案</t>
+          <t>115年度合作社制度宣導短片託播案</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>950000</v>
+        <v>800000</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4643,22 +4643,22 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>LA115028</t>
+          <t>115HT-NH090806</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>頒獎典禮</t>
+          <t>宣導短片</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -4678,25 +4678,25 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>花蓮縣政府</t>
+          <t>花蓮縣議會</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>115年花蓮縣精品咖啡行銷推廣計畫</t>
+          <t>花蓮縣議會「第21屆議員宣誓就職典禮暨正副議長選舉」委託專業服務案</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>1100000</v>
+        <v>360000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4711,21 +4711,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>AG1150018061</t>
+          <t>115GA31</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>行銷推廣</t>
+          <t>典禮</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
@@ -4746,20 +4746,20 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>社團法人花蓮縣基督教會花蓮靈糧堂宣教協會</t>
+          <t>南投縣水里鄉公所</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026花蓮幸福聖誕城行銷宣傳及城市聯合宣傳規劃案</t>
+          <t>「2026水里觀光行銷暨農特產推廣系列活動」勞務採購案</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>6789600</v>
+        <v>4300000</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4774,21 +4774,21 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-2HLLC</t>
+          <t>115SHTS06</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>行銷宣傳</t>
+          <t>系列活動、觀光行銷、推廣</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
@@ -4809,25 +4809,25 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>社團法人花蓮縣基督教會花蓮靈糧堂宣教協會</t>
+          <t>花蓮縣政府</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026花蓮幸福聖誕城活動執行案</t>
+          <t>115年花蓮縣長青大學結業典禮暨成果展活動</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>9950000</v>
+        <v>1150000</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-1HLLC</t>
+          <t>SC1150020901</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4847,11 +4847,11 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>成果展、活動、典禮</t>
         </is>
       </c>
       <c r="K70" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
@@ -4872,20 +4872,20 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>桃園市平鎮區公所</t>
+          <t>臺南市政府經濟發展局</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>116年桃園市平鎮區元旦升旗典禮活動</t>
+          <t>「116年永康迎春嘉年華」活動規劃執行服務</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>450000</v>
+        <v>600000</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1151005A01</t>
+          <t>115ECON71S1</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4910,11 +4910,11 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>活動、典禮</t>
+          <t>嘉年華、活動規劃</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
@@ -4935,35 +4935,35 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>彰化縣田中鎮公所</t>
+          <t>臺北表演藝術中心</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026田中藝術節–愛閱田中・藝起嗨劇場委託專業服務採購案</t>
+          <t>第三屆臺北戲劇獎頒獎典禮暨系列活動製作執行勞務採購案</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>700000</v>
+        <v>15000000</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>115-081</t>
+          <t>TPACRD1150141</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4973,11 +4973,11 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>藝術節</t>
+          <t>頒獎典禮、系列活動</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
@@ -4998,25 +4998,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>屏東縣獅子鄉公所</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>116年屏東縣政府社會處網路媒體行銷維運案</t>
+          <t>屏東縣獅子鄉115年度慶祝重陽節聯合表揚暨族語文化推廣與文化健康站成果展活動勞務採購案</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>2000000</v>
+        <v>1162700</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5026,21 +5026,21 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>A058-1151007-2</t>
+          <t>1151001AA</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>媒體行銷</t>
+          <t>成果展、活動、推廣</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
@@ -5061,20 +5061,20 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>南投縣政府</t>
+          <t>宜蘭縣政府</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>115年縣政成果及重大活動影音攝製行銷案</t>
+          <t>「宜蘭縣115年國際移民嘉年華」活動規劃執行委託案</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>1400000</v>
+        <v>400000</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -5089,21 +5089,21 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>115-07-06-011E</t>
+          <t>CVSL115019</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>活動、行銷</t>
+          <t>嘉年華、活動規劃</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
@@ -5124,20 +5124,20 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>苗栗縣政府</t>
+          <t>財政部高雄國稅局</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>「2027台灣燈會在苗栗」廣播錄製暨執行委託專業服務案</t>
+          <t>115年度結合統一發票推行暨「來稅局找碴-觀察力培養計畫」租稅宣導活動委外服務案</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>500000</v>
+        <v>445000</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5152,21 +5152,21 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>115141f</t>
+          <t>1150042</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>燈會</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
@@ -5187,20 +5187,20 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>臺南市政府經濟發展局</t>
+          <t>國立臺中教育大學</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>「2027新化年貨大街」活動委託服務案</t>
+          <t>115年原住民族教育論壇暨原住民族教育資源中心成果交流會</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>1100000</v>
+        <v>1450000</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5215,21 +5215,21 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>115ECON72S1</t>
+          <t>115-C062</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>論壇</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
@@ -5245,30 +5245,30 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>花蓮縣政府</t>
+          <t>衛生福利部疾病管制署</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026花蓮星潮原聲系列活動規劃執行案</t>
+          <t>「115年度防疫績優獎頒獎典禮專業服務」採購案</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>40000000</v>
+        <v>950000</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>AB1150007224</t>
+          <t>LA115028</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5288,11 +5288,11 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>系列活動、活動規劃</t>
+          <t>頒獎典禮</t>
         </is>
       </c>
       <c r="K77" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
@@ -5308,25 +5308,25 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>南投縣政府</t>
+          <t>花蓮縣政府</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>「2026南投花卉嘉年華－草屯展區系列活動」勞務採購案</t>
+          <t>115年花蓮縣精品咖啡行銷推廣計畫</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>1000000</v>
+        <v>1100000</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5341,21 +5341,21 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>1150602018G</t>
+          <t>AG1150018061</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>嘉年華、系列活動</t>
+          <t>行銷推廣</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
@@ -5371,30 +5371,30 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>內政部</t>
+          <t>社團法人花蓮縣基督教會花蓮靈糧堂宣教協會</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>116年第84屆兵役節慶祝大會暨頒獎典禮委外服務案</t>
+          <t>2026花蓮幸福聖誕城行銷宣傳及城市聯合宣傳規劃案</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>1230000</v>
+        <v>6789600</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5404,21 +5404,21 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>115YJ-ST15</t>
+          <t>2026-2HLLC</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>國際會議論壇/活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>大會、頒獎典禮</t>
+          <t>行銷宣傳</t>
         </is>
       </c>
       <c r="K79" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
@@ -5434,30 +5434,30 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>國立臺灣美術館</t>
+          <t>社團法人花蓮縣基督教會花蓮靈糧堂宣教協會</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">國家珍藏作品之線上藝廊推廣影片製作採購案 </t>
+          <t>2026花蓮幸福聖誕城活動執行案</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>600000</v>
+        <v>9950000</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5467,21 +5467,21 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>115118</t>
+          <t>2026-1HLLC</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>影片製作、推廣</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="K80" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
@@ -5497,30 +5497,30 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>苗栗縣苗栗市公所</t>
+          <t>桃園市平鎮區公所</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>苗栗市2026冬迎璀璨歲末藝文嘉年華</t>
+          <t>116年桃園市平鎮區元旦升旗典禮活動</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>2440000</v>
+        <v>450000</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>C548</t>
+          <t>1151005A01</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>嘉年華</t>
+          <t>活動、典禮</t>
         </is>
       </c>
       <c r="K81" t="n">
@@ -5560,21 +5560,21 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>苗栗縣苗栗市公所</t>
+          <t>彰化縣田中鎮公所</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>115年度苗栗市親子蘿蔔節活動執行委託專業服務採購案</t>
+          <t>2026田中藝術節–愛閱田中・藝起嗨劇場委託專業服務採購案</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>1000000</v>
+        <v>700000</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -5588,12 +5588,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>B1600</t>
+          <t>115-081</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>藝術節</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -5623,17 +5623,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>桃園市政府工務局</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>115年桃園市食農教育執行成果展委託專業服務案</t>
+          <t>116年屏東縣政府社會處網路媒體行銷維運案</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5656,17 +5656,17 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1151005-3</t>
+          <t>A058-1151007-2</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>成果展</t>
+          <t>媒體行銷</t>
         </is>
       </c>
       <c r="K83" t="n">
@@ -5686,25 +5686,25 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>新竹縣尖石鄉公所</t>
+          <t>南投縣政府</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>新竹縣尖石鄉115年尖石鄉鄉長盃第二屆傳統路跑嘉年華暨傳統擲矛、傳統狩獵活動勞務採購案</t>
+          <t>115年縣政成果及重大活動影音攝製行銷案</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>950000</v>
+        <v>1400000</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5719,17 +5719,17 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>1159226</t>
+          <t>115-07-06-011E</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>嘉年華</t>
+          <t>活動、行銷</t>
         </is>
       </c>
       <c r="K84" t="n">
@@ -5749,30 +5749,30 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>嘉義縣文化觀光局</t>
+          <t>苗栗縣政府</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>「116年度嘉義縣觀光旅遊數位整合行銷」委託專業服務案</t>
+          <t>「2027台灣燈會在苗栗」廣播錄製暨執行委託專業服務案</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>2000000</v>
+        <v>500000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5782,21 +5782,21 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1150011120</t>
+          <t>115141f</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>整合行銷</t>
+          <t>燈會</t>
         </is>
       </c>
       <c r="K85" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
@@ -5812,25 +5812,25 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>台灣中油股份有限公司探採事業部</t>
+          <t>臺南市政府經濟發展局</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>碳封存監測資料彙整分析及社會溝通顧問服務</t>
+          <t>「2027新化年貨大街」活動委託服務案</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>1490000</v>
+        <v>1100000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5840,26 +5840,26 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>BEA1500013</t>
+          <t>115ECON72S1</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>政策溝通</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>社會溝通</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K86" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
@@ -5880,25 +5880,25 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>中央選舉委員會</t>
+          <t>花蓮縣政府</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>115年地方公職人員選舉及公民投票選務滿意度民意調查採購案</t>
+          <t>2026花蓮星潮原聲系列活動規劃執行案</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>500000</v>
+        <v>40000000</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5908,21 +5908,21 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1150909</t>
+          <t>AB1150007224</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>政策溝通</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>民意調查</t>
+          <t>系列活動、活動規劃</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="L87" s="3" t="inlineStr">
         <is>
@@ -5943,12 +5943,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>桃園市政府捷運工程局</t>
+          <t>南投縣政府</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>桃園市八德區德和路一段第2階段通車活動委託服務案</t>
+          <t>「2026南投花卉嘉年華－草屯展區系列活動」勞務採購案</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1151006</t>
+          <t>1150602018G</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5981,11 +5981,11 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>嘉年華、系列活動</t>
         </is>
       </c>
       <c r="K88" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
@@ -6001,30 +6001,30 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>國防部</t>
+          <t>內政部</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>國軍招募宣傳電視廣告託播</t>
+          <t>116年第84屆兵役節慶祝大會暨頒獎典禮委外服務案</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>2000000</v>
+        <v>1230000</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>公開招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6034,21 +6034,21 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>CC15003L050</t>
+          <t>115YJ-ST15</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>國際會議論壇/活動執行</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>廣告託播、宣傳</t>
+          <t>大會、頒獎典禮</t>
         </is>
       </c>
       <c r="K89" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L89" s="3" t="inlineStr">
         <is>
@@ -6064,30 +6064,30 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>衛生福利部社會及家庭署</t>
+          <t>國立臺灣美術館</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>116年度強化社會安全網績優人員及團體獎項品牌識別系統專業服務案</t>
+          <t xml:space="preserve">國家珍藏作品之線上藝廊推廣影片製作採購案 </t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>2550000</v>
+        <v>600000</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>C116001</t>
+          <t>115118</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6107,11 +6107,11 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>品牌識別</t>
+          <t>影片製作、推廣</t>
         </is>
       </c>
       <c r="K90" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
@@ -6127,25 +6127,25 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>臺北市政府觀光傳播局</t>
+          <t>苗栗縣苗栗市公所</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>116年度臺北開齋節暨穆斯林友善城市推廣活動案</t>
+          <t>苗栗市2026冬迎璀璨歲末藝文嘉年華</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>4000000</v>
+        <v>2440000</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>1150075</t>
+          <t>C548</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>活動、推廣</t>
+          <t>嘉年華</t>
         </is>
       </c>
       <c r="K91" t="n">
@@ -6190,25 +6190,25 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>國立歷史博物館</t>
+          <t>苗栗縣苗栗市公所</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>常設展手語導覽影片製作案</t>
+          <t>115年度苗栗市親子蘿蔔節活動執行委託專業服務採購案</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>950000</v>
+        <v>1000000</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -6223,17 +6223,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>115046</t>
+          <t>B1600</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>影片製作</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -6253,25 +6253,25 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>內政部國土管理署</t>
+          <t>桃園市政府工務局</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>116年度住宅政策推廣影音及多媒體製作案</t>
+          <t>115年桃園市食農教育執行成果展委託專業服務案</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>9950000</v>
+        <v>2000000</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6286,17 +6286,17 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>115A-066</t>
+          <t>1151005-3</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>推廣、媒體</t>
+          <t>成果展</t>
         </is>
       </c>
       <c r="K93" t="n">
@@ -6316,30 +6316,30 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>高雄市政府勞工局訓練就業中心</t>
+          <t>新竹縣尖石鄉公所</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>「116年度鳳山、岡山就業服務站現場徵才活動」委託服務案</t>
+          <t>新竹縣尖石鄉115年尖石鄉鄉長盃第二屆傳統路跑嘉年華暨傳統擲矛、傳統狩獵活動勞務採購案</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>2892100</v>
+        <v>950000</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>116F002</t>
+          <t>1159226</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6359,11 +6359,11 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>嘉年華</t>
         </is>
       </c>
       <c r="K94" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
@@ -6379,54 +6379,54 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>新北市政府勞工局</t>
+          <t>嘉義縣文化觀光局</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>新北市政府116年度外國人文化與休閒活動計畫-越南、印尼活動委託專業服務採購案</t>
+          <t>「116年度嘉義縣觀光旅遊數位整合行銷」委託專業服務案</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>1300000</v>
+        <v>2000000</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>TPLAB115013</t>
+          <t>1150011120</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>整合行銷</t>
         </is>
       </c>
       <c r="K95" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L95" s="3" t="inlineStr">
         <is>
@@ -6442,25 +6442,25 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>臺中市石岡區公所</t>
+          <t>台灣中油股份有限公司探採事業部</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>115年石岡童樂會暨水資源宣導活動</t>
+          <t>碳封存監測資料彙整分析及社會溝通顧問服務</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>800000</v>
+        <v>1490000</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -6470,26 +6470,26 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>115SK20</t>
+          <t>BEA1500013</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>政策溝通</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>社會溝通</t>
         </is>
       </c>
       <c r="K96" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
@@ -6505,25 +6505,25 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>臺中市石岡區公所</t>
+          <t>中央選舉委員會</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026臺中市民野餐日（石岡區）暨觀光活化水資源宣導活動</t>
+          <t>115年地方公職人員選舉及公民投票選務滿意度民意調查採購案</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>920000</v>
+        <v>500000</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -6538,21 +6538,21 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>115SK19</t>
+          <t>1150909</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>政策溝通</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>民意調查</t>
         </is>
       </c>
       <c r="K97" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L97" s="3" t="inlineStr">
         <is>
@@ -6568,30 +6568,30 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>新竹縣芎林鄉公所</t>
+          <t>桃園市政府捷運工程局</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2027芎林路跑嘉年華活動計畫委託專業服務案</t>
+          <t>桃園市八德區德和路一段第2階段通車活動委託服務案</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>2400000</v>
+        <v>1000000</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1160001P</t>
+          <t>1151006</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6611,11 +6611,11 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>嘉年華、活動</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K98" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L98" s="3" t="inlineStr">
         <is>
@@ -6631,30 +6631,30 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>海洋委員會</t>
+          <t>國防部</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>海洋博覽會整體規劃暨先期策略研析委託專業服務案</t>
+          <t>國軍招募宣傳電視廣告託播</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開招標公告</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -6664,21 +6664,21 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>OAC115044</t>
+          <t>CC15003L050</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>博覽會</t>
+          <t>廣告託播、宣傳</t>
         </is>
       </c>
       <c r="K99" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L99" s="3" t="inlineStr">
         <is>
@@ -6694,25 +6694,25 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>花蓮縣政府</t>
+          <t>衛生福利部社會及家庭署</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>115年花蓮宜居城市行銷採購案(開口契約)</t>
+          <t>116年度強化社會安全網績優人員及團體獎項品牌識別系統專業服務案</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>9450000</v>
+        <v>2550000</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>SK1150005862</t>
+          <t>C116001</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>城市行銷</t>
+          <t>品牌識別</t>
         </is>
       </c>
       <c r="K100" t="n">
@@ -6757,30 +6757,30 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>花蓮縣政府</t>
+          <t>臺北市政府觀光傳播局</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>115年花蓮縣社區照顧關懷據點及社區長照站成果展</t>
+          <t>116年度臺北開齋節暨穆斯林友善城市推廣活動案</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>1250000</v>
+        <v>4000000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6790,17 +6790,17 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>SC1150020073</t>
+          <t>1150075</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>成果展</t>
+          <t>活動、推廣</t>
         </is>
       </c>
       <c r="K101" t="n">
@@ -6820,25 +6820,25 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>桃園市政府文化局</t>
+          <t>國立歷史博物館</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026桃園仙草花節系列活動-民歌演唱會委託專業服務案</t>
+          <t>常設展手語導覽影片製作案</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>500000</v>
+        <v>950000</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6853,17 +6853,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>TYC115-39</t>
+          <t>115046</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>系列活動</t>
+          <t>影片製作</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -6883,25 +6883,25 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>宜蘭縣政府</t>
+          <t>內政部國土管理署</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>宜蘭縣115年度原有住宅無障礙設施補助委託辦理推廣宣導評估案</t>
+          <t>116年度住宅政策推廣影音及多媒體製作案</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>1210000</v>
+        <v>9950000</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>CNSL115032</t>
+          <t>115A-066</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>宣導、推廣</t>
+          <t>推廣、媒體</t>
         </is>
       </c>
       <c r="K103" t="n">
@@ -6946,21 +6946,21 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>財團法人嘉義市文化基金會</t>
+          <t>高雄市政府勞工局訓練就業中心</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026嘉義市管樂節晚會舞台暨表演節目規畫執行委託服務案</t>
+          <t>「116年度鳳山、岡山就業服務站現場徵才活動」委託服務案</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>15000000</v>
+        <v>2892100</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>115A001</t>
+          <t>116F002</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6989,7 +6989,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>晚會</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K104" t="n">
@@ -7009,40 +7009,40 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>新竹市政府</t>
+          <t>新北市政府勞工局</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>「2026客家藝文活動」委託專業服務案</t>
+          <t>新北市政府116年度外國人文化與休閒活動計畫-越南、印尼活動委託專業服務採購案</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>2400000</v>
+        <v>1300000</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>1150292</t>
+          <t>TPLAB115013</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7072,30 +7072,30 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>新北市政府觀光旅遊局</t>
+          <t>臺中市石岡區公所</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>116年度跨媒體整合傳播採購案</t>
+          <t>115年石岡童樂會暨水資源宣導活動</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>7350000</v>
+        <v>800000</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7105,21 +7105,21 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>1151911877</t>
+          <t>115SK20</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>整合傳播、跨媒體</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K106" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L106" s="3" t="inlineStr">
         <is>
@@ -7135,30 +7135,30 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>司法院</t>
+          <t>臺中市石岡區公所</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>司法院115年司法博物館主題活動規劃執行採購案</t>
+          <t>2026臺中市民野餐日（石岡區）暨觀光活化水資源宣導活動</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>3400000</v>
+        <v>920000</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -7168,21 +7168,21 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>1151400844</t>
+          <t>115SK19</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>活動規劃、主題活動</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K107" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L107" s="3" t="inlineStr">
         <is>
@@ -7198,50 +7198,50 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>彰化縣伸港鄉公所</t>
+          <t>新竹縣芎林鄉公所</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2027年伸港飛揚-元旦升旗健行齊步走暨節能減碳宣導活動委託服務案</t>
+          <t>2027芎林路跑嘉年華活動計畫委託專業服務案</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>1152300</v>
+        <v>2400000</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>1152006</t>
+          <t>1160001P</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>嘉年華、活動</t>
         </is>
       </c>
       <c r="K108" t="n">
@@ -7261,30 +7261,30 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>臺東縣政府</t>
+          <t>海洋委員會</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>興隆國小--臺東縣115年度環境變遷與藍碳發展論壇暨體驗學習活動</t>
+          <t>海洋博覽會整體規劃暨先期策略研析委託專業服務案</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>420000</v>
+        <v>3000000</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>115310130545</t>
+          <t>OAC115044</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>論壇</t>
+          <t>博覽會</t>
         </is>
       </c>
       <c r="K109" t="n">
@@ -7324,21 +7324,21 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>桃園市政府文化局</t>
+          <t>花蓮縣政府</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026桃園社造博覽會規劃執行案</t>
+          <t>115年花蓮宜居城市行銷採購案(開口契約)</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>2000000</v>
+        <v>9450000</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -7357,21 +7357,21 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>1150276</t>
+          <t>SK1150005862</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>博覽會</t>
+          <t>城市行銷</t>
         </is>
       </c>
       <c r="K110" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L110" s="3" t="inlineStr">
         <is>
@@ -7387,25 +7387,25 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>新北市政府水利局</t>
+          <t>花蓮縣政府</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>新北市治水、清水、親水水環境治理成果影片製作案</t>
+          <t>115年花蓮縣社區照顧關懷據點及社區長照站成果展</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>1200000</v>
+        <v>1250000</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -7420,17 +7420,17 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>1150930A</t>
+          <t>SC1150020073</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>影片製作</t>
+          <t>成果展</t>
         </is>
       </c>
       <c r="K111" t="n">
@@ -7450,25 +7450,25 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>彰化縣田中鎮公所</t>
+          <t>桃園市政府文化局</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026田中藝術節–愛閱田中・藝起嗨劇場委託專業服務採購案</t>
+          <t>2026桃園仙草花節系列活動-民歌演唱會委託專業服務案</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>700000</v>
+        <v>500000</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>115-081</t>
+          <t>TYC115-39</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>藝術節</t>
+          <t>系列活動</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -7513,30 +7513,30 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>外交部領事事務局</t>
+          <t>宜蘭縣政府</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>115年度推廣外交部領事事務局「LINE官方帳號」靜態貼圖廣告方案</t>
+          <t>宜蘭縣115年度原有住宅無障礙設施補助委託辦理推廣宣導評估案</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>630000</v>
+        <v>1210000</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>T115027CB</t>
+          <t>CNSL115032</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>廣告、推廣</t>
+          <t>宣導、推廣</t>
         </is>
       </c>
       <c r="K113" t="n">
@@ -7576,68 +7576,698 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>財團法人嘉義市文化基金會</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026嘉義市管樂節晚會舞台暨表演節目規畫執行委託服務案</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>115A001</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>活動執行</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>晚會</t>
+        </is>
+      </c>
+      <c r="K114" t="n">
+        <v>4</v>
+      </c>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>新竹市政府</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>「2026客家藝文活動」委託專業服務案</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>1150292</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>活動執行</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>活動</t>
+        </is>
+      </c>
+      <c r="K115" t="n">
+        <v>4</v>
+      </c>
+      <c r="L115" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>新北市政府觀光旅遊局</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>116年度跨媒體整合傳播採購案</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>7350000</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>1151911877</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>宣導行銷</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>整合傳播、跨媒體</t>
+        </is>
+      </c>
+      <c r="K116" t="n">
+        <v>16</v>
+      </c>
+      <c r="L116" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>司法院</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>司法院115年司法博物館主題活動規劃執行採購案</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>1151400844</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>活動執行</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>活動規劃、主題活動</t>
+        </is>
+      </c>
+      <c r="K117" t="n">
+        <v>16</v>
+      </c>
+      <c r="L117" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>彰化縣伸港鄉公所</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2027年伸港飛揚-元旦升旗健行齊步走暨節能減碳宣導活動委託服務案</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>1152300</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>公開取得報價單或企劃書公告</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>1152006</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>活動執行/宣導行銷</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>活動、宣導活動</t>
+        </is>
+      </c>
+      <c r="K118" t="n">
+        <v>12</v>
+      </c>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>臺東縣政府</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>興隆國小--臺東縣115年度環境變遷與藍碳發展論壇暨體驗學習活動</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>420000</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>公開取得報價單或企劃書公告</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>115310130545</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>國際會議論壇</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>論壇</t>
+        </is>
+      </c>
+      <c r="K119" t="n">
+        <v>10</v>
+      </c>
+      <c r="L119" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>桃園市政府文化局</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2026桃園社造博覽會規劃執行案</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>1150276</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>國際會議論壇</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>博覽會</t>
+        </is>
+      </c>
+      <c r="K120" t="n">
+        <v>10</v>
+      </c>
+      <c r="L120" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>新北市政府水利局</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>新北市治水、清水、親水水環境治理成果影片製作案</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>公開取得報價單或企劃書公告</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>1150930A</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>宣導行銷</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>影片製作</t>
+        </is>
+      </c>
+      <c r="K121" t="n">
+        <v>8</v>
+      </c>
+      <c r="L121" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>彰化縣田中鎮公所</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2026田中藝術節–愛閱田中・藝起嗨劇場委託專業服務採購案</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>700000</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>公開取得報價單或企劃書公告</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>115-081</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>活動執行</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>藝術節</t>
+        </is>
+      </c>
+      <c r="K122" t="n">
+        <v>8</v>
+      </c>
+      <c r="L122" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>外交部領事事務局</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>115年度推廣外交部領事事務局「LINE官方帳號」靜態貼圖廣告方案</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>630000</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>公開取得報價單或企劃書公告</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>T115027CB</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>宣導行銷</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>廣告、推廣</t>
+        </is>
+      </c>
+      <c r="K123" t="n">
+        <v>8</v>
+      </c>
+      <c r="L123" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
         <is>
           <t>勞動部勞動力發展署桃竹苗分署</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>116年機關整合行銷勞務採購案</t>
         </is>
       </c>
-      <c r="D114" s="2" t="n">
+      <c r="D124" s="2" t="n">
         <v>1330000</v>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="E124" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="F124" t="inlineStr">
         <is>
           <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
         <is>
           <t>116Y020</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
+      <c r="I124" t="inlineStr">
         <is>
           <t>宣導行銷</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr">
+      <c r="J124" t="inlineStr">
         <is>
           <t>整合行銷</t>
         </is>
       </c>
-      <c r="K114" t="n">
+      <c r="K124" t="n">
         <v>8</v>
       </c>
-      <c r="L114" s="3" t="inlineStr">
-        <is>
-          <t>開啟</t>
-        </is>
-      </c>
-      <c r="M114" t="inlineStr">
+      <c r="L124" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
         <is>
           <t>2026-10-15 08:34</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M114"/>
+  <autoFilter ref="A1:M124"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -7752,6 +8382,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L112" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L113" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L124" r:id="rId123"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7801,13 +8441,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4550</v>
+        <v>4968</v>
       </c>
       <c r="C2" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>306863861</v>
+        <v>329878970</v>
       </c>
     </row>
   </sheetData>
@@ -7837,7 +8477,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>產生時間：2026-10-19 08:10　資料庫共 113 筆</t>
+          <t>產生時間：2026-10-20 09:04　資料庫共 123 筆</t>
         </is>
       </c>
     </row>

--- a/data/標案資料庫.xlsx
+++ b/data/標案資料庫.xlsx
@@ -12,7 +12,7 @@
     <sheet name="說明" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'標案資料庫'!$A$1:$M$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'標案資料庫'!$A$1:$M$135</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M124"/>
+  <dimension ref="A1:M135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -524,50 +524,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>衛生福利部</t>
+          <t>宜蘭縣政府</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>116年度「社會工作專業人員表揚典禮暨宣導活動」</t>
+          <t>「宜蘭縣115年國際移民嘉年華」活動規劃執行委託案</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2600000</v>
+        <v>400000</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>M1604017</t>
+          <t>CVSL115019</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>活動、典禮、宣導活動</t>
+          <t>嘉年華、活動規劃</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,37 +580,37 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-20 09:04</t>
+          <t>2026-10-21 08:35</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>高雄市政府新聞局</t>
+          <t>桃園市政府工務局</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>施政成果暨大型活動平面整合行銷案</t>
+          <t>桃園市116年績優社工人員表揚典禮暨社工日系列活動</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1100000</v>
+        <v>4000000</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -620,17 +620,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1151015B</t>
+          <t>1151019-2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>活動、整合行銷</t>
+          <t>系列活動、典禮</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -643,28 +643,28 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-20 09:04</t>
+          <t>2026-10-21 08:35</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>高雄市政府工務局公園處</t>
+          <t>台灣中油股份有限公司天然氣事業部觀塘液化天然氣廠</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115-116年度工務建設宣導活動案(開口契約)</t>
+          <t>觀塘廠多媒體影片製作</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2445109</v>
+        <v>935101</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -683,17 +683,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>11504SB012</t>
+          <t>LEA1540001</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>影片製作、媒體</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -706,61 +706,61 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-20 09:04</t>
+          <t>2026-10-21 08:35</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>苗栗縣政府衛生局</t>
+          <t>勞動部勞動力發展署桃竹苗分署</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>115年預防保健業務之戶外廣告行銷推廣</t>
+          <t>「2027桃竹苗OpenHouse就業博覽會官方網站」勞務採購案</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>580000</v>
+        <v>3324999</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>11532</t>
+          <t>116Y045</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>行銷推廣、廣告</t>
+          <t>博覽會</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -769,37 +769,37 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-20 09:04</t>
+          <t>2026-10-21 08:35</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>臺北市立美術館</t>
+          <t>農業部</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>「當代藝術與技術論壇」錄影案</t>
+          <t>116年度整體農業政策整合行銷案</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>220000</v>
+        <v>25000000</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>公開招標公告</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -809,21 +809,21 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>115RE0118</t>
+          <t>11559T</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>論壇</t>
+          <t>整合行銷</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -832,37 +832,37 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-20 09:04</t>
+          <t>2026-10-21 08:35</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>桃園市政府客家事務局</t>
+          <t>新竹市政府</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>桃園市政府客家事務局115-116年桃園市客家文化館展覽活動等營運管理勞務採購案</t>
+          <t>115年新竹市志願服務表揚暨社區成果展委託專業服務案</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>5100000</v>
+        <v>1312500</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>115-022</t>
+          <t>1150307</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>活動、展覽</t>
+          <t>成果展</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -895,47 +895,47 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-20 09:04</t>
+          <t>2026-10-21 08:35</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>南投縣政府</t>
+          <t>宜蘭縣政府</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>115年度幸福南投短影音行銷宣傳採購案</t>
+          <t>宜蘭縣115年度原有住宅無障礙設施補助委託辦理推廣宣導評估案</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1400000</v>
+        <v>1210000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>115-07-07-006G</t>
+          <t>CNSL115032</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>行銷宣傳</t>
+          <t>宣導、推廣</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -958,32 +958,32 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-20 09:04</t>
+          <t>2026-10-21 08:35</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>農業部林業及自然保育署花蓮分署</t>
+          <t>南投縣草屯鎮公所</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>林田山遊客中心佈展(含活動駐館)委託專業服務</t>
+          <t>2026草屯聖誕煙火嘉年華委託專業服務勞務採購案</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>5900000</v>
+        <v>7000000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>115m011</t>
+          <t>115FR122501</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1008,11 +1008,11 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>嘉年華</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -1021,37 +1021,37 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-20 09:04</t>
+          <t>2026-10-21 08:35</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>臺中市神岡區公所</t>
+          <t>核能安全委員會</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>【2026臺中市民野餐日(神岡區)雙場地活動】委託專業服務採購案</t>
+          <t>116及117年度新聞媒體監測資料檢索系統勞務採購案</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1920000</v>
+        <v>964800</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1061,21 +1061,21 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>115-LS37</t>
+          <t>NSC11510044L</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>政策溝通</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>媒體監測</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -1084,32 +1084,32 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-20 09:04</t>
+          <t>2026-10-21 08:35</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>臺中市政府客家事務委員會</t>
+          <t>苗栗縣政府</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2027臺中東勢新丁粄節-文宣暨會場佈置委託專業服務勞務採購案</t>
+          <t>「2027台灣燈會在苗栗－整體展演策劃、製作及執行」委託專業服務案</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1750000</v>
+        <v>55500000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1124,17 +1124,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1151102</t>
+          <t>115229</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>文宣</t>
+          <t>燈會</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1147,37 +1147,37 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-20 09:04</t>
+          <t>2026-10-21 08:35</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>國家人權博物館</t>
+          <t>屏東縣長治鄉公所</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>「解嚴40週年國際論壇暨紀念專書籌劃」委託專業服務案</t>
+          <t>2027年繁華義勇恩公文化祭暨祭祀慶典活動委託專業服務案</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>2200000</v>
+        <v>800000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1187,21 +1187,21 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>11590Z</t>
+          <t>1151015</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>國際論壇、論壇</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
@@ -1210,57 +1210,57 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-21 08:35</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>南投縣政府</t>
+          <t>衛生福利部</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>「2026南投花卉嘉年華－草屯展區系列活動」勞務採購案</t>
+          <t>116年度「社會工作專業人員表揚典禮暨宣導活動」</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1000000</v>
+        <v>2600000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1150602018G</t>
+          <t>M1604017</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>嘉年華、系列活動</t>
+          <t>活動、典禮、宣導活動</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1273,30 +1273,32 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>臺南市政府農業局</t>
+          <t>高雄市政府新聞局</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>日本地區臺南市農漁產推廣暨行銷活動策畫與執行委託專業服務案</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr"/>
+          <t>施政成果暨大型活動平面整合行銷案</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>1100000</v>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1311,7 +1313,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>115AGR080</t>
+          <t>1151015B</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1321,7 +1323,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>活動、行銷、推廣</t>
+          <t>活動、整合行銷</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1334,37 +1336,37 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>桃園市政府環境管理處</t>
+          <t>高雄市政府工務局公園處</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>115年度職業安全衛生業務標竿學習宣導活動計畫</t>
+          <t>115-116年度工務建設宣導活動案(開口契約)</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1300000</v>
+        <v>2445109</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1374,7 +1376,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1150036916</t>
+          <t>11504SB012</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1397,57 +1399,57 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>南投縣政府社會及勞動局</t>
+          <t>苗栗縣政府衛生局</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>南投縣115年度國際身心障礙者日宣導活動</t>
+          <t>115年預防保健業務之戶外廣告行銷推廣</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>2500000</v>
+        <v>580000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>115-10-10-005-E</t>
+          <t>11532</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>行銷推廣、廣告</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1460,37 +1462,37 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>財團法人蘭陽農業發展基金會</t>
+          <t>臺北市立美術館</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2027宜蘭綠色博覽會－海洋館委託專業服務案</t>
+          <t>「當代藝術與技術論壇」錄影案</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>7000000</v>
+        <v>220000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1500,7 +1502,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>115101305</t>
+          <t>115RE0118</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1510,7 +1512,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>博覽會</t>
+          <t>論壇</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1523,32 +1525,32 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>財團法人蘭陽農業發展基金會</t>
+          <t>桃園市政府客家事務局</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2027宜蘭綠色博覽會－森林館委託專業服務案</t>
+          <t>桃園市政府客家事務局115-116年桃園市客家文化館展覽活動等營運管理勞務採購案</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>3950000</v>
+        <v>5100000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1563,21 +1565,21 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>115101301</t>
+          <t>115-022</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>博覽會</t>
+          <t>活動、展覽</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
@@ -1586,28 +1588,28 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>雲林縣政府</t>
+          <t>南投縣政府</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>「2026雲林文創聯合徵選暨雲林設計獎」頒獎典禮委託規劃執行案</t>
+          <t>115年度幸福南投短影音行銷宣傳採購案</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>500000</v>
+        <v>1400000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1621,22 +1623,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1152H10116</t>
+          <t>115-07-07-006G</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>頒獎典禮</t>
+          <t>行銷宣傳</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1649,37 +1651,37 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>臺北市教師研習中心</t>
+          <t>農業部林業及自然保育署花蓮分署</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>116年度優質學校頒獎典禮、杏壇芬芳獎表揚典禮、臺北教育111標竿學校頒獎典禮採購案</t>
+          <t>林田山遊客中心佈展(含活動駐館)委託專業服務</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>869500</v>
+        <v>5900000</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1689,7 +1691,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>11605</t>
+          <t>115m011</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1699,11 +1701,11 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>頒獎典禮</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
@@ -1712,37 +1714,37 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>臺中市政府數位發展局</t>
+          <t>臺中市神岡區公所</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>台中通特店消費推廣暨抽獎活動案</t>
+          <t>【2026臺中市民野餐日(神岡區)雙場地活動】委託專業服務採購案</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>950000</v>
+        <v>1920000</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1752,21 +1754,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>115B-10</t>
+          <t>115-LS37</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>活動、推廣</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
@@ -1775,32 +1777,32 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>桃園市政府客家事務局</t>
+          <t>臺中市政府客家事務委員會</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>「桃園市客家文化館開館系列活動」勞務採購案</t>
+          <t>2027臺中東勢新丁粄節-文宣暨會場佈置委託專業服務勞務採購案</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>5500000</v>
+        <v>1750000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1815,21 +1817,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>115-021</t>
+          <t>1151102</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>系列活動</t>
+          <t>文宣</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
@@ -1838,7 +1840,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
@@ -1850,20 +1852,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>嘉義市政府</t>
+          <t>國家人權博物館</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>嘉義市政府116年家庭暴力暨性侵害防治中心宣導行銷計畫</t>
+          <t>「解嚴40週年國際論壇暨紀念專書籌劃」委託專業服務案</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>1800000</v>
+        <v>2200000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1878,21 +1880,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>115266</t>
+          <t>11590Z</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>宣導、行銷</t>
+          <t>國際論壇、論壇</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
@@ -1913,20 +1915,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>國家科學及技術委員會南部科學園區管理局</t>
+          <t>南投縣政府</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>國家科學及技術委員會116年度科學園區滿意度調查計畫</t>
+          <t>「2026南投花卉嘉年華－草屯展區系列活動」勞務採購案</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>1236708</v>
+        <v>1000000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1936,26 +1938,26 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>115660D01151</t>
+          <t>1150602018G</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>政策溝通</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>滿意度調查</t>
+          <t>嘉年華、系列活動</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
@@ -1976,25 +1978,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>農業部林業及自然保育署阿里山林業鐵路及文化資產管理處</t>
+          <t>臺南市政府農業局</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>116-117年「阿里山林鐵行動學校」跨館際展覽委託專業服務案</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>2800000</v>
-      </c>
+          <t>日本地區臺南市農漁產推廣暨行銷活動策畫與執行委託專業服務案</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2004,21 +2004,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>116-EDU-001</t>
+          <t>115AGR080</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>展覽</t>
+          <t>活動、行銷、推廣</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
@@ -2039,20 +2039,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>新北市政府觀光旅遊局</t>
+          <t>桃園市政府環境管理處</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>115年新北市平日住宿及生日券獎助活動專案管理委託專業服務案</t>
+          <t>115年度職業安全衛生業務標竿學習宣導活動計畫</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>700000</v>
+        <v>1300000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2067,21 +2067,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1152038719</t>
+          <t>1150036916</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
@@ -2102,25 +2102,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>中華郵政股份有限公司</t>
+          <t>南投縣政府社會及勞動局</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>「羊來了-生肖郵票特展」策、布展及開幕活動委託服務</t>
+          <t>南投縣115年度國際身心障礙者日宣導活動</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1480000</v>
+        <v>2500000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2130,21 +2130,21 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>115-3-167</t>
+          <t>115-10-10-005-E</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
@@ -2160,25 +2160,25 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>桃園市政府藝文設施管理中心</t>
+          <t>財團法人蘭陽農業發展基金會</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>「2027桃園鐵玫瑰藝術節活動執行統籌及行銷」委託專業服務採購案</t>
+          <t>2027宜蘭綠色博覽會－海洋館委託專業服務案</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>9000000</v>
+        <v>7000000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2188,26 +2188,26 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>115AFMC-017</t>
+          <t>115101305</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>活動執行、藝術節、行銷</t>
+          <t>博覽會</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
@@ -2216,61 +2216,61 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>屏東縣獅子鄉公所</t>
+          <t>財團法人蘭陽農業發展基金會</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>屏東縣獅子鄉115年度慶祝重陽節聯合表揚暨族語文化推廣與文化健康站成果展活動勞務採購案</t>
+          <t>2027宜蘭綠色博覽會－森林館委託專業服務案</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>1162700</v>
+        <v>3950000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1151001AA</t>
+          <t>115101301</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>成果展、活動、推廣</t>
+          <t>博覽會</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
@@ -2279,61 +2279,61 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>勞動部勞動力發展署雲嘉南分署</t>
+          <t>雲林縣政府</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>116年度社群平台整合行銷委託計畫</t>
+          <t>「2026雲林文創聯合徵選暨雲林設計獎」頒獎典禮委託規劃執行案</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>2000000</v>
+        <v>500000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>yctrb1150129</t>
+          <t>1152H10116</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>整合行銷、社群平台</t>
+          <t>頒獎典禮</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
@@ -2342,32 +2342,32 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>內政部</t>
+          <t>臺北市教師研習中心</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>116年第84屆兵役節慶祝大會暨頒獎典禮委外服務案</t>
+          <t>116年度優質學校頒獎典禮、杏壇芬芳獎表揚典禮、臺北教育111標竿學校頒獎典禮採購案</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1230000</v>
+        <v>869500</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2377,26 +2377,26 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>115YJ-ST15</t>
+          <t>11605</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>國際會議論壇/活動執行</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>大會、頒獎典禮</t>
+          <t>頒獎典禮</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
@@ -2405,37 +2405,37 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>桃園市八德區公所</t>
+          <t>臺中市政府數位發展局</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>116年度桃園市元旦升旗典禮活動規劃與執行</t>
+          <t>台中通特店消費推廣暨抽獎活動案</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1600000</v>
+        <v>950000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2445,21 +2445,21 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>BB1151015</t>
+          <t>115B-10</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>活動規劃、典禮</t>
+          <t>活動、推廣</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
@@ -2468,37 +2468,37 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>國立臺中教育大學</t>
+          <t>桃園市政府客家事務局</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>數位內容充實與推廣總計畫成果紀錄影片製作採購案</t>
+          <t>「桃園市客家文化館開館系列活動」勞務採購案</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>465000</v>
+        <v>5500000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2508,21 +2508,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>115-C063</t>
+          <t>115-021</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>影片製作、推廣</t>
+          <t>系列活動</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
@@ -2531,32 +2531,32 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>文化部</t>
+          <t>嘉義市政府</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>文化部「蒙藏文化情境展示及體驗活動」展場設計製作布卸展及活動執行藝文採購案</t>
+          <t>嘉義市政府116年家庭暴力暨性侵害防治中心宣導行銷計畫</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>3350000</v>
+        <v>1800000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2571,17 +2571,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>11510159</t>
+          <t>115266</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導、行銷</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2594,32 +2594,32 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>國立雲林科技大學</t>
+          <t>國家科學及技術委員會南部科學園區管理局</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026研發成果展場地佈置案</t>
+          <t>國家科學及技術委員會116年度科學園區滿意度調查計畫</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>840000</v>
+        <v>1236708</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2634,21 +2634,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>HTL115040</t>
+          <t>115660D01151</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>政策溝通</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>成果展</t>
+          <t>滿意度調查</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
@@ -2657,37 +2657,37 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>桃園市政府觀光旅遊局</t>
+          <t>農業部林業及自然保育署阿里山林業鐵路及文化資產管理處</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>116年桃園觀光旅遊局輿情蒐集及通報服務勞務採購案</t>
+          <t>116-117年「阿里山林鐵行動學校」跨館際展覽委託專業服務案</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>247008</v>
+        <v>2800000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2697,21 +2697,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1151015-AA1</t>
+          <t>116-EDU-001</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>政策溝通</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>輿情</t>
+          <t>展覽</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
@@ -2720,32 +2720,32 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>臺中市立圖書館</t>
+          <t>新北市政府觀光旅遊局</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026臺中市立圖書館羅布森圖書館展覽委託專業服務採購案</t>
+          <t>115年新北市平日住宿及生日券獎助活動專案管理委託專業服務案</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>1120000</v>
+        <v>700000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>115058</t>
+          <t>1152038719</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>展覽</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>中華郵政股份有限公司</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>115年客家記憶共創計畫-客家文化中心古契約展覽策劃執行</t>
+          <t>「羊來了-生肖郵票特展」策、布展及開幕活動委託服務</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>850000</v>
+        <v>1480000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>A132-1151015-1</t>
+          <t>115-3-167</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>展覽</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2846,61 +2846,61 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>廣亞學校財團法人育達科技大學</t>
+          <t>桃園市政府藝文設施管理中心</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>研究發展處創新創業輔導暨育成中心115年青年創業工作坊專案管理計畫青年遴選活動頒獎典禮暨成果展評選採購</t>
+          <t>「2027桃園鐵玫瑰藝術節活動執行統籌及行銷」委託專業服務採購案</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>350000</v>
+        <v>9000000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>115J-04</t>
+          <t>115AFMC-017</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>頒獎典禮、成果展、活動、工作坊</t>
+          <t>活動執行、藝術節、行銷</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
@@ -2909,32 +2909,32 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>苗栗縣政府衛生局</t>
+          <t>屏東縣獅子鄉公所</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>115年衛生教育之媒體廣告行銷推廣</t>
+          <t>屏東縣獅子鄉115年度慶祝重陽節聯合表揚暨族語文化推廣與文化健康站成果展活動勞務採購案</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>770000</v>
+        <v>1162700</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2944,22 +2944,22 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>11535</t>
+          <t>1151001AA</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>行銷推廣、廣告、媒體</t>
+          <t>成果展、活動、推廣</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2972,32 +2972,32 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>新竹市政府</t>
+          <t>勞動部勞動力發展署雲嘉南分署</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>116年新竹市政府城市行銷處社群網站管理</t>
+          <t>116年度社群平台整合行銷委託計畫</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1900000</v>
+        <v>2000000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1150300</t>
+          <t>yctrb1150129</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>城市行銷、社群網站</t>
+          <t>整合行銷、社群平台</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -3035,32 +3035,32 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>高雄市政府地政局</t>
+          <t>內政部</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>115年度不動產防詐暨交易安全宣導活動委外服務案</t>
+          <t>116年第84屆兵役節慶祝大會暨頒獎典禮委外服務案</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>400000</v>
+        <v>1230000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3070,26 +3070,26 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>115019</t>
+          <t>115YJ-ST15</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>國際會議論壇/活動執行</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>大會、頒獎典禮</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
@@ -3098,32 +3098,32 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>桃園市政府環境保護局</t>
+          <t>桃園市八德區公所</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>116年社群網路環境教育推廣維運計畫</t>
+          <t>116年度桃園市元旦升旗典禮活動規劃與執行</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>3800000</v>
+        <v>1600000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3138,21 +3138,21 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1150085608</t>
+          <t>BB1151015</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>推廣、社群</t>
+          <t>活動規劃、典禮</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
@@ -3161,32 +3161,32 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>嘉義縣表演藝術中心</t>
+          <t>國立臺中教育大學</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>嘉義縣表演藝術中心115年表演節目整合傳播委託專業服務案</t>
+          <t>數位內容充實與推廣總計畫成果紀錄影片製作採購案</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>800000</v>
+        <v>465000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1150002654</t>
+          <t>115-C063</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3211,11 +3211,11 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>整合傳播</t>
+          <t>影片製作、推廣</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
@@ -3224,37 +3224,37 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>南投縣水里鄉公所</t>
+          <t>文化部</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>「2026水里觀光行銷暨農特產品推廣系列活動—煙火設計及施放勞務採購案」</t>
+          <t>文化部「蒙藏文化情境展示及體驗活動」展場設計製作布卸展及活動執行藝文採購案</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>1000000</v>
+        <v>3350000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3264,21 +3264,21 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>115SHTS07</t>
+          <t>11510159</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>系列活動、觀光行銷、推廣</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
@@ -3287,32 +3287,32 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>國立臺灣大學</t>
+          <t>國立雲林科技大學</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2027年臺大杜鵑花節學系博覽會場佈</t>
+          <t>2026研發成果展場地佈置案</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>1250000</v>
+        <v>840000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3327,21 +3327,21 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1150963</t>
+          <t>HTL115040</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>博覽會</t>
+          <t>成果展</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
@@ -3350,32 +3350,32 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>高雄市政府運動發展局</t>
+          <t>桃園市政府觀光旅遊局</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>企業22年甲級排球聯賽高雄台電女子排球隊主場賽事行銷活動案</t>
+          <t>116年桃園觀光旅遊局輿情蒐集及通報服務勞務採購案</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>590000</v>
+        <v>247008</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3390,21 +3390,21 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>115-B-76</t>
+          <t>1151015-AA1</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>政策溝通</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>活動、行銷</t>
+          <t>輿情</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
@@ -3413,37 +3413,37 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>臺中市立圖書館</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>115年度管路灌溉成果推廣活動</t>
+          <t>2026臺中市立圖書館羅布森圖書館展覽委託專業服務採購案</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>4000000</v>
+        <v>1120000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3453,21 +3453,21 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>TY115B030</t>
+          <t>115058</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>活動、推廣</t>
+          <t>展覽</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
@@ -3476,47 +3476,47 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>臺北市政府工務局</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>116年全國大專院校運動會開閉幕典禮活動</t>
+          <t>115年客家記憶共創計畫-客家文化中心古契約展覽策劃執行</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>10000000</v>
+        <v>850000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1150826S0096</t>
+          <t>A132-1151015-1</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3526,11 +3526,11 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>活動、典禮</t>
+          <t>展覽</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
@@ -3539,28 +3539,28 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>臺中市政府環境保護局</t>
+          <t>廣亞學校財團法人育達科技大學</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>115年度環保英雄歲末嘉年華活動採購案</t>
+          <t>研究發展處創新創業輔導暨育成中心115年青年創業工作坊專案管理計畫青年遴選活動頒獎典禮暨成果展評選採購</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>1105000</v>
+        <v>350000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>N1151013101</t>
+          <t>115J-04</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3589,11 +3589,11 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>嘉年華</t>
+          <t>頒獎典禮、成果展、活動、工作坊</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
@@ -3609,30 +3609,30 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>新北市政府環境保護局</t>
+          <t>苗栗縣政府衛生局</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>116年度資源回收推動及形象改造計畫</t>
+          <t>115年衛生教育之媒體廣告行銷推廣</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>9670000</v>
+        <v>770000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>115-177</t>
+          <t>11535</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3652,11 +3652,11 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>形象改造</t>
+          <t>行銷推廣、廣告、媒體</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
@@ -3672,25 +3672,25 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>原住民族委員會原住民族文化發展中心</t>
+          <t>新竹市政府</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>116年公益彩券回饋金計畫-文化觀光行銷專業人才勞務採購案</t>
+          <t>116年新竹市政府城市行銷處社群網站管理</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>4681825</v>
+        <v>1900000</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1150006860</t>
+          <t>1150300</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3715,11 +3715,11 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>觀光行銷</t>
+          <t>城市行銷、社群網站</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
@@ -3735,21 +3735,21 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>勞動部</t>
+          <t>高雄市政府地政局</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>115年度「勞工自願提繳退休金影片製作案」</t>
+          <t>115年度不動產防詐暨交易安全宣導活動委外服務案</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>997920</v>
+        <v>400000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -3768,21 +3768,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>03-11509091</t>
+          <t>115019</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>影片製作</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
@@ -3798,54 +3798,54 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>桃園市政府捷運工程局</t>
+          <t>桃園市政府環境保護局</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>桃園市八德區德和路一段第2階段通車活動委託服務案</t>
+          <t>116年社群網路環境教育推廣維運計畫</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1000000</v>
+        <v>3800000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1151006</t>
+          <t>1150085608</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>推廣、社群</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
@@ -3861,30 +3861,30 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>中華郵政股份有限公司</t>
+          <t>嘉義縣表演藝術中心</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>115年度郵政形象廣告電視託播</t>
+          <t>嘉義縣表演藝術中心115年表演節目整合傳播委託專業服務案</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>6000000</v>
+        <v>800000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>公開招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>115-5-294</t>
+          <t>1150002654</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3904,11 +3904,11 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>電視託播、形象廣告</t>
+          <t>整合傳播</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
@@ -3924,30 +3924,30 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>臺銀人壽保險股份有限公司</t>
+          <t>南投縣水里鄉公所</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>115年壽險行銷研討會-理財激勵專案</t>
+          <t>「2026水里觀光行銷暨農特產品推廣系列活動—煙火設計及施放勞務採購案」</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>8330000</v>
+        <v>1000000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3957,21 +3957,21 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>115-005-106-CL-1-798</t>
+          <t>115SHTS07</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>研討會</t>
+          <t>系列活動、觀光行銷、推廣</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
@@ -3987,23 +3987,25 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>國立臺南大學</t>
+          <t>國立臺灣大學</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>幼兒美感教育社群與國際交流影音紀錄</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr"/>
+          <t>2027年臺大杜鵑花節學系博覽會場佈</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>1250000</v>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4018,21 +4020,21 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1151065-TL</t>
+          <t>1150963</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>國際會議論壇/宣導行銷</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>國際交流、社群</t>
+          <t>博覽會</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
@@ -4048,21 +4050,21 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>臺東縣鹿野鄉公所</t>
+          <t>高雄市政府運動發展局</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026鹿野馬拉松系列活動賽事勞務採購案</t>
+          <t>企業22年甲級排球聯賽高雄台電女子排球隊主場賽事行銷活動案</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>1460000</v>
+        <v>590000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -4081,17 +4083,17 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1150929</t>
+          <t>115-B-76</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>系列活動</t>
+          <t>活動、行銷</t>
         </is>
       </c>
       <c r="K58" t="n">
@@ -4111,30 +4113,30 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>臺中市大里區公所</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>115年大里區運動會暨里鄰長健行活動規劃執行委託專業服務採購</t>
+          <t>115年度管路灌溉成果推廣活動</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>400000</v>
+        <v>4000000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4144,17 +4146,17 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>115dali032</t>
+          <t>TY115B030</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>活動規劃</t>
+          <t>活動、推廣</t>
         </is>
       </c>
       <c r="K59" t="n">
@@ -4174,50 +4176,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>桃園市復興區公所</t>
+          <t>臺北市政府工務局</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>桃園市復興區115年度甜柿推廣活動好柿發聲勞務採購案</t>
+          <t>116年全國大專院校運動會開閉幕典禮活動</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>766500</v>
+        <v>10000000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>115D52</t>
+          <t>1150826S0096</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>活動、推廣</t>
+          <t>活動、典禮</t>
         </is>
       </c>
       <c r="K60" t="n">
@@ -4237,25 +4239,25 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>南投縣政府</t>
+          <t>臺中市政府環境保護局</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>115年度南投拍片好所在影視音協拍多元媒體宣傳採購案</t>
+          <t>115年度環保英雄歲末嘉年華活動採購案</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>1100000</v>
+        <v>1105000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4270,17 +4272,17 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1150707005G</t>
+          <t>N1151013101</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>媒體宣傳</t>
+          <t>嘉年華</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -4300,25 +4302,25 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>農業部林業及自然保育署阿里山林業鐵路及文化資產管理處</t>
+          <t>新北市政府環境保護局</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>阿里山林鐵服務中心小葉子館之展覽、賣店、服務設施規劃暨製作案</t>
+          <t>116年度資源回收推動及形象改造計畫</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>2500000</v>
+        <v>9670000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4328,26 +4330,26 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>115-ALI-001</t>
+          <t>115-177</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>展覽</t>
+          <t>形象改造</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
@@ -4363,30 +4365,30 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>苗栗縣政府</t>
+          <t>原住民族委員會原住民族文化發展中心</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>苗栗縣政府115年度短影音攝製暨電視宣傳委託專業服務案</t>
+          <t>116年公益彩券回饋金計畫-文化觀光行銷專業人才勞務採購案</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>650000</v>
+        <v>4681825</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4396,7 +4398,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>115147f</t>
+          <t>1150006860</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4406,11 +4408,11 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>宣傳</t>
+          <t>觀光行銷</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
@@ -4426,25 +4428,25 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>花蓮縣豐濱鄉公所</t>
+          <t>勞動部</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>115年「點亮豐濱！族語詩歌高聲唱耶誕嘉年華暨文化健康站成果展」勞務採購案</t>
+          <t>115年度「勞工自願提繳退休金影片製作案」</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>1100000</v>
+        <v>997920</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4459,21 +4461,21 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>FB1151218</t>
+          <t>03-11509091</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>嘉年華、成果展</t>
+          <t>影片製作</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
@@ -4489,54 +4491,54 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>臺中市政府研究發展考核委員會</t>
+          <t>桃園市政府捷運工程局</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>「115年度臺中市經濟發展與城市行銷推廣案」委託專業服務案</t>
+          <t>桃園市八德區德和路一段第2階段通車活動委託服務案</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>2520000</v>
+        <v>1000000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>115RCP16</t>
+          <t>1151006</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>行銷推廣、城市行銷</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
@@ -4552,30 +4554,30 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>高雄市政府經濟發展局</t>
+          <t>中華郵政股份有限公司</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>「2027高雄過好年聯合記者會」委託專業服務案</t>
+          <t>115年度郵政形象廣告電視託播</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>500000</v>
+        <v>6000000</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>公開招標公告</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4585,21 +4587,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>115090</t>
+          <t>115-5-294</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>記者會</t>
+          <t>電視託播、形象廣告</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
@@ -4615,54 +4617,54 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>內政部</t>
+          <t>臺銀人壽保險股份有限公司</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>115年度合作社制度宣導短片託播案</t>
+          <t>115年壽險行銷研討會-理財激勵專案</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>800000</v>
+        <v>8330000</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>115HT-NH090806</t>
+          <t>115-005-106-CL-1-798</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>宣導短片</t>
+          <t>研討會</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
@@ -4678,25 +4680,23 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>花蓮縣議會</t>
+          <t>國立臺南大學</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>花蓮縣議會「第21屆議員宣誓就職典禮暨正副議長選舉」委託專業服務案</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="n">
-        <v>360000</v>
-      </c>
+          <t>幼兒美感教育社群與國際交流影音紀錄</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4711,21 +4711,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>115GA31</t>
+          <t>1151065-TL</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>國際會議論壇/宣導行銷</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>典禮</t>
+          <t>國際交流、社群</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
@@ -4741,30 +4741,30 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>南投縣水里鄉公所</t>
+          <t>臺東縣鹿野鄉公所</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>「2026水里觀光行銷暨農特產推廣系列活動」勞務採購案</t>
+          <t>2026鹿野馬拉松系列活動賽事勞務採購案</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>4300000</v>
+        <v>1460000</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4774,21 +4774,21 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>115SHTS06</t>
+          <t>1150929</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>系列活動、觀光行銷、推廣</t>
+          <t>系列活動</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
@@ -4804,25 +4804,25 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>花蓮縣政府</t>
+          <t>臺中市大里區公所</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>115年花蓮縣長青大學結業典禮暨成果展活動</t>
+          <t>115年大里區運動會暨里鄰長健行活動規劃執行委託專業服務採購</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>1150000</v>
+        <v>400000</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>SC1150020901</t>
+          <t>115dali032</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4847,11 +4847,11 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>成果展、活動、典禮</t>
+          <t>活動規劃</t>
         </is>
       </c>
       <c r="K70" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
@@ -4867,25 +4867,25 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>臺南市政府經濟發展局</t>
+          <t>桃園市復興區公所</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>「116年永康迎春嘉年華」活動規劃執行服務</t>
+          <t>桃園市復興區115年度甜柿推廣活動好柿發聲勞務採購案</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>600000</v>
+        <v>766500</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4900,21 +4900,21 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>115ECON71S1</t>
+          <t>115D52</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>嘉年華、活動規劃</t>
+          <t>活動、推廣</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
@@ -4930,30 +4930,30 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>臺北表演藝術中心</t>
+          <t>南投縣政府</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>第三屆臺北戲劇獎頒獎典禮暨系列活動製作執行勞務採購案</t>
+          <t>115年度南投拍片好所在影視音協拍多元媒體宣傳採購案</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>15000000</v>
+        <v>1100000</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4963,21 +4963,21 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>TPACRD1150141</t>
+          <t>1150707005G</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>頒獎典禮、系列活動</t>
+          <t>媒體宣傳</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
@@ -4993,54 +4993,54 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>屏東縣獅子鄉公所</t>
+          <t>農業部林業及自然保育署阿里山林業鐵路及文化資產管理處</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>屏東縣獅子鄉115年度慶祝重陽節聯合表揚暨族語文化推廣與文化健康站成果展活動勞務採購案</t>
+          <t>阿里山林鐵服務中心小葉子館之展覽、賣店、服務設施規劃暨製作案</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>1162700</v>
+        <v>2500000</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1151001AA</t>
+          <t>115-ALI-001</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>成果展、活動、推廣</t>
+          <t>展覽</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
@@ -5056,21 +5056,21 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>宜蘭縣政府</t>
+          <t>苗栗縣政府</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>「宜蘭縣115年國際移民嘉年華」活動規劃執行委託案</t>
+          <t>苗栗縣政府115年度短影音攝製暨電視宣傳委託專業服務案</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>400000</v>
+        <v>650000</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -5089,21 +5089,21 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>CVSL115019</t>
+          <t>115147f</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>嘉年華、活動規劃</t>
+          <t>宣傳</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
@@ -5119,25 +5119,25 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>財政部高雄國稅局</t>
+          <t>花蓮縣豐濱鄉公所</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>115年度結合統一發票推行暨「來稅局找碴-觀察力培養計畫」租稅宣導活動委外服務案</t>
+          <t>115年「點亮豐濱！族語詩歌高聲唱耶誕嘉年華暨文化健康站成果展」勞務採購案</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>445000</v>
+        <v>1100000</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5152,21 +5152,21 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>1150042</t>
+          <t>FB1151218</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>嘉年華、成果展</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
@@ -5182,30 +5182,30 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>國立臺中教育大學</t>
+          <t>臺中市政府研究發展考核委員會</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>115年原住民族教育論壇暨原住民族教育資源中心成果交流會</t>
+          <t>「115年度臺中市經濟發展與城市行銷推廣案」委託專業服務案</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>1450000</v>
+        <v>2520000</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5215,21 +5215,21 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>115-C062</t>
+          <t>115RCP16</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>論壇</t>
+          <t>行銷推廣、城市行銷</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
@@ -5245,21 +5245,21 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>衛生福利部疾病管制署</t>
+          <t>高雄市政府經濟發展局</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>「115年度防疫績優獎頒獎典禮專業服務」採購案</t>
+          <t>「2027高雄過好年聯合記者會」委託專業服務案</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>950000</v>
+        <v>500000</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>LA115028</t>
+          <t>115090</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>頒獎典禮</t>
+          <t>記者會</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -5308,25 +5308,25 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>花蓮縣政府</t>
+          <t>內政部</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>115年花蓮縣精品咖啡行銷推廣計畫</t>
+          <t>115年度合作社制度宣導短片託播案</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>1100000</v>
+        <v>800000</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>AG1150018061</t>
+          <t>115HT-NH090806</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>行銷推廣</t>
+          <t>宣導短片</t>
         </is>
       </c>
       <c r="K78" t="n">
@@ -5371,21 +5371,21 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>社團法人花蓮縣基督教會花蓮靈糧堂宣教協會</t>
+          <t>花蓮縣議會</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026花蓮幸福聖誕城行銷宣傳及城市聯合宣傳規劃案</t>
+          <t>花蓮縣議會「第21屆議員宣誓就職典禮暨正副議長選舉」委託專業服務案</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>6789600</v>
+        <v>360000</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5404,21 +5404,21 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-2HLLC</t>
+          <t>115GA31</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>行銷宣傳</t>
+          <t>典禮</t>
         </is>
       </c>
       <c r="K79" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
@@ -5439,20 +5439,20 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>社團法人花蓮縣基督教會花蓮靈糧堂宣教協會</t>
+          <t>南投縣水里鄉公所</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026花蓮幸福聖誕城活動執行案</t>
+          <t>「2026水里觀光行銷暨農特產推廣系列活動」勞務採購案</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>9950000</v>
+        <v>4300000</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5467,21 +5467,21 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-1HLLC</t>
+          <t>115SHTS06</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>系列活動、觀光行銷、推廣</t>
         </is>
       </c>
       <c r="K80" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
@@ -5502,16 +5502,16 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>桃園市平鎮區公所</t>
+          <t>花蓮縣政府</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>116年桃園市平鎮區元旦升旗典禮活動</t>
+          <t>115年花蓮縣長青大學結業典禮暨成果展活動</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>450000</v>
+        <v>1150000</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>1151005A01</t>
+          <t>SC1150020901</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5540,11 +5540,11 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>活動、典禮</t>
+          <t>成果展、活動、典禮</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
@@ -5565,20 +5565,20 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>彰化縣田中鎮公所</t>
+          <t>臺南市政府經濟發展局</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026田中藝術節–愛閱田中・藝起嗨劇場委託專業服務採購案</t>
+          <t>「116年永康迎春嘉年華」活動規劃執行服務</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>700000</v>
+        <v>600000</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>115-081</t>
+          <t>115ECON71S1</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5603,11 +5603,11 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>藝術節</t>
+          <t>嘉年華、活動規劃</t>
         </is>
       </c>
       <c r="K82" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
@@ -5628,20 +5628,20 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>臺北表演藝術中心</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>116年屏東縣政府社會處網路媒體行銷維運案</t>
+          <t>第三屆臺北戲劇獎頒獎典禮暨系列活動製作執行勞務採購案</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>2000000</v>
+        <v>15000000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5656,21 +5656,21 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>A058-1151007-2</t>
+          <t>TPACRD1150141</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>媒體行銷</t>
+          <t>頒獎典禮、系列活動</t>
         </is>
       </c>
       <c r="K83" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
@@ -5691,20 +5691,20 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>南投縣政府</t>
+          <t>屏東縣獅子鄉公所</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>115年縣政成果及重大活動影音攝製行銷案</t>
+          <t>屏東縣獅子鄉115年度慶祝重陽節聯合表揚暨族語文化推廣與文化健康站成果展活動勞務採購案</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>1400000</v>
+        <v>1162700</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>115-07-06-011E</t>
+          <t>1151001AA</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5729,11 +5729,11 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>活動、行銷</t>
+          <t>成果展、活動、推廣</t>
         </is>
       </c>
       <c r="K84" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
@@ -5754,20 +5754,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>苗栗縣政府</t>
+          <t>宜蘭縣政府</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>「2027台灣燈會在苗栗」廣播錄製暨執行委託專業服務案</t>
+          <t>「宜蘭縣115年國際移民嘉年華」活動規劃執行委託案</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>500000</v>
+        <v>400000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>115141f</t>
+          <t>CVSL115019</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5792,11 +5792,11 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>燈會</t>
+          <t>嘉年華、活動規劃</t>
         </is>
       </c>
       <c r="K85" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
@@ -5817,20 +5817,20 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>臺南市政府經濟發展局</t>
+          <t>財政部高雄國稅局</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>「2027新化年貨大街」活動委託服務案</t>
+          <t>115年度結合統一發票推行暨「來稅局找碴-觀察力培養計畫」租稅宣導活動委外服務案</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>1100000</v>
+        <v>445000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5845,21 +5845,21 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>115ECON72S1</t>
+          <t>1150042</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K86" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
@@ -5875,30 +5875,30 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>花蓮縣政府</t>
+          <t>國立臺中教育大學</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026花蓮星潮原聲系列活動規劃執行案</t>
+          <t>115年原住民族教育論壇暨原住民族教育資源中心成果交流會</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>40000000</v>
+        <v>1450000</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5908,21 +5908,21 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>AB1150007224</t>
+          <t>115-C062</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>系列活動、活動規劃</t>
+          <t>論壇</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="L87" s="3" t="inlineStr">
         <is>
@@ -5938,25 +5938,25 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>南投縣政府</t>
+          <t>衛生福利部疾病管制署</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>「2026南投花卉嘉年華－草屯展區系列活動」勞務採購案</t>
+          <t>「115年度防疫績優獎頒獎典禮專業服務」採購案</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>1000000</v>
+        <v>950000</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1150602018G</t>
+          <t>LA115028</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5981,11 +5981,11 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>嘉年華、系列活動</t>
+          <t>頒獎典禮</t>
         </is>
       </c>
       <c r="K88" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
@@ -6001,25 +6001,25 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>內政部</t>
+          <t>花蓮縣政府</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>116年第84屆兵役節慶祝大會暨頒獎典禮委外服務案</t>
+          <t>115年花蓮縣精品咖啡行銷推廣計畫</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>1230000</v>
+        <v>1100000</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -6034,21 +6034,21 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>115YJ-ST15</t>
+          <t>AG1150018061</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>國際會議論壇/活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>大會、頒獎典禮</t>
+          <t>行銷推廣</t>
         </is>
       </c>
       <c r="K89" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L89" s="3" t="inlineStr">
         <is>
@@ -6064,30 +6064,30 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>國立臺灣美術館</t>
+          <t>社團法人花蓮縣基督教會花蓮靈糧堂宣教協會</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">國家珍藏作品之線上藝廊推廣影片製作採購案 </t>
+          <t>2026花蓮幸福聖誕城行銷宣傳及城市聯合宣傳規劃案</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>600000</v>
+        <v>6789600</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>115118</t>
+          <t>2026-2HLLC</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6107,11 +6107,11 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>影片製作、推廣</t>
+          <t>行銷宣傳</t>
         </is>
       </c>
       <c r="K90" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
@@ -6127,25 +6127,25 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>苗栗縣苗栗市公所</t>
+          <t>社團法人花蓮縣基督教會花蓮靈糧堂宣教協會</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>苗栗市2026冬迎璀璨歲末藝文嘉年華</t>
+          <t>2026花蓮幸福聖誕城活動執行案</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>2440000</v>
+        <v>9950000</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>C548</t>
+          <t>2026-1HLLC</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>嘉年華</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="K91" t="n">
@@ -6190,25 +6190,25 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>苗栗縣苗栗市公所</t>
+          <t>桃園市平鎮區公所</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>115年度苗栗市親子蘿蔔節活動執行委託專業服務採購案</t>
+          <t>116年桃園市平鎮區元旦升旗典禮活動</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>1000000</v>
+        <v>450000</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>B1600</t>
+          <t>1151005A01</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動、典禮</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -6253,40 +6253,40 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>桃園市政府工務局</t>
+          <t>彰化縣田中鎮公所</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>115年桃園市食農教育執行成果展委託專業服務案</t>
+          <t>2026田中藝術節–愛閱田中・藝起嗨劇場委託專業服務採購案</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>2000000</v>
+        <v>700000</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>1151005-3</t>
+          <t>115-081</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>成果展</t>
+          <t>藝術節</t>
         </is>
       </c>
       <c r="K93" t="n">
@@ -6316,30 +6316,30 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>新竹縣尖石鄉公所</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>新竹縣尖石鄉115年尖石鄉鄉長盃第二屆傳統路跑嘉年華暨傳統擲矛、傳統狩獵活動勞務採購案</t>
+          <t>116年屏東縣政府社會處網路媒體行銷維運案</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>950000</v>
+        <v>2000000</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -6349,17 +6349,17 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1159226</t>
+          <t>A058-1151007-2</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>嘉年華</t>
+          <t>媒體行銷</t>
         </is>
       </c>
       <c r="K94" t="n">
@@ -6379,30 +6379,30 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>嘉義縣文化觀光局</t>
+          <t>南投縣政府</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>「116年度嘉義縣觀光旅遊數位整合行銷」委託專業服務案</t>
+          <t>115年縣政成果及重大活動影音攝製行銷案</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>2000000</v>
+        <v>1400000</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -6412,17 +6412,17 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1150011120</t>
+          <t>115-07-06-011E</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>整合行銷</t>
+          <t>活動、行銷</t>
         </is>
       </c>
       <c r="K95" t="n">
@@ -6442,21 +6442,21 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>台灣中油股份有限公司探採事業部</t>
+          <t>苗栗縣政府</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>碳封存監測資料彙整分析及社會溝通顧問服務</t>
+          <t>「2027台灣燈會在苗栗」廣播錄製暨執行委託專業服務案</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>1490000</v>
+        <v>500000</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -6470,26 +6470,26 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>BEA1500013</t>
+          <t>115141f</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>政策溝通</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>社會溝通</t>
+          <t>燈會</t>
         </is>
       </c>
       <c r="K96" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
@@ -6505,25 +6505,25 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>中央選舉委員會</t>
+          <t>臺南市政府經濟發展局</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>115年地方公職人員選舉及公民投票選務滿意度民意調查採購案</t>
+          <t>「2027新化年貨大街」活動委託服務案</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>500000</v>
+        <v>1100000</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -6538,21 +6538,21 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>1150909</t>
+          <t>115ECON72S1</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>政策溝通</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>民意調查</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K97" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L97" s="3" t="inlineStr">
         <is>
@@ -6573,25 +6573,25 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>桃園市政府捷運工程局</t>
+          <t>花蓮縣政府</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>桃園市八德區德和路一段第2階段通車活動委託服務案</t>
+          <t>2026花蓮星潮原聲系列活動規劃執行案</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>1000000</v>
+        <v>40000000</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1151006</t>
+          <t>AB1150007224</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6611,11 +6611,11 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>系列活動、活動規劃</t>
         </is>
       </c>
       <c r="K98" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="L98" s="3" t="inlineStr">
         <is>
@@ -6631,30 +6631,30 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>國防部</t>
+          <t>南投縣政府</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>國軍招募宣傳電視廣告託播</t>
+          <t>「2026南投花卉嘉年華－草屯展區系列活動」勞務採購案</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>公開招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -6664,21 +6664,21 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>CC15003L050</t>
+          <t>1150602018G</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>廣告託播、宣傳</t>
+          <t>嘉年華、系列活動</t>
         </is>
       </c>
       <c r="K99" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L99" s="3" t="inlineStr">
         <is>
@@ -6694,30 +6694,30 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>衛生福利部社會及家庭署</t>
+          <t>內政部</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>116年度強化社會安全網績優人員及團體獎項品牌識別系統專業服務案</t>
+          <t>116年第84屆兵役節慶祝大會暨頒獎典禮委外服務案</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>2550000</v>
+        <v>1230000</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6727,21 +6727,21 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>C116001</t>
+          <t>115YJ-ST15</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>國際會議論壇/活動執行</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>品牌識別</t>
+          <t>大會、頒獎典禮</t>
         </is>
       </c>
       <c r="K100" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
@@ -6757,30 +6757,30 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>臺北市政府觀光傳播局</t>
+          <t>國立臺灣美術館</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>116年度臺北開齋節暨穆斯林友善城市推廣活動案</t>
+          <t xml:space="preserve">國家珍藏作品之線上藝廊推廣影片製作採購案 </t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>4000000</v>
+        <v>600000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6790,21 +6790,21 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>1150075</t>
+          <t>115118</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>活動、推廣</t>
+          <t>影片製作、推廣</t>
         </is>
       </c>
       <c r="K101" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L101" s="3" t="inlineStr">
         <is>
@@ -6820,30 +6820,30 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>國立歷史博物館</t>
+          <t>苗栗縣苗栗市公所</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>常設展手語導覽影片製作案</t>
+          <t>苗栗市2026冬迎璀璨歲末藝文嘉年華</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>950000</v>
+        <v>2440000</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6853,17 +6853,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>115046</t>
+          <t>C548</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>影片製作</t>
+          <t>嘉年華</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -6883,30 +6883,30 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>內政部國土管理署</t>
+          <t>苗栗縣苗栗市公所</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>116年度住宅政策推廣影音及多媒體製作案</t>
+          <t>115年度苗栗市親子蘿蔔節活動執行委託專業服務採購案</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>9950000</v>
+        <v>1000000</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6916,17 +6916,17 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>115A-066</t>
+          <t>B1600</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>推廣、媒體</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="K103" t="n">
@@ -6946,25 +6946,25 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>高雄市政府勞工局訓練就業中心</t>
+          <t>桃園市政府工務局</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>「116年度鳳山、岡山就業服務站現場徵才活動」委託服務案</t>
+          <t>115年桃園市食農教育執行成果展委託專業服務案</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>2892100</v>
+        <v>2000000</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>116F002</t>
+          <t>1151005-3</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6989,11 +6989,11 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>成果展</t>
         </is>
       </c>
       <c r="K104" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L104" s="3" t="inlineStr">
         <is>
@@ -7009,25 +7009,25 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>新北市政府勞工局</t>
+          <t>新竹縣尖石鄉公所</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>新北市政府116年度外國人文化與休閒活動計畫-越南、印尼活動委託專業服務採購案</t>
+          <t>新竹縣尖石鄉115年尖石鄉鄉長盃第二屆傳統路跑嘉年華暨傳統擲矛、傳統狩獵活動勞務採購案</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>1300000</v>
+        <v>950000</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -7037,12 +7037,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>TPLAB115013</t>
+          <t>1159226</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7052,11 +7052,11 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>嘉年華</t>
         </is>
       </c>
       <c r="K105" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L105" s="3" t="inlineStr">
         <is>
@@ -7072,30 +7072,30 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>臺中市石岡區公所</t>
+          <t>嘉義縣文化觀光局</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>115年石岡童樂會暨水資源宣導活動</t>
+          <t>「116年度嘉義縣觀光旅遊數位整合行銷」委託專業服務案</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>800000</v>
+        <v>2000000</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7105,21 +7105,21 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>115SK20</t>
+          <t>1150011120</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>整合行銷</t>
         </is>
       </c>
       <c r="K106" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L106" s="3" t="inlineStr">
         <is>
@@ -7135,21 +7135,21 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>臺中市石岡區公所</t>
+          <t>台灣中油股份有限公司探採事業部</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026臺中市民野餐日（石岡區）暨觀光活化水資源宣導活動</t>
+          <t>碳封存監測資料彙整分析及社會溝通顧問服務</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>920000</v>
+        <v>1490000</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -7163,26 +7163,26 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>115SK19</t>
+          <t>BEA1500013</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>政策溝通</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>社會溝通</t>
         </is>
       </c>
       <c r="K107" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L107" s="3" t="inlineStr">
         <is>
@@ -7198,30 +7198,30 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>新竹縣芎林鄉公所</t>
+          <t>中央選舉委員會</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2027芎林路跑嘉年華活動計畫委託專業服務案</t>
+          <t>115年地方公職人員選舉及公民投票選務滿意度民意調查採購案</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>2400000</v>
+        <v>500000</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -7231,21 +7231,21 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>1160001P</t>
+          <t>1150909</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>政策溝通</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>嘉年華、活動</t>
+          <t>民意調查</t>
         </is>
       </c>
       <c r="K108" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L108" s="3" t="inlineStr">
         <is>
@@ -7261,30 +7261,30 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>海洋委員會</t>
+          <t>桃園市政府捷運工程局</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>海洋博覽會整體規劃暨先期策略研析委託專業服務案</t>
+          <t>桃園市八德區德和路一段第2階段通車活動委託服務案</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>3000000</v>
+        <v>1000000</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -7294,21 +7294,21 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>OAC115044</t>
+          <t>1151006</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>博覽會</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K109" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L109" s="3" t="inlineStr">
         <is>
@@ -7324,30 +7324,30 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>花蓮縣政府</t>
+          <t>國防部</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>115年花蓮宜居城市行銷採購案(開口契約)</t>
+          <t>國軍招募宣傳電視廣告託播</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>9450000</v>
+        <v>2000000</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開招標公告</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>SK1150005862</t>
+          <t>CC15003L050</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7367,11 +7367,11 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>城市行銷</t>
+          <t>廣告託播、宣傳</t>
         </is>
       </c>
       <c r="K110" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L110" s="3" t="inlineStr">
         <is>
@@ -7387,30 +7387,30 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>花蓮縣政府</t>
+          <t>衛生福利部社會及家庭署</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>115年花蓮縣社區照顧關懷據點及社區長照站成果展</t>
+          <t>116年度強化社會安全網績優人員及團體獎項品牌識別系統專業服務案</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>1250000</v>
+        <v>2550000</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -7420,17 +7420,17 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>SC1150020073</t>
+          <t>C116001</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>成果展</t>
+          <t>品牌識別</t>
         </is>
       </c>
       <c r="K111" t="n">
@@ -7450,30 +7450,30 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>桃園市政府文化局</t>
+          <t>臺北市政府觀光傳播局</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026桃園仙草花節系列活動-民歌演唱會委託專業服務案</t>
+          <t>116年度臺北開齋節暨穆斯林友善城市推廣活動案</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>500000</v>
+        <v>4000000</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -7483,17 +7483,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>TYC115-39</t>
+          <t>1150075</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>系列活動</t>
+          <t>活動、推廣</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -7513,21 +7513,21 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>宜蘭縣政府</t>
+          <t>國立歷史博物館</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>宜蘭縣115年度原有住宅無障礙設施補助委託辦理推廣宣導評估案</t>
+          <t>常設展手語導覽影片製作案</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>1210000</v>
+        <v>950000</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>CNSL115032</t>
+          <t>115046</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>宣導、推廣</t>
+          <t>影片製作</t>
         </is>
       </c>
       <c r="K113" t="n">
@@ -7576,25 +7576,25 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>財團法人嘉義市文化基金會</t>
+          <t>內政部國土管理署</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026嘉義市管樂節晚會舞台暨表演節目規畫執行委託服務案</t>
+          <t>116年度住宅政策推廣影音及多媒體製作案</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>15000000</v>
+        <v>9950000</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -7609,21 +7609,21 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>115A001</t>
+          <t>115A-066</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>晚會</t>
+          <t>推廣、媒體</t>
         </is>
       </c>
       <c r="K114" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L114" s="3" t="inlineStr">
         <is>
@@ -7639,21 +7639,21 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>新竹市政府</t>
+          <t>高雄市政府勞工局訓練就業中心</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>「2026客家藝文活動」委託專業服務案</t>
+          <t>「116年度鳳山、岡山就業服務站現場徵才活動」委託服務案</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>2400000</v>
+        <v>2892100</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>1150292</t>
+          <t>116F002</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7702,54 +7702,54 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>新北市政府觀光旅遊局</t>
+          <t>新北市政府勞工局</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>116年度跨媒體整合傳播採購案</t>
+          <t>新北市政府116年度外國人文化與休閒活動計畫-越南、印尼活動委託專業服務採購案</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>7350000</v>
+        <v>1300000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>1151911877</t>
+          <t>TPLAB115013</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>整合傳播、跨媒體</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K116" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L116" s="3" t="inlineStr">
         <is>
@@ -7765,30 +7765,30 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>司法院</t>
+          <t>臺中市石岡區公所</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>司法院115年司法博物館主題活動規劃執行採購案</t>
+          <t>115年石岡童樂會暨水資源宣導活動</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>3400000</v>
+        <v>800000</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -7798,21 +7798,21 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>1151400844</t>
+          <t>115SK20</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>活動規劃、主題活動</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K117" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L117" s="3" t="inlineStr">
         <is>
@@ -7828,21 +7828,21 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>彰化縣伸港鄉公所</t>
+          <t>臺中市石岡區公所</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2027年伸港飛揚-元旦升旗健行齊步走暨節能減碳宣導活動委託服務案</t>
+          <t>2026臺中市民野餐日（石岡區）暨觀光活化水資源宣導活動</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>1152300</v>
+        <v>920000</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -7856,12 +7856,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>1152006</t>
+          <t>115SK19</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7891,30 +7891,30 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>臺東縣政府</t>
+          <t>新竹縣芎林鄉公所</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>興隆國小--臺東縣115年度環境變遷與藍碳發展論壇暨體驗學習活動</t>
+          <t>2027芎林路跑嘉年華活動計畫委託專業服務案</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>420000</v>
+        <v>2400000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -7924,21 +7924,21 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>115310130545</t>
+          <t>1160001P</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>論壇</t>
+          <t>嘉年華、活動</t>
         </is>
       </c>
       <c r="K119" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L119" s="3" t="inlineStr">
         <is>
@@ -7954,25 +7954,25 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>桃園市政府文化局</t>
+          <t>海洋委員會</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026桃園社造博覽會規劃執行案</t>
+          <t>海洋博覽會整體規劃暨先期策略研析委託專業服務案</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -7987,7 +7987,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>1150276</t>
+          <t>OAC115044</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -8017,30 +8017,30 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>新北市政府水利局</t>
+          <t>花蓮縣政府</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>新北市治水、清水、親水水環境治理成果影片製作案</t>
+          <t>115年花蓮宜居城市行銷採購案(開口契約)</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>1200000</v>
+        <v>9450000</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>1150930A</t>
+          <t>SK1150005862</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>影片製作</t>
+          <t>城市行銷</t>
         </is>
       </c>
       <c r="K121" t="n">
@@ -8080,25 +8080,25 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>彰化縣田中鎮公所</t>
+          <t>花蓮縣政府</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026田中藝術節–愛閱田中・藝起嗨劇場委託專業服務採購案</t>
+          <t>115年花蓮縣社區照顧關懷據點及社區長照站成果展</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>700000</v>
+        <v>1250000</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>115-081</t>
+          <t>SC1150020073</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>藝術節</t>
+          <t>成果展</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -8143,25 +8143,25 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>外交部領事事務局</t>
+          <t>桃園市政府文化局</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>115年度推廣外交部領事事務局「LINE官方帳號」靜態貼圖廣告方案</t>
+          <t>2026桃園仙草花節系列活動-民歌演唱會委託專業服務案</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>630000</v>
+        <v>500000</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -8176,17 +8176,17 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>T115027CB</t>
+          <t>TYC115-39</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>廣告、推廣</t>
+          <t>系列活動</t>
         </is>
       </c>
       <c r="K123" t="n">
@@ -8206,30 +8206,30 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>勞動部勞動力發展署桃竹苗分署</t>
+          <t>宜蘭縣政府</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>116年機關整合行銷勞務採購案</t>
+          <t>宜蘭縣115年度原有住宅無障礙設施補助委託辦理推廣宣導評估案</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>1330000</v>
+        <v>1210000</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>116Y020</t>
+          <t>CNSL115032</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>整合行銷</t>
+          <t>宣導、推廣</t>
         </is>
       </c>
       <c r="K124" t="n">
@@ -8266,8 +8266,701 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>財團法人嘉義市文化基金會</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2026嘉義市管樂節晚會舞台暨表演節目規畫執行委託服務案</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>115A001</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>活動執行</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>晚會</t>
+        </is>
+      </c>
+      <c r="K125" t="n">
+        <v>4</v>
+      </c>
+      <c r="L125" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>新竹市政府</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>「2026客家藝文活動」委託專業服務案</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>1150292</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>活動執行</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>活動</t>
+        </is>
+      </c>
+      <c r="K126" t="n">
+        <v>4</v>
+      </c>
+      <c r="L126" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>新北市政府觀光旅遊局</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>116年度跨媒體整合傳播採購案</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>7350000</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>1151911877</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>宣導行銷</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>整合傳播、跨媒體</t>
+        </is>
+      </c>
+      <c r="K127" t="n">
+        <v>16</v>
+      </c>
+      <c r="L127" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>司法院</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>司法院115年司法博物館主題活動規劃執行採購案</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>1151400844</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>活動執行</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>活動規劃、主題活動</t>
+        </is>
+      </c>
+      <c r="K128" t="n">
+        <v>16</v>
+      </c>
+      <c r="L128" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>彰化縣伸港鄉公所</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2027年伸港飛揚-元旦升旗健行齊步走暨節能減碳宣導活動委託服務案</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>1152300</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>公開取得報價單或企劃書公告</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>1152006</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>活動執行/宣導行銷</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>活動、宣導活動</t>
+        </is>
+      </c>
+      <c r="K129" t="n">
+        <v>12</v>
+      </c>
+      <c r="L129" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>臺東縣政府</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>興隆國小--臺東縣115年度環境變遷與藍碳發展論壇暨體驗學習活動</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>420000</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>公開取得報價單或企劃書公告</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>115310130545</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>國際會議論壇</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>論壇</t>
+        </is>
+      </c>
+      <c r="K130" t="n">
+        <v>10</v>
+      </c>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>桃園市政府文化局</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2026桃園社造博覽會規劃執行案</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>1150276</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>國際會議論壇</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>博覽會</t>
+        </is>
+      </c>
+      <c r="K131" t="n">
+        <v>10</v>
+      </c>
+      <c r="L131" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>新北市政府水利局</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>新北市治水、清水、親水水環境治理成果影片製作案</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>公開取得報價單或企劃書公告</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>1150930A</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>宣導行銷</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>影片製作</t>
+        </is>
+      </c>
+      <c r="K132" t="n">
+        <v>8</v>
+      </c>
+      <c r="L132" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>彰化縣田中鎮公所</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2026田中藝術節–愛閱田中・藝起嗨劇場委託專業服務採購案</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>700000</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>公開取得報價單或企劃書公告</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>115-081</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>活動執行</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>藝術節</t>
+        </is>
+      </c>
+      <c r="K133" t="n">
+        <v>8</v>
+      </c>
+      <c r="L133" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>外交部領事事務局</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>115年度推廣外交部領事事務局「LINE官方帳號」靜態貼圖廣告方案</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>630000</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>公開取得報價單或企劃書公告</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>T115027CB</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>宣導行銷</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>廣告、推廣</t>
+        </is>
+      </c>
+      <c r="K134" t="n">
+        <v>8</v>
+      </c>
+      <c r="L134" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>勞動部勞動力發展署桃竹苗分署</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>116年機關整合行銷勞務採購案</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>1330000</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>公開取得報價單或企劃書公告</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>116Y020</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>宣導行銷</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>整合行銷</t>
+        </is>
+      </c>
+      <c r="K135" t="n">
+        <v>8</v>
+      </c>
+      <c r="L135" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M124"/>
+  <autoFilter ref="A1:M135"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -8392,6 +9085,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L122" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L123" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L135" r:id="rId134"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8441,13 +9145,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4968</v>
+        <v>5485</v>
       </c>
       <c r="C2" t="n">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>329878970</v>
+        <v>430326370</v>
       </c>
     </row>
   </sheetData>
@@ -8477,7 +9181,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>產生時間：2026-10-20 09:04　資料庫共 123 筆</t>
+          <t>產生時間：2026-10-21 08:35　資料庫共 134 筆</t>
         </is>
       </c>
     </row>

--- a/data/標案資料庫.xlsx
+++ b/data/標案資料庫.xlsx
@@ -12,7 +12,7 @@
     <sheet name="說明" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'標案資料庫'!$A$1:$M$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'標案資料庫'!$A$1:$M$144</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M135"/>
+  <dimension ref="A1:M144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -524,25 +524,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>宜蘭縣政府</t>
+          <t>高雄市政府新聞局</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>「宜蘭縣115年國際移民嘉年華」活動規劃執行委託案</t>
+          <t>115年打造智慧城市網路媒體行銷案</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>400000</v>
+        <v>300000</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -552,26 +552,26 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CVSL115019</t>
+          <t>1151020B</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>嘉年華、活動規劃</t>
+          <t>媒體行銷</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -580,37 +580,37 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-21 08:35</t>
+          <t>2026-10-22 08:39</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>桃園市政府工務局</t>
+          <t>苗栗縣苗栗市公所</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>桃園市116年績優社工人員表揚典禮暨社工日系列活動</t>
+          <t>115年度苗栗市親子蘿蔔節活動執行委託專業服務採購案</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4000000</v>
+        <v>1060000</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1151019-2</t>
+          <t>B1605</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -630,11 +630,11 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>系列活動、典禮</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -643,37 +643,37 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-21 08:35</t>
+          <t>2026-10-22 08:39</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>台灣中油股份有限公司天然氣事業部觀塘液化天然氣廠</t>
+          <t>臺東縣政府</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>觀塘廠多媒體影片製作</t>
+          <t>台東紅烏龍產業培力暨跨域行銷推廣計畫委託專業服務案</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>935101</v>
+        <v>10500000</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>LEA1540001</t>
+          <t>115810430549</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -693,11 +693,11 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>影片製作、媒體</t>
+          <t>行銷推廣</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -706,37 +706,37 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-21 08:35</t>
+          <t>2026-10-22 08:39</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>勞動部勞動力發展署桃竹苗分署</t>
+          <t>臺東縣政府</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>「2027桃竹苗OpenHouse就業博覽會官方網站」勞務採購案</t>
+          <t>臺東縣116年度元旦及國慶升旗典禮慶祝活動</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>3324999</v>
+        <v>1440000</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -746,21 +746,21 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>116Y045</t>
+          <t>115130230570</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>博覽會</t>
+          <t>活動、典禮</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -769,37 +769,37 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-21 08:35</t>
+          <t>2026-10-22 08:39</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>農業部</t>
+          <t>海洋委員會海洋保育署</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>116年度整體農業政策整合行銷案</t>
+          <t>2028國際海龜年會(ISTS46)籌辦及宣傳推廣計畫</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>25000000</v>
+        <v>6000000</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>公開招標公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>11559T</t>
+          <t>115-C-106</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>整合行銷</t>
+          <t>宣傳推廣</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -832,37 +832,37 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-21 08:35</t>
+          <t>2026-10-22 08:39</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>新竹市政府</t>
+          <t>內政部國家公園署</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>115年新竹市志願服務表揚暨社區成果展委託專業服務案</t>
+          <t>臺灣濕地日品牌推廣及濕地保育社會參與計畫</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1312500</v>
+        <v>8430000</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -872,17 +872,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1150307</t>
+          <t>115N-026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>成果展</t>
+          <t>推廣、品牌</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -895,32 +895,32 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-21 08:35</t>
+          <t>2026-10-22 08:39</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>宜蘭縣政府</t>
+          <t>臺中市風景區管理所</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>宜蘭縣115年度原有住宅無障礙設施補助委託辦理推廣宣導評估案</t>
+          <t>大安港媽祖文化園區假日主題市集活動委託專業服務案</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1210000</v>
+        <v>0</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -930,26 +930,26 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>CNSL115032</t>
+          <t>115102040</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>宣導、推廣</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -958,28 +958,28 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-21 08:35</t>
+          <t>2026-10-22 08:39</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>南投縣草屯鎮公所</t>
+          <t>新竹市政府</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026草屯聖誕煙火嘉年華委託專業服務勞務採購案</t>
+          <t>新竹市政府2027年國外食品展佈展及行銷委託專業服務案</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>7000000</v>
+        <v>8000000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -998,21 +998,21 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>115FR122501</t>
+          <t>1150309</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>嘉年華</t>
+          <t>行銷</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -1021,32 +1021,32 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-21 08:35</t>
+          <t>2026-10-22 08:39</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>核能安全委員會</t>
+          <t>彰化縣員林市公所</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>116及117年度新聞媒體監測資料檢索系統勞務採購案</t>
+          <t>「116年新春揮毫贈春聯活動」委託專業服務案</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>964800</v>
+        <v>577000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1061,21 +1061,21 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>NSC11510044L</t>
+          <t>02115033</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>政策溝通</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>媒體監測</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-21 08:35</t>
+          <t>2026-10-22 08:39</t>
         </is>
       </c>
     </row>
@@ -1096,35 +1096,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>苗栗縣政府</t>
+          <t>宜蘭縣政府</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>「2027台灣燈會在苗栗－整體展演策劃、製作及執行」委託專業服務案</t>
+          <t>「宜蘭縣115年國際移民嘉年華」活動規劃執行委託案</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>55500000</v>
+        <v>400000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>115229</t>
+          <t>CVSL115019</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1134,11 +1134,11 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>燈會</t>
+          <t>嘉年華、活動規劃</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -1159,25 +1159,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>屏東縣長治鄉公所</t>
+          <t>桃園市政府工務局</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2027年繁華義勇恩公文化祭暨祭祀慶典活動委託專業服務案</t>
+          <t>桃園市116年績優社工人員表揚典禮暨社工日系列活動</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>800000</v>
+        <v>4000000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1151015</t>
+          <t>1151019-2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1197,11 +1197,11 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>系列活動、典禮</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
@@ -1217,30 +1217,30 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>衛生福利部</t>
+          <t>台灣中油股份有限公司天然氣事業部觀塘液化天然氣廠</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>116年度「社會工作專業人員表揚典禮暨宣導活動」</t>
+          <t>觀塘廠多媒體影片製作</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>2600000</v>
+        <v>935101</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1250,21 +1250,21 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>M1604017</t>
+          <t>LEA1540001</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>活動、典禮、宣導活動</t>
+          <t>影片製作、媒體</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
@@ -1273,37 +1273,37 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-20 09:04</t>
+          <t>2026-10-21 08:35</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>高雄市政府新聞局</t>
+          <t>勞動部勞動力發展署桃竹苗分署</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>施政成果暨大型活動平面整合行銷案</t>
+          <t>「2027桃竹苗OpenHouse就業博覽會官方網站」勞務採購案</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1100000</v>
+        <v>3324999</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1313,21 +1313,21 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1151015B</t>
+          <t>116Y045</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>活動、整合行銷</t>
+          <t>博覽會</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
@@ -1336,37 +1336,37 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-20 09:04</t>
+          <t>2026-10-21 08:35</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>高雄市政府工務局公園處</t>
+          <t>農業部</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>115-116年度工務建設宣導活動案(開口契約)</t>
+          <t>116年度整體農業政策整合行銷案</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>2445109</v>
+        <v>25000000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開招標公告</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1376,21 +1376,21 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>11504SB012</t>
+          <t>11559T</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>整合行銷</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
@@ -1399,28 +1399,28 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-20 09:04</t>
+          <t>2026-10-21 08:35</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>苗栗縣政府衛生局</t>
+          <t>新竹市政府</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>115年預防保健業務之戶外廣告行銷推廣</t>
+          <t>115年新竹市志願服務表揚暨社區成果展委託專業服務案</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>580000</v>
+        <v>1312500</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1434,26 +1434,26 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11532</t>
+          <t>1150307</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>行銷推廣、廣告</t>
+          <t>成果展</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
@@ -1462,28 +1462,28 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-20 09:04</t>
+          <t>2026-10-21 08:35</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>臺北市立美術館</t>
+          <t>宜蘭縣政府</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>「當代藝術與技術論壇」錄影案</t>
+          <t>宜蘭縣115年度原有住宅無障礙設施補助委託辦理推廣宣導評估案</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>220000</v>
+        <v>1210000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1492,31 +1492,31 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>115RE0118</t>
+          <t>CNSL115032</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>論壇</t>
+          <t>宣導、推廣</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
@@ -1525,32 +1525,32 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-20 09:04</t>
+          <t>2026-10-21 08:35</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>桃園市政府客家事務局</t>
+          <t>南投縣草屯鎮公所</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>桃園市政府客家事務局115-116年桃園市客家文化館展覽活動等營運管理勞務採購案</t>
+          <t>2026草屯聖誕煙火嘉年華委託專業服務勞務採購案</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>5100000</v>
+        <v>7000000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>115-022</t>
+          <t>115FR122501</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>活動、展覽</t>
+          <t>嘉年華</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1588,32 +1588,32 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-20 09:04</t>
+          <t>2026-10-21 08:35</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>南投縣政府</t>
+          <t>核能安全委員會</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>115年度幸福南投短影音行銷宣傳採購案</t>
+          <t>116及117年度新聞媒體監測資料檢索系統勞務採購案</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1400000</v>
+        <v>964800</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1628,21 +1628,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>115-07-07-006G</t>
+          <t>NSC11510044L</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>政策溝通</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>行銷宣傳</t>
+          <t>媒體監測</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
@@ -1651,32 +1651,32 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-20 09:04</t>
+          <t>2026-10-21 08:35</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>農業部林業及自然保育署花蓮分署</t>
+          <t>苗栗縣政府</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>林田山遊客中心佈展(含活動駐館)委託專業服務</t>
+          <t>「2027台灣燈會在苗栗－整體展演策劃、製作及執行」委託專業服務案</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>5900000</v>
+        <v>55500000</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>115m011</t>
+          <t>115229</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>燈會</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1714,37 +1714,37 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-20 09:04</t>
+          <t>2026-10-21 08:35</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>臺中市神岡區公所</t>
+          <t>屏東縣長治鄉公所</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>【2026臺中市民野餐日(神岡區)雙場地活動】委託專業服務採購案</t>
+          <t>2027年繁華義勇恩公文化祭暨祭祀慶典活動委託專業服務案</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1920000</v>
+        <v>800000</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>115-LS37</t>
+          <t>1151015</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-20 09:04</t>
+          <t>2026-10-21 08:35</t>
         </is>
       </c>
     </row>
@@ -1789,20 +1789,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>臺中市政府客家事務委員會</t>
+          <t>衛生福利部</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2027臺中東勢新丁粄節-文宣暨會場佈置委託專業服務勞務採購案</t>
+          <t>116年度「社會工作專業人員表揚典禮暨宣導活動」</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>1750000</v>
+        <v>2600000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1817,21 +1817,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1151102</t>
+          <t>M1604017</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>文宣</t>
+          <t>活動、典禮、宣導活動</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
@@ -1847,30 +1847,30 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>國家人權博物館</t>
+          <t>高雄市政府新聞局</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>「解嚴40週年國際論壇暨紀念專書籌劃」委託專業服務案</t>
+          <t>施政成果暨大型活動平面整合行銷案</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>2200000</v>
+        <v>1100000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1880,21 +1880,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>11590Z</t>
+          <t>1151015B</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>國際論壇、論壇</t>
+          <t>活動、整合行銷</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
@@ -1903,61 +1903,61 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>南投縣政府</t>
+          <t>高雄市政府工務局公園處</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>「2026南投花卉嘉年華－草屯展區系列活動」勞務採購案</t>
+          <t>115-116年度工務建設宣導活動案(開口契約)</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>1000000</v>
+        <v>2445109</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1150602018G</t>
+          <t>11504SB012</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>嘉年華、系列活動</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
@@ -1966,30 +1966,32 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>臺南市政府農業局</t>
+          <t>苗栗縣政府衛生局</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>日本地區臺南市農漁產推廣暨行銷活動策畫與執行委託專業服務案</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr"/>
+          <t>115年預防保健業務之戶外廣告行銷推廣</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>580000</v>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1999,22 +2001,22 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>115AGR080</t>
+          <t>11532</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>活動、行銷、推廣</t>
+          <t>行銷推廣、廣告</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -2027,28 +2029,28 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>桃園市政府環境管理處</t>
+          <t>臺北市立美術館</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>115年度職業安全衛生業務標竿學習宣導活動計畫</t>
+          <t>「當代藝術與技術論壇」錄影案</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1300000</v>
+        <v>220000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -2067,21 +2069,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1150036916</t>
+          <t>115RE0118</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>論壇</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
@@ -2090,32 +2092,32 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>南投縣政府社會及勞動局</t>
+          <t>桃園市政府客家事務局</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>南投縣115年度國際身心障礙者日宣導活動</t>
+          <t>桃園市政府客家事務局115-116年桃園市客家文化館展覽活動等營運管理勞務採購案</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>2500000</v>
+        <v>5100000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2130,21 +2132,21 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>115-10-10-005-E</t>
+          <t>115-022</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>活動、展覽</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
@@ -2153,37 +2155,37 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>財團法人蘭陽農業發展基金會</t>
+          <t>南投縣政府</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2027宜蘭綠色博覽會－海洋館委託專業服務案</t>
+          <t>115年度幸福南投短影音行銷宣傳採購案</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>7000000</v>
+        <v>1400000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2193,21 +2195,21 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>115101305</t>
+          <t>115-07-07-006G</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>博覽會</t>
+          <t>行銷宣傳</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
@@ -2216,32 +2218,32 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>財團法人蘭陽農業發展基金會</t>
+          <t>農業部林業及自然保育署花蓮分署</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2027宜蘭綠色博覽會－森林館委託專業服務案</t>
+          <t>林田山遊客中心佈展(含活動駐館)委託專業服務</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>3950000</v>
+        <v>5900000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2256,21 +2258,21 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>115101301</t>
+          <t>115m011</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>博覽會</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
@@ -2279,47 +2281,47 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>雲林縣政府</t>
+          <t>臺中市神岡區公所</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>「2026雲林文創聯合徵選暨雲林設計獎」頒獎典禮委託規劃執行案</t>
+          <t>【2026臺中市民野餐日(神岡區)雙場地活動】委託專業服務採購案</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>500000</v>
+        <v>1920000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1152H10116</t>
+          <t>115-LS37</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2329,11 +2331,11 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>頒獎典禮</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
@@ -2342,37 +2344,37 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>臺北市教師研習中心</t>
+          <t>臺中市政府客家事務委員會</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>116年度優質學校頒獎典禮、杏壇芬芳獎表揚典禮、臺北教育111標竿學校頒獎典禮採購案</t>
+          <t>2027臺中東勢新丁粄節-文宣暨會場佈置委託專業服務勞務採購案</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>869500</v>
+        <v>1750000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2382,21 +2384,21 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>11605</t>
+          <t>1151102</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>頒獎典禮</t>
+          <t>文宣</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
@@ -2405,7 +2407,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
@@ -2417,25 +2419,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>臺中市政府數位發展局</t>
+          <t>國家人權博物館</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>台中通特店消費推廣暨抽獎活動案</t>
+          <t>「解嚴40週年國際論壇暨紀念專書籌劃」委託專業服務案</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>950000</v>
+        <v>2200000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2445,21 +2447,21 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>115B-10</t>
+          <t>11590Z</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>活動、推廣</t>
+          <t>國際論壇、論壇</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
@@ -2480,35 +2482,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>桃園市政府客家事務局</t>
+          <t>南投縣政府</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>「桃園市客家文化館開館系列活動」勞務採購案</t>
+          <t>「2026南投花卉嘉年華－草屯展區系列活動」勞務採購案</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>5500000</v>
+        <v>1000000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>115-021</t>
+          <t>1150602018G</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2518,11 +2520,11 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>系列活動</t>
+          <t>嘉年華、系列活動</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
@@ -2543,25 +2545,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>嘉義市政府</t>
+          <t>臺南市政府農業局</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>嘉義市政府116年家庭暴力暨性侵害防治中心宣導行銷計畫</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>1800000</v>
-      </c>
+          <t>日本地區臺南市農漁產推廣暨行銷活動策畫與執行委託專業服務案</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2571,21 +2571,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>115266</t>
+          <t>115AGR080</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>宣導、行銷</t>
+          <t>活動、行銷、推廣</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
@@ -2606,20 +2606,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>國家科學及技術委員會南部科學園區管理局</t>
+          <t>桃園市政府環境管理處</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>國家科學及技術委員會116年度科學園區滿意度調查計畫</t>
+          <t>115年度職業安全衛生業務標竿學習宣導活動計畫</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>1236708</v>
+        <v>1300000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2634,21 +2634,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>115660D01151</t>
+          <t>1150036916</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>政策溝通</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>滿意度調查</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
@@ -2669,20 +2669,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>農業部林業及自然保育署阿里山林業鐵路及文化資產管理處</t>
+          <t>南投縣政府社會及勞動局</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>116-117年「阿里山林鐵行動學校」跨館際展覽委託專業服務案</t>
+          <t>南投縣115年度國際身心障礙者日宣導活動</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>2800000</v>
+        <v>2500000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2697,21 +2697,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>116-EDU-001</t>
+          <t>115-10-10-005-E</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>展覽</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
@@ -2732,16 +2732,16 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>新北市政府觀光旅遊局</t>
+          <t>財團法人蘭陽農業發展基金會</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>115年新北市平日住宿及生日券獎助活動專案管理委託專業服務案</t>
+          <t>2027宜蘭綠色博覽會－海洋館委託專業服務案</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>700000</v>
+        <v>7000000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2760,21 +2760,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1152038719</t>
+          <t>115101305</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>博覽會</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
@@ -2795,25 +2795,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>中華郵政股份有限公司</t>
+          <t>財團法人蘭陽農業發展基金會</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>「羊來了-生肖郵票特展」策、布展及開幕活動委託服務</t>
+          <t>2027宜蘭綠色博覽會－森林館委託專業服務案</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>1480000</v>
+        <v>3950000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2823,21 +2823,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>115-3-167</t>
+          <t>115101301</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>博覽會</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
@@ -2853,30 +2853,30 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>桃園市政府藝文設施管理中心</t>
+          <t>雲林縣政府</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>「2027桃園鐵玫瑰藝術節活動執行統籌及行銷」委託專業服務採購案</t>
+          <t>「2026雲林文創聯合徵選暨雲林設計獎」頒獎典禮委託規劃執行案</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>9000000</v>
+        <v>500000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2886,21 +2886,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>115AFMC-017</t>
+          <t>1152H10116</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>活動執行、藝術節、行銷</t>
+          <t>頒獎典禮</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
@@ -2909,32 +2909,32 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>屏東縣獅子鄉公所</t>
+          <t>臺北市教師研習中心</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>屏東縣獅子鄉115年度慶祝重陽節聯合表揚暨族語文化推廣與文化健康站成果展活動勞務採購案</t>
+          <t>116年度優質學校頒獎典禮、杏壇芬芳獎表揚典禮、臺北教育111標竿學校頒獎典禮採購案</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>1162700</v>
+        <v>869500</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2944,26 +2944,26 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1151001AA</t>
+          <t>11605</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>成果展、活動、推廣</t>
+          <t>頒獎典禮</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
@@ -2972,37 +2972,37 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>勞動部勞動力發展署雲嘉南分署</t>
+          <t>臺中市政府數位發展局</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>116年度社群平台整合行銷委託計畫</t>
+          <t>台中通特店消費推廣暨抽獎活動案</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>2000000</v>
+        <v>950000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3012,21 +3012,21 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>yctrb1150129</t>
+          <t>115B-10</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>整合行銷、社群平台</t>
+          <t>活動、推廣</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
@@ -3035,61 +3035,61 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>內政部</t>
+          <t>桃園市政府客家事務局</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>116年第84屆兵役節慶祝大會暨頒獎典禮委外服務案</t>
+          <t>「桃園市客家文化館開館系列活動」勞務採購案</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>1230000</v>
+        <v>5500000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>115YJ-ST15</t>
+          <t>115-021</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>國際會議論壇/活動執行</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>大會、頒獎典禮</t>
+          <t>系列活動</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
@@ -3098,32 +3098,32 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>桃園市八德區公所</t>
+          <t>嘉義市政府</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>116年度桃園市元旦升旗典禮活動規劃與執行</t>
+          <t>嘉義市政府116年家庭暴力暨性侵害防治中心宣導行銷計畫</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>1600000</v>
+        <v>1800000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3138,21 +3138,21 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>BB1151015</t>
+          <t>115266</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>活動規劃、典禮</t>
+          <t>宣導、行銷</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
@@ -3161,32 +3161,32 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>國立臺中教育大學</t>
+          <t>國家科學及技術委員會南部科學園區管理局</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>數位內容充實與推廣總計畫成果紀錄影片製作採購案</t>
+          <t>國家科學及技術委員會116年度科學園區滿意度調查計畫</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>465000</v>
+        <v>1236708</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3201,21 +3201,21 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>115-C063</t>
+          <t>115660D01151</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>政策溝通</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>影片製作、推廣</t>
+          <t>滿意度調查</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
@@ -3224,32 +3224,32 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>文化部</t>
+          <t>農業部林業及自然保育署阿里山林業鐵路及文化資產管理處</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>文化部「蒙藏文化情境展示及體驗活動」展場設計製作布卸展及活動執行藝文採購案</t>
+          <t>116-117年「阿里山林鐵行動學校」跨館際展覽委託專業服務案</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>3350000</v>
+        <v>2800000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>11510159</t>
+          <t>116-EDU-001</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3274,11 +3274,11 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>展覽</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
@@ -3287,32 +3287,32 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>國立雲林科技大學</t>
+          <t>新北市政府觀光旅遊局</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026研發成果展場地佈置案</t>
+          <t>115年新北市平日住宿及生日券獎助活動專案管理委託專業服務案</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>840000</v>
+        <v>700000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>HTL115040</t>
+          <t>1152038719</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3337,11 +3337,11 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>成果展</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
@@ -3350,32 +3350,32 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>桃園市政府觀光旅遊局</t>
+          <t>中華郵政股份有限公司</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>116年桃園觀光旅遊局輿情蒐集及通報服務勞務採購案</t>
+          <t>「羊來了-生肖郵票特展」策、布展及開幕活動委託服務</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>247008</v>
+        <v>1480000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3390,21 +3390,21 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1151015-AA1</t>
+          <t>115-3-167</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>政策溝通</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>輿情</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
@@ -3425,16 +3425,16 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>臺中市立圖書館</t>
+          <t>桃園市政府藝文設施管理中心</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026臺中市立圖書館羅布森圖書館展覽委託專業服務採購案</t>
+          <t>「2027桃園鐵玫瑰藝術節活動執行統籌及行銷」委託專業服務採購案</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>1120000</v>
+        <v>9000000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -3443,31 +3443,31 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>115058</t>
+          <t>115AFMC-017</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>展覽</t>
+          <t>活動執行、藝術節、行銷</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
@@ -3488,20 +3488,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>屏東縣獅子鄉公所</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>115年客家記憶共創計畫-客家文化中心古契約展覽策劃執行</t>
+          <t>屏東縣獅子鄉115年度慶祝重陽節聯合表揚暨族語文化推廣與文化健康站成果展活動勞務採購案</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>850000</v>
+        <v>1162700</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3511,26 +3511,26 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>A132-1151015-1</t>
+          <t>1151001AA</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>展覽</t>
+          <t>成果展、活動、推廣</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
@@ -3546,30 +3546,30 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>廣亞學校財團法人育達科技大學</t>
+          <t>勞動部勞動力發展署雲嘉南分署</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>研究發展處創新創業輔導暨育成中心115年青年創業工作坊專案管理計畫青年遴選活動頒獎典禮暨成果展評選採購</t>
+          <t>116年度社群平台整合行銷委託計畫</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>350000</v>
+        <v>2000000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3579,21 +3579,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>115J-04</t>
+          <t>yctrb1150129</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>頒獎典禮、成果展、活動、工作坊</t>
+          <t>整合行銷、社群平台</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
@@ -3602,28 +3602,28 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>苗栗縣政府衛生局</t>
+          <t>內政部</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>115年衛生教育之媒體廣告行銷推廣</t>
+          <t>116年第84屆兵役節慶祝大會暨頒獎典禮委外服務案</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>770000</v>
+        <v>1230000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -3637,26 +3637,26 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>11535</t>
+          <t>115YJ-ST15</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>國際會議論壇/活動執行</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>行銷推廣、廣告、媒體</t>
+          <t>大會、頒獎典禮</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
@@ -3665,32 +3665,32 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>新竹市政府</t>
+          <t>桃園市八德區公所</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>116年新竹市政府城市行銷處社群網站管理</t>
+          <t>116年度桃園市元旦升旗典禮活動規劃與執行</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>1900000</v>
+        <v>1600000</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3705,21 +3705,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1150300</t>
+          <t>BB1151015</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>城市行銷、社群網站</t>
+          <t>活動規劃、典禮</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
@@ -3728,28 +3728,28 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>高雄市政府地政局</t>
+          <t>國立臺中教育大學</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>115年度不動產防詐暨交易安全宣導活動委外服務案</t>
+          <t>數位內容充實與推廣總計畫成果紀錄影片製作採購案</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>400000</v>
+        <v>465000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -3768,17 +3768,17 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>115019</t>
+          <t>115-C063</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>影片製作、推廣</t>
         </is>
       </c>
       <c r="K53" t="n">
@@ -3791,32 +3791,32 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>桃園市政府環境保護局</t>
+          <t>文化部</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>116年社群網路環境教育推廣維運計畫</t>
+          <t>文化部「蒙藏文化情境展示及體驗活動」展場設計製作布卸展及活動執行藝文採購案</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>3800000</v>
+        <v>3350000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3831,17 +3831,17 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1150085608</t>
+          <t>11510159</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>推廣、社群</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="K54" t="n">
@@ -3854,32 +3854,32 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>嘉義縣表演藝術中心</t>
+          <t>國立雲林科技大學</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>嘉義縣表演藝術中心115年表演節目整合傳播委託專業服務案</t>
+          <t>2026研發成果展場地佈置案</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>800000</v>
+        <v>840000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3894,17 +3894,17 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1150002654</t>
+          <t>HTL115040</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>整合傳播</t>
+          <t>成果展</t>
         </is>
       </c>
       <c r="K55" t="n">
@@ -3917,32 +3917,32 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>南投縣水里鄉公所</t>
+          <t>桃園市政府觀光旅遊局</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>「2026水里觀光行銷暨農特產品推廣系列活動—煙火設計及施放勞務採購案」</t>
+          <t>116年桃園觀光旅遊局輿情蒐集及通報服務勞務採購案</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>1000000</v>
+        <v>247008</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3957,21 +3957,21 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>115SHTS07</t>
+          <t>1151015-AA1</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>政策溝通</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>系列活動、觀光行銷、推廣</t>
+          <t>輿情</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
@@ -3980,32 +3980,32 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>國立臺灣大學</t>
+          <t>臺中市立圖書館</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2027年臺大杜鵑花節學系博覽會場佈</t>
+          <t>2026臺中市立圖書館羅布森圖書館展覽委託專業服務採購案</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>1250000</v>
+        <v>1120000</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4020,21 +4020,21 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1150963</t>
+          <t>115058</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>博覽會</t>
+          <t>展覽</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
@@ -4043,32 +4043,32 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>高雄市政府運動發展局</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>企業22年甲級排球聯賽高雄台電女子排球隊主場賽事行銷活動案</t>
+          <t>115年客家記憶共創計畫-客家文化中心古契約展覽策劃執行</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>590000</v>
+        <v>850000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4083,21 +4083,21 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>115-B-76</t>
+          <t>A132-1151015-1</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>活動、行銷</t>
+          <t>展覽</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
@@ -4106,37 +4106,37 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>廣亞學校財團法人育達科技大學</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>115年度管路灌溉成果推廣活動</t>
+          <t>研究發展處創新創業輔導暨育成中心115年青年創業工作坊專案管理計畫青年遴選活動頒獎典禮暨成果展評選採購</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>4000000</v>
+        <v>350000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4146,21 +4146,21 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>TY115B030</t>
+          <t>115J-04</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>活動、推廣</t>
+          <t>頒獎典禮、成果展、活動、工作坊</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
@@ -4176,54 +4176,54 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>臺北市政府工務局</t>
+          <t>苗栗縣政府衛生局</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>116年全國大專院校運動會開閉幕典禮活動</t>
+          <t>115年衛生教育之媒體廣告行銷推廣</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>10000000</v>
+        <v>770000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1150826S0096</t>
+          <t>11535</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>活動、典禮</t>
+          <t>行銷推廣、廣告、媒體</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
@@ -4239,30 +4239,30 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>臺中市政府環境保護局</t>
+          <t>新竹市政府</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>115年度環保英雄歲末嘉年華活動採購案</t>
+          <t>116年新竹市政府城市行銷處社群網站管理</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>1105000</v>
+        <v>1900000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4272,21 +4272,21 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>N1151013101</t>
+          <t>1150300</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>嘉年華</t>
+          <t>城市行銷、社群網站</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
@@ -4302,30 +4302,30 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>新北市政府環境保護局</t>
+          <t>高雄市政府地政局</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>116年度資源回收推動及形象改造計畫</t>
+          <t>115年度不動產防詐暨交易安全宣導活動委外服務案</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>9670000</v>
+        <v>400000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4335,21 +4335,21 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>115-177</t>
+          <t>115019</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>形象改造</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
@@ -4365,25 +4365,25 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>原住民族委員會原住民族文化發展中心</t>
+          <t>桃園市政府環境保護局</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>116年公益彩券回饋金計畫-文化觀光行銷專業人才勞務採購案</t>
+          <t>116年社群網路環境教育推廣維運計畫</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>4681825</v>
+        <v>3800000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>1150006860</t>
+          <t>1150085608</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>觀光行銷</t>
+          <t>推廣、社群</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -4428,25 +4428,25 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>勞動部</t>
+          <t>嘉義縣表演藝術中心</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>115年度「勞工自願提繳退休金影片製作案」</t>
+          <t>嘉義縣表演藝術中心115年表演節目整合傳播委託專業服務案</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>997920</v>
+        <v>800000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>03-11509091</t>
+          <t>1150002654</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>影片製作</t>
+          <t>整合傳播</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>桃園市政府捷運工程局</t>
+          <t>南投縣水里鄉公所</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>桃園市八德區德和路一段第2階段通車活動委託服務案</t>
+          <t>「2026水里觀光行銷暨農特產品推廣系列活動—煙火設計及施放勞務採購案」</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4519,26 +4519,26 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1151006</t>
+          <t>115SHTS07</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>系列活動、觀光行銷、推廣</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
@@ -4554,30 +4554,30 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>中華郵政股份有限公司</t>
+          <t>國立臺灣大學</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>115年度郵政形象廣告電視託播</t>
+          <t>2027年臺大杜鵑花節學系博覽會場佈</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>6000000</v>
+        <v>1250000</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>公開招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4587,21 +4587,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>115-5-294</t>
+          <t>1150963</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>電視託播、形象廣告</t>
+          <t>博覽會</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
@@ -4617,30 +4617,30 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>臺銀人壽保險股份有限公司</t>
+          <t>高雄市政府運動發展局</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>115年壽險行銷研討會-理財激勵專案</t>
+          <t>企業22年甲級排球聯賽高雄台電女子排球隊主場賽事行銷活動案</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>8330000</v>
+        <v>590000</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4650,21 +4650,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>115-005-106-CL-1-798</t>
+          <t>115-B-76</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>研討會</t>
+          <t>活動、行銷</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
@@ -4680,28 +4680,30 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>國立臺南大學</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>幼兒美感教育社群與國際交流影音紀錄</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr"/>
+          <t>115年度管路灌溉成果推廣活動</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>4000000</v>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4711,21 +4713,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1151065-TL</t>
+          <t>TY115B030</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>國際會議論壇/宣導行銷</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>國際交流、社群</t>
+          <t>活動、推廣</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
@@ -4741,40 +4743,40 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>臺東縣鹿野鄉公所</t>
+          <t>臺北市政府工務局</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026鹿野馬拉松系列活動賽事勞務採購案</t>
+          <t>116年全國大專院校運動會開閉幕典禮活動</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>1460000</v>
+        <v>10000000</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1150929</t>
+          <t>1150826S0096</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4784,7 +4786,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>系列活動</t>
+          <t>活動、典禮</t>
         </is>
       </c>
       <c r="K69" t="n">
@@ -4804,25 +4806,25 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>臺中市大里區公所</t>
+          <t>臺中市政府環境保護局</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>115年大里區運動會暨里鄰長健行活動規劃執行委託專業服務採購</t>
+          <t>115年度環保英雄歲末嘉年華活動採購案</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>400000</v>
+        <v>1105000</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4837,7 +4839,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>115dali032</t>
+          <t>N1151013101</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4847,7 +4849,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>活動規劃</t>
+          <t>嘉年華</t>
         </is>
       </c>
       <c r="K70" t="n">
@@ -4867,30 +4869,30 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>桃園市復興區公所</t>
+          <t>新北市政府環境保護局</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>桃園市復興區115年度甜柿推廣活動好柿發聲勞務採購案</t>
+          <t>116年度資源回收推動及形象改造計畫</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>766500</v>
+        <v>9670000</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4900,17 +4902,17 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>115D52</t>
+          <t>115-177</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>活動、推廣</t>
+          <t>形象改造</t>
         </is>
       </c>
       <c r="K71" t="n">
@@ -4930,30 +4932,30 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>南投縣政府</t>
+          <t>原住民族委員會原住民族文化發展中心</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>115年度南投拍片好所在影視音協拍多元媒體宣傳採購案</t>
+          <t>116年公益彩券回饋金計畫-文化觀光行銷專業人才勞務採購案</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>1100000</v>
+        <v>4681825</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4963,7 +4965,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1150707005G</t>
+          <t>1150006860</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4973,7 +4975,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>媒體宣傳</t>
+          <t>觀光行銷</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -4993,54 +4995,54 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>農業部林業及自然保育署阿里山林業鐵路及文化資產管理處</t>
+          <t>勞動部</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>阿里山林鐵服務中心小葉子館之展覽、賣店、服務設施規劃暨製作案</t>
+          <t>115年度「勞工自願提繳退休金影片製作案」</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>2500000</v>
+        <v>997920</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>115-ALI-001</t>
+          <t>03-11509091</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>展覽</t>
+          <t>影片製作</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
@@ -5056,21 +5058,21 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>苗栗縣政府</t>
+          <t>桃園市政府捷運工程局</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>苗栗縣政府115年度短影音攝製暨電視宣傳委託專業服務案</t>
+          <t>桃園市八德區德和路一段第2階段通車活動委託服務案</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>650000</v>
+        <v>1000000</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -5084,22 +5086,22 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>115147f</t>
+          <t>1151006</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>宣傳</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K74" t="n">
@@ -5119,30 +5121,30 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>花蓮縣豐濱鄉公所</t>
+          <t>中華郵政股份有限公司</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>115年「點亮豐濱！族語詩歌高聲唱耶誕嘉年華暨文化健康站成果展」勞務採購案</t>
+          <t>115年度郵政形象廣告電視託播</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>1100000</v>
+        <v>6000000</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>公開招標公告</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5152,17 +5154,17 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>FB1151218</t>
+          <t>115-5-294</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>嘉年華、成果展</t>
+          <t>電視託播、形象廣告</t>
         </is>
       </c>
       <c r="K75" t="n">
@@ -5182,25 +5184,25 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>臺中市政府研究發展考核委員會</t>
+          <t>臺銀人壽保險股份有限公司</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>「115年度臺中市經濟發展與城市行銷推廣案」委託專業服務案</t>
+          <t>115年壽險行銷研討會-理財激勵專案</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>2520000</v>
+        <v>8330000</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5215,21 +5217,21 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>115RCP16</t>
+          <t>115-005-106-CL-1-798</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>行銷推廣、城市行銷</t>
+          <t>研討會</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
@@ -5245,25 +5247,23 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>高雄市政府經濟發展局</t>
+          <t>國立臺南大學</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>「2027高雄過好年聯合記者會」委託專業服務案</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="n">
-        <v>500000</v>
-      </c>
+          <t>幼兒美感教育社群與國際交流影音紀錄</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5278,21 +5278,21 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>115090</t>
+          <t>1151065-TL</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>國際會議論壇/宣導行銷</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>記者會</t>
+          <t>國際交流、社群</t>
         </is>
       </c>
       <c r="K77" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
@@ -5308,25 +5308,25 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>內政部</t>
+          <t>臺東縣鹿野鄉公所</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>115年度合作社制度宣導短片託播案</t>
+          <t>2026鹿野馬拉松系列活動賽事勞務採購案</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>800000</v>
+        <v>1460000</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5336,22 +5336,22 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>115HT-NH090806</t>
+          <t>1150929</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>宣導短片</t>
+          <t>系列活動</t>
         </is>
       </c>
       <c r="K78" t="n">
@@ -5371,25 +5371,25 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>花蓮縣議會</t>
+          <t>臺中市大里區公所</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>花蓮縣議會「第21屆議員宣誓就職典禮暨正副議長選舉」委託專業服務案</t>
+          <t>115年大里區運動會暨里鄰長健行活動規劃執行委託專業服務採購</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>360000</v>
+        <v>400000</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>115GA31</t>
+          <t>115dali032</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5414,11 +5414,11 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>典禮</t>
+          <t>活動規劃</t>
         </is>
       </c>
       <c r="K79" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
@@ -5434,30 +5434,30 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>南投縣水里鄉公所</t>
+          <t>桃園市復興區公所</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>「2026水里觀光行銷暨農特產推廣系列活動」勞務採購案</t>
+          <t>桃園市復興區115年度甜柿推廣活動好柿發聲勞務採購案</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>4300000</v>
+        <v>766500</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>115SHTS06</t>
+          <t>115D52</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5477,11 +5477,11 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>系列活動、觀光行銷、推廣</t>
+          <t>活動、推廣</t>
         </is>
       </c>
       <c r="K80" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
@@ -5497,25 +5497,25 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>花蓮縣政府</t>
+          <t>南投縣政府</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>115年花蓮縣長青大學結業典禮暨成果展活動</t>
+          <t>115年度南投拍片好所在影視音協拍多元媒體宣傳採購案</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>1150000</v>
+        <v>1100000</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5530,21 +5530,21 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>SC1150020901</t>
+          <t>1150707005G</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>成果展、活動、典禮</t>
+          <t>媒體宣傳</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
@@ -5560,40 +5560,40 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>臺南市政府經濟發展局</t>
+          <t>農業部林業及自然保育署阿里山林業鐵路及文化資產管理處</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>「116年永康迎春嘉年華」活動規劃執行服務</t>
+          <t>阿里山林鐵服務中心小葉子館之展覽、賣店、服務設施規劃暨製作案</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>600000</v>
+        <v>2500000</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>115ECON71S1</t>
+          <t>115-ALI-001</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5603,11 +5603,11 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>嘉年華、活動規劃</t>
+          <t>展覽</t>
         </is>
       </c>
       <c r="K82" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
@@ -5623,30 +5623,30 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>臺北表演藝術中心</t>
+          <t>苗栗縣政府</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>第三屆臺北戲劇獎頒獎典禮暨系列活動製作執行勞務採購案</t>
+          <t>苗栗縣政府115年度短影音攝製暨電視宣傳委託專業服務案</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>15000000</v>
+        <v>650000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5656,21 +5656,21 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>TPACRD1150141</t>
+          <t>115147f</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>頒獎典禮、系列活動</t>
+          <t>宣傳</t>
         </is>
       </c>
       <c r="K83" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
@@ -5686,25 +5686,25 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>屏東縣獅子鄉公所</t>
+          <t>花蓮縣豐濱鄉公所</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>屏東縣獅子鄉115年度慶祝重陽節聯合表揚暨族語文化推廣與文化健康站成果展活動勞務採購案</t>
+          <t>115年「點亮豐濱！族語詩歌高聲唱耶誕嘉年華暨文化健康站成果展」勞務採購案</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>1162700</v>
+        <v>1100000</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5719,17 +5719,17 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>1151001AA</t>
+          <t>FB1151218</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>成果展、活動、推廣</t>
+          <t>嘉年華、成果展</t>
         </is>
       </c>
       <c r="K84" t="n">
@@ -5749,30 +5749,30 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>宜蘭縣政府</t>
+          <t>臺中市政府研究發展考核委員會</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>「宜蘭縣115年國際移民嘉年華」活動規劃執行委託案</t>
+          <t>「115年度臺中市經濟發展與城市行銷推廣案」委託專業服務案</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>400000</v>
+        <v>2520000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5782,17 +5782,17 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>CVSL115019</t>
+          <t>115RCP16</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>嘉年華、活動規劃</t>
+          <t>行銷推廣、城市行銷</t>
         </is>
       </c>
       <c r="K85" t="n">
@@ -5812,25 +5812,25 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>財政部高雄國稅局</t>
+          <t>高雄市政府經濟發展局</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>115年度結合統一發票推行暨「來稅局找碴-觀察力培養計畫」租稅宣導活動委外服務案</t>
+          <t>「2027高雄過好年聯合記者會」委託專業服務案</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>445000</v>
+        <v>500000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5845,21 +5845,21 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>1150042</t>
+          <t>115090</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>記者會</t>
         </is>
       </c>
       <c r="K86" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
@@ -5875,21 +5875,21 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>國立臺中教育大學</t>
+          <t>內政部</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>115年原住民族教育論壇暨原住民族教育資源中心成果交流會</t>
+          <t>115年度合作社制度宣導短片託播案</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>1450000</v>
+        <v>800000</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -5903,26 +5903,26 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>115-C062</t>
+          <t>115HT-NH090806</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>論壇</t>
+          <t>宣導短片</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L87" s="3" t="inlineStr">
         <is>
@@ -5938,25 +5938,25 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>衛生福利部疾病管制署</t>
+          <t>花蓮縣議會</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>「115年度防疫績優獎頒獎典禮專業服務」採購案</t>
+          <t>花蓮縣議會「第21屆議員宣誓就職典禮暨正副議長選舉」委託專業服務案</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>950000</v>
+        <v>360000</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>LA115028</t>
+          <t>115GA31</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5981,11 +5981,11 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>頒獎典禮</t>
+          <t>典禮</t>
         </is>
       </c>
       <c r="K88" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
@@ -6006,25 +6006,25 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>花蓮縣政府</t>
+          <t>南投縣水里鄉公所</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>115年花蓮縣精品咖啡行銷推廣計畫</t>
+          <t>「2026水里觀光行銷暨農特產推廣系列活動」勞務採購案</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>1100000</v>
+        <v>4300000</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6034,21 +6034,21 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>AG1150018061</t>
+          <t>115SHTS06</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>行銷推廣</t>
+          <t>系列活動、觀光行銷、推廣</t>
         </is>
       </c>
       <c r="K89" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="L89" s="3" t="inlineStr">
         <is>
@@ -6069,25 +6069,25 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>社團法人花蓮縣基督教會花蓮靈糧堂宣教協會</t>
+          <t>花蓮縣政府</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026花蓮幸福聖誕城行銷宣傳及城市聯合宣傳規劃案</t>
+          <t>115年花蓮縣長青大學結業典禮暨成果展活動</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>6789600</v>
+        <v>1150000</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6097,21 +6097,21 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-2HLLC</t>
+          <t>SC1150020901</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>行銷宣傳</t>
+          <t>成果展、活動、典禮</t>
         </is>
       </c>
       <c r="K90" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
@@ -6132,25 +6132,25 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>社團法人花蓮縣基督教會花蓮靈糧堂宣教協會</t>
+          <t>臺南市政府經濟發展局</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026花蓮幸福聖誕城活動執行案</t>
+          <t>「116年永康迎春嘉年華」活動規劃執行服務</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>9950000</v>
+        <v>600000</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-1HLLC</t>
+          <t>115ECON71S1</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6170,11 +6170,11 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>嘉年華、活動規劃</t>
         </is>
       </c>
       <c r="K91" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L91" s="3" t="inlineStr">
         <is>
@@ -6195,25 +6195,25 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>桃園市平鎮區公所</t>
+          <t>臺北表演藝術中心</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>116年桃園市平鎮區元旦升旗典禮活動</t>
+          <t>第三屆臺北戲劇獎頒獎典禮暨系列活動製作執行勞務採購案</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>450000</v>
+        <v>15000000</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1151005A01</t>
+          <t>TPACRD1150141</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6233,11 +6233,11 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>活動、典禮</t>
+          <t>頒獎典禮、系列活動</t>
         </is>
       </c>
       <c r="K92" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
@@ -6258,20 +6258,20 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>彰化縣田中鎮公所</t>
+          <t>屏東縣獅子鄉公所</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026田中藝術節–愛閱田中・藝起嗨劇場委託專業服務採購案</t>
+          <t>屏東縣獅子鄉115年度慶祝重陽節聯合表揚暨族語文化推廣與文化健康站成果展活動勞務採購案</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>700000</v>
+        <v>1162700</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6281,26 +6281,26 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>115-081</t>
+          <t>1151001AA</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>藝術節</t>
+          <t>成果展、活動、推廣</t>
         </is>
       </c>
       <c r="K93" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L93" s="3" t="inlineStr">
         <is>
@@ -6321,16 +6321,16 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>宜蘭縣政府</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>116年屏東縣政府社會處網路媒體行銷維運案</t>
+          <t>「宜蘭縣115年國際移民嘉年華」活動規劃執行委託案</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>2000000</v>
+        <v>400000</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -6349,21 +6349,21 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>A058-1151007-2</t>
+          <t>CVSL115019</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>媒體行銷</t>
+          <t>嘉年華、活動規劃</t>
         </is>
       </c>
       <c r="K94" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
@@ -6384,16 +6384,16 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>南投縣政府</t>
+          <t>財政部高雄國稅局</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>115年縣政成果及重大活動影音攝製行銷案</t>
+          <t>115年度結合統一發票推行暨「來稅局找碴-觀察力培養計畫」租稅宣導活動委外服務案</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>1400000</v>
+        <v>445000</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>115-07-06-011E</t>
+          <t>1150042</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6422,11 +6422,11 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>活動、行銷</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K95" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L95" s="3" t="inlineStr">
         <is>
@@ -6447,20 +6447,20 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>苗栗縣政府</t>
+          <t>國立臺中教育大學</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>「2027台灣燈會在苗栗」廣播錄製暨執行委託專業服務案</t>
+          <t>115年原住民族教育論壇暨原住民族教育資源中心成果交流會</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>500000</v>
+        <v>1450000</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -6475,21 +6475,21 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>115141f</t>
+          <t>115-C062</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>燈會</t>
+          <t>論壇</t>
         </is>
       </c>
       <c r="K96" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
@@ -6510,20 +6510,20 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>臺南市政府經濟發展局</t>
+          <t>衛生福利部疾病管制署</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>「2027新化年貨大街」活動委託服務案</t>
+          <t>「115年度防疫績優獎頒獎典禮專業服務」採購案</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1100000</v>
+        <v>950000</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -6538,7 +6538,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>115ECON72S1</t>
+          <t>LA115028</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6548,11 +6548,11 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>頒獎典禮</t>
         </is>
       </c>
       <c r="K97" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L97" s="3" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6578,11 +6578,11 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026花蓮星潮原聲系列活動規劃執行案</t>
+          <t>115年花蓮縣精品咖啡行銷推廣計畫</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>40000000</v>
+        <v>1100000</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -6601,21 +6601,21 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>AB1150007224</t>
+          <t>AG1150018061</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>系列活動、活動規劃</t>
+          <t>行銷推廣</t>
         </is>
       </c>
       <c r="K98" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L98" s="3" t="inlineStr">
         <is>
@@ -6631,30 +6631,30 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>南投縣政府</t>
+          <t>社團法人花蓮縣基督教會花蓮靈糧堂宣教協會</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>「2026南投花卉嘉年華－草屯展區系列活動」勞務採購案</t>
+          <t>2026花蓮幸福聖誕城行銷宣傳及城市聯合宣傳規劃案</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>1000000</v>
+        <v>6789600</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -6664,21 +6664,21 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>1150602018G</t>
+          <t>2026-2HLLC</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>嘉年華、系列活動</t>
+          <t>行銷宣傳</t>
         </is>
       </c>
       <c r="K99" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L99" s="3" t="inlineStr">
         <is>
@@ -6694,30 +6694,30 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>內政部</t>
+          <t>社團法人花蓮縣基督教會花蓮靈糧堂宣教協會</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>116年第84屆兵役節慶祝大會暨頒獎典禮委外服務案</t>
+          <t>2026花蓮幸福聖誕城活動執行案</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>1230000</v>
+        <v>9950000</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6727,21 +6727,21 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>115YJ-ST15</t>
+          <t>2026-1HLLC</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>國際會議論壇/活動執行</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>大會、頒獎典禮</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="K100" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
@@ -6757,25 +6757,25 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>國立臺灣美術館</t>
+          <t>桃園市平鎮區公所</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">國家珍藏作品之線上藝廊推廣影片製作採購案 </t>
+          <t>116年桃園市平鎮區元旦升旗典禮活動</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>600000</v>
+        <v>450000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6790,21 +6790,21 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>115118</t>
+          <t>1151005A01</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>影片製作、推廣</t>
+          <t>活動、典禮</t>
         </is>
       </c>
       <c r="K101" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L101" s="3" t="inlineStr">
         <is>
@@ -6820,40 +6820,40 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>苗栗縣苗栗市公所</t>
+          <t>彰化縣田中鎮公所</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>苗栗市2026冬迎璀璨歲末藝文嘉年華</t>
+          <t>2026田中藝術節–愛閱田中・藝起嗨劇場委託專業服務採購案</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>2440000</v>
+        <v>700000</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>C548</t>
+          <t>115-081</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>嘉年華</t>
+          <t>藝術節</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -6883,30 +6883,30 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>苗栗縣苗栗市公所</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>115年度苗栗市親子蘿蔔節活動執行委託專業服務採購案</t>
+          <t>116年屏東縣政府社會處網路媒體行銷維運案</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6916,17 +6916,17 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>B1600</t>
+          <t>A058-1151007-2</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>媒體行銷</t>
         </is>
       </c>
       <c r="K103" t="n">
@@ -6946,30 +6946,30 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>桃園市政府工務局</t>
+          <t>南投縣政府</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>115年桃園市食農教育執行成果展委託專業服務案</t>
+          <t>115年縣政成果及重大活動影音攝製行銷案</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>2000000</v>
+        <v>1400000</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6979,17 +6979,17 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>1151005-3</t>
+          <t>115-07-06-011E</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>成果展</t>
+          <t>活動、行銷</t>
         </is>
       </c>
       <c r="K104" t="n">
@@ -7009,25 +7009,25 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>新竹縣尖石鄉公所</t>
+          <t>苗栗縣政府</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>新竹縣尖石鄉115年尖石鄉鄉長盃第二屆傳統路跑嘉年華暨傳統擲矛、傳統狩獵活動勞務採購案</t>
+          <t>「2027台灣燈會在苗栗」廣播錄製暨執行委託專業服務案</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>950000</v>
+        <v>500000</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>1159226</t>
+          <t>115141f</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7052,11 +7052,11 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>嘉年華</t>
+          <t>燈會</t>
         </is>
       </c>
       <c r="K105" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L105" s="3" t="inlineStr">
         <is>
@@ -7072,30 +7072,30 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>嘉義縣文化觀光局</t>
+          <t>臺南市政府經濟發展局</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>「116年度嘉義縣觀光旅遊數位整合行銷」委託專業服務案</t>
+          <t>「2027新化年貨大街」活動委託服務案</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>2000000</v>
+        <v>1100000</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7105,21 +7105,21 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>1150011120</t>
+          <t>115ECON72S1</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>整合行銷</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K106" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L106" s="3" t="inlineStr">
         <is>
@@ -7140,49 +7140,49 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>台灣中油股份有限公司探採事業部</t>
+          <t>花蓮縣政府</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>碳封存監測資料彙整分析及社會溝通顧問服務</t>
+          <t>2026花蓮星潮原聲系列活動規劃執行案</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>1490000</v>
+        <v>40000000</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>BEA1500013</t>
+          <t>AB1150007224</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>政策溝通</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>社會溝通</t>
+          <t>系列活動、活動規劃</t>
         </is>
       </c>
       <c r="K107" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="L107" s="3" t="inlineStr">
         <is>
@@ -7203,20 +7203,20 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>中央選舉委員會</t>
+          <t>南投縣政府</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>115年地方公職人員選舉及公民投票選務滿意度民意調查採購案</t>
+          <t>「2026南投花卉嘉年華－草屯展區系列活動」勞務採購案</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -7231,21 +7231,21 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>1150909</t>
+          <t>1150602018G</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>政策溝通</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>民意調查</t>
+          <t>嘉年華、系列活動</t>
         </is>
       </c>
       <c r="K108" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="L108" s="3" t="inlineStr">
         <is>
@@ -7266,20 +7266,20 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>桃園市政府捷運工程局</t>
+          <t>內政部</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>桃園市八德區德和路一段第2階段通車活動委託服務案</t>
+          <t>116年第84屆兵役節慶祝大會暨頒獎典禮委外服務案</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>1000000</v>
+        <v>1230000</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -7294,21 +7294,21 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>1151006</t>
+          <t>115YJ-ST15</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>國際會議論壇/活動執行</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>大會、頒獎典禮</t>
         </is>
       </c>
       <c r="K109" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="L109" s="3" t="inlineStr">
         <is>
@@ -7324,30 +7324,30 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>國防部</t>
+          <t>國立臺灣美術館</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>國軍招募宣傳電視廣告託播</t>
+          <t xml:space="preserve">國家珍藏作品之線上藝廊推廣影片製作採購案 </t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>2000000</v>
+        <v>600000</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>公開招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>CC15003L050</t>
+          <t>115118</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7367,7 +7367,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>廣告託播、宣傳</t>
+          <t>影片製作、推廣</t>
         </is>
       </c>
       <c r="K110" t="n">
@@ -7387,25 +7387,25 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>衛生福利部社會及家庭署</t>
+          <t>苗栗縣苗栗市公所</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>116年度強化社會安全網績優人員及團體獎項品牌識別系統專業服務案</t>
+          <t>苗栗市2026冬迎璀璨歲末藝文嘉年華</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>2550000</v>
+        <v>2440000</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -7420,17 +7420,17 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>C116001</t>
+          <t>C548</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>品牌識別</t>
+          <t>嘉年華</t>
         </is>
       </c>
       <c r="K111" t="n">
@@ -7450,30 +7450,30 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>臺北市政府觀光傳播局</t>
+          <t>苗栗縣苗栗市公所</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>116年度臺北開齋節暨穆斯林友善城市推廣活動案</t>
+          <t>115年度苗栗市親子蘿蔔節活動執行委託專業服務採購案</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>4000000</v>
+        <v>1000000</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -7483,17 +7483,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>1150075</t>
+          <t>B1600</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>活動、推廣</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -7513,30 +7513,30 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>國立歷史博物館</t>
+          <t>桃園市政府工務局</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>常設展手語導覽影片製作案</t>
+          <t>115年桃園市食農教育執行成果展委託專業服務案</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>950000</v>
+        <v>2000000</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -7546,17 +7546,17 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>115046</t>
+          <t>1151005-3</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>影片製作</t>
+          <t>成果展</t>
         </is>
       </c>
       <c r="K113" t="n">
@@ -7576,30 +7576,30 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>內政部國土管理署</t>
+          <t>新竹縣尖石鄉公所</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>116年度住宅政策推廣影音及多媒體製作案</t>
+          <t>新竹縣尖石鄉115年尖石鄉鄉長盃第二屆傳統路跑嘉年華暨傳統擲矛、傳統狩獵活動勞務採購案</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>9950000</v>
+        <v>950000</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -7609,17 +7609,17 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>115A-066</t>
+          <t>1159226</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>推廣、媒體</t>
+          <t>嘉年華</t>
         </is>
       </c>
       <c r="K114" t="n">
@@ -7639,21 +7639,21 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>高雄市政府勞工局訓練就業中心</t>
+          <t>嘉義縣文化觀光局</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>「116年度鳳山、岡山就業服務站現場徵才活動」委託服務案</t>
+          <t>「116年度嘉義縣觀光旅遊數位整合行銷」委託專業服務案</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>2892100</v>
+        <v>2000000</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -7672,21 +7672,21 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>116F002</t>
+          <t>1150011120</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>整合行銷</t>
         </is>
       </c>
       <c r="K115" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L115" s="3" t="inlineStr">
         <is>
@@ -7702,21 +7702,21 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>新北市政府勞工局</t>
+          <t>台灣中油股份有限公司探採事業部</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>新北市政府116年度外國人文化與休閒活動計畫-越南、印尼活動委託專業服務採購案</t>
+          <t>碳封存監測資料彙整分析及社會溝通顧問服務</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>1300000</v>
+        <v>1490000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -7735,21 +7735,21 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>TPLAB115013</t>
+          <t>BEA1500013</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>政策溝通</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>社會溝通</t>
         </is>
       </c>
       <c r="K116" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L116" s="3" t="inlineStr">
         <is>
@@ -7765,21 +7765,21 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>臺中市石岡區公所</t>
+          <t>中央選舉委員會</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>115年石岡童樂會暨水資源宣導活動</t>
+          <t>115年地方公職人員選舉及公民投票選務滿意度民意調查採購案</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>800000</v>
+        <v>500000</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -7798,21 +7798,21 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>115SK20</t>
+          <t>1150909</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>政策溝通</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>民意調查</t>
         </is>
       </c>
       <c r="K117" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L117" s="3" t="inlineStr">
         <is>
@@ -7828,25 +7828,25 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>臺中市石岡區公所</t>
+          <t>桃園市政府捷運工程局</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026臺中市民野餐日（石岡區）暨觀光活化水資源宣導活動</t>
+          <t>桃園市八德區德和路一段第2階段通車活動委託服務案</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>920000</v>
+        <v>1000000</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -7861,21 +7861,21 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>115SK19</t>
+          <t>1151006</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K118" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L118" s="3" t="inlineStr">
         <is>
@@ -7891,30 +7891,30 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>新竹縣芎林鄉公所</t>
+          <t>國防部</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2027芎林路跑嘉年華活動計畫委託專業服務案</t>
+          <t>國軍招募宣傳電視廣告託播</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>2400000</v>
+        <v>2000000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開招標公告</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -7924,17 +7924,17 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>1160001P</t>
+          <t>CC15003L050</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>嘉年華、活動</t>
+          <t>廣告託播、宣傳</t>
         </is>
       </c>
       <c r="K119" t="n">
@@ -7954,25 +7954,25 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>海洋委員會</t>
+          <t>衛生福利部社會及家庭署</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>海洋博覽會整體規劃暨先期策略研析委託專業服務案</t>
+          <t>116年度強化社會安全網績優人員及團體獎項品牌識別系統專業服務案</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>3000000</v>
+        <v>2550000</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -7987,21 +7987,21 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>OAC115044</t>
+          <t>C116001</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>博覽會</t>
+          <t>品牌識別</t>
         </is>
       </c>
       <c r="K120" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L120" s="3" t="inlineStr">
         <is>
@@ -8017,25 +8017,25 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>花蓮縣政府</t>
+          <t>臺北市政府觀光傳播局</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>115年花蓮宜居城市行銷採購案(開口契約)</t>
+          <t>116年度臺北開齋節暨穆斯林友善城市推廣活動案</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>9450000</v>
+        <v>4000000</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -8050,17 +8050,17 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>SK1150005862</t>
+          <t>1150075</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>城市行銷</t>
+          <t>活動、推廣</t>
         </is>
       </c>
       <c r="K121" t="n">
@@ -8080,25 +8080,25 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>花蓮縣政府</t>
+          <t>國立歷史博物館</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>115年花蓮縣社區照顧關懷據點及社區長照站成果展</t>
+          <t>常設展手語導覽影片製作案</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>1250000</v>
+        <v>950000</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -8113,17 +8113,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>SC1150020073</t>
+          <t>115046</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>成果展</t>
+          <t>影片製作</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -8143,30 +8143,30 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>桃園市政府文化局</t>
+          <t>內政部國土管理署</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026桃園仙草花節系列活動-民歌演唱會委託專業服務案</t>
+          <t>116年度住宅政策推廣影音及多媒體製作案</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>500000</v>
+        <v>9950000</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -8176,17 +8176,17 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>TYC115-39</t>
+          <t>115A-066</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>系列活動</t>
+          <t>推廣、媒體</t>
         </is>
       </c>
       <c r="K123" t="n">
@@ -8206,21 +8206,21 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>宜蘭縣政府</t>
+          <t>高雄市政府勞工局訓練就業中心</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>宜蘭縣115年度原有住宅無障礙設施補助委託辦理推廣宣導評估案</t>
+          <t>「116年度鳳山、岡山就業服務站現場徵才活動」委託服務案</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>1210000</v>
+        <v>2892100</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -8239,21 +8239,21 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>CNSL115032</t>
+          <t>116F002</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>宣導、推廣</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K124" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L124" s="3" t="inlineStr">
         <is>
@@ -8269,40 +8269,40 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>財團法人嘉義市文化基金會</t>
+          <t>新北市政府勞工局</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026嘉義市管樂節晚會舞台暨表演節目規畫執行委託服務案</t>
+          <t>新北市政府116年度外國人文化與休閒活動計畫-越南、印尼活動委託專業服務採購案</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>15000000</v>
+        <v>1300000</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>115A001</t>
+          <t>TPLAB115013</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8312,7 +8312,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>晚會</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K125" t="n">
@@ -8337,25 +8337,25 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>新竹市政府</t>
+          <t>臺中市石岡區公所</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>「2026客家藝文活動」委託專業服務案</t>
+          <t>115年石岡童樂會暨水資源宣導活動</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>2400000</v>
+        <v>800000</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -8365,21 +8365,21 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>1150292</t>
+          <t>115SK20</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K126" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L126" s="3" t="inlineStr">
         <is>
@@ -8395,30 +8395,30 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>新北市政府觀光旅遊局</t>
+          <t>臺中市石岡區公所</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>116年度跨媒體整合傳播採購案</t>
+          <t>2026臺中市民野餐日（石岡區）暨觀光活化水資源宣導活動</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>7350000</v>
+        <v>920000</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -8428,21 +8428,21 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>1151911877</t>
+          <t>115SK19</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>整合傳播、跨媒體</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K127" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L127" s="3" t="inlineStr">
         <is>
@@ -8458,25 +8458,25 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>司法院</t>
+          <t>新竹縣芎林鄉公所</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>司法院115年司法博物館主題活動規劃執行採購案</t>
+          <t>2027芎林路跑嘉年華活動計畫委託專業服務案</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>3400000</v>
+        <v>2400000</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>1151400844</t>
+          <t>1160001P</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8501,11 +8501,11 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>活動規劃、主題活動</t>
+          <t>嘉年華、活動</t>
         </is>
       </c>
       <c r="K128" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L128" s="3" t="inlineStr">
         <is>
@@ -8521,54 +8521,54 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>彰化縣伸港鄉公所</t>
+          <t>海洋委員會</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2027年伸港飛揚-元旦升旗健行齊步走暨節能減碳宣導活動委託服務案</t>
+          <t>海洋博覽會整體規劃暨先期策略研析委託專業服務案</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>1152300</v>
+        <v>3000000</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>1152006</t>
+          <t>OAC115044</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>博覽會</t>
         </is>
       </c>
       <c r="K129" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L129" s="3" t="inlineStr">
         <is>
@@ -8584,30 +8584,30 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>臺東縣政府</t>
+          <t>花蓮縣政府</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>興隆國小--臺東縣115年度環境變遷與藍碳發展論壇暨體驗學習活動</t>
+          <t>115年花蓮宜居城市行銷採購案(開口契約)</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>420000</v>
+        <v>9450000</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -8617,21 +8617,21 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>115310130545</t>
+          <t>SK1150005862</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>論壇</t>
+          <t>城市行銷</t>
         </is>
       </c>
       <c r="K130" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L130" s="3" t="inlineStr">
         <is>
@@ -8647,30 +8647,30 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>桃園市政府文化局</t>
+          <t>花蓮縣政府</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026桃園社造博覽會規劃執行案</t>
+          <t>115年花蓮縣社區照顧關懷據點及社區長照站成果展</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>2000000</v>
+        <v>1250000</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -8680,21 +8680,21 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>1150276</t>
+          <t>SC1150020073</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>博覽會</t>
+          <t>成果展</t>
         </is>
       </c>
       <c r="K131" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L131" s="3" t="inlineStr">
         <is>
@@ -8710,25 +8710,25 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>新北市政府水利局</t>
+          <t>桃園市政府文化局</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>新北市治水、清水、親水水環境治理成果影片製作案</t>
+          <t>2026桃園仙草花節系列活動-民歌演唱會委託專業服務案</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>1200000</v>
+        <v>500000</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -8743,17 +8743,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>1150930A</t>
+          <t>TYC115-39</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>影片製作</t>
+          <t>系列活動</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -8773,30 +8773,30 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>彰化縣田中鎮公所</t>
+          <t>宜蘭縣政府</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026田中藝術節–愛閱田中・藝起嗨劇場委託專業服務採購案</t>
+          <t>宜蘭縣115年度原有住宅無障礙設施補助委託辦理推廣宣導評估案</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>700000</v>
+        <v>1210000</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -8806,17 +8806,17 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>115-081</t>
+          <t>CNSL115032</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>藝術節</t>
+          <t>宣導、推廣</t>
         </is>
       </c>
       <c r="K133" t="n">
@@ -8836,30 +8836,30 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>外交部領事事務局</t>
+          <t>財團法人嘉義市文化基金會</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>115年度推廣外交部領事事務局「LINE官方帳號」靜態貼圖廣告方案</t>
+          <t>2026嘉義市管樂節晚會舞台暨表演節目規畫執行委託服務案</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>630000</v>
+        <v>15000000</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -8869,21 +8869,21 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>T115027CB</t>
+          <t>115A001</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>廣告、推廣</t>
+          <t>晚會</t>
         </is>
       </c>
       <c r="K134" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L134" s="3" t="inlineStr">
         <is>
@@ -8899,68 +8899,635 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>新竹市政府</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>「2026客家藝文活動」委託專業服務案</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>1150292</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>活動執行</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>活動</t>
+        </is>
+      </c>
+      <c r="K135" t="n">
+        <v>4</v>
+      </c>
+      <c r="L135" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>新北市政府觀光旅遊局</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>116年度跨媒體整合傳播採購案</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>7350000</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>1151911877</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>宣導行銷</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>整合傳播、跨媒體</t>
+        </is>
+      </c>
+      <c r="K136" t="n">
+        <v>16</v>
+      </c>
+      <c r="L136" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>司法院</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>司法院115年司法博物館主題活動規劃執行採購案</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>1151400844</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>活動執行</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>活動規劃、主題活動</t>
+        </is>
+      </c>
+      <c r="K137" t="n">
+        <v>16</v>
+      </c>
+      <c r="L137" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>彰化縣伸港鄉公所</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2027年伸港飛揚-元旦升旗健行齊步走暨節能減碳宣導活動委託服務案</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>1152300</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>公開取得報價單或企劃書公告</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>1152006</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>活動執行/宣導行銷</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>活動、宣導活動</t>
+        </is>
+      </c>
+      <c r="K138" t="n">
+        <v>12</v>
+      </c>
+      <c r="L138" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>臺東縣政府</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>興隆國小--臺東縣115年度環境變遷與藍碳發展論壇暨體驗學習活動</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>420000</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>公開取得報價單或企劃書公告</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>115310130545</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>國際會議論壇</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>論壇</t>
+        </is>
+      </c>
+      <c r="K139" t="n">
+        <v>10</v>
+      </c>
+      <c r="L139" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>桃園市政府文化局</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2026桃園社造博覽會規劃執行案</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>1150276</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>國際會議論壇</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>博覽會</t>
+        </is>
+      </c>
+      <c r="K140" t="n">
+        <v>10</v>
+      </c>
+      <c r="L140" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>新北市政府水利局</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>新北市治水、清水、親水水環境治理成果影片製作案</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>公開取得報價單或企劃書公告</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>1150930A</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>宣導行銷</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>影片製作</t>
+        </is>
+      </c>
+      <c r="K141" t="n">
+        <v>8</v>
+      </c>
+      <c r="L141" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>彰化縣田中鎮公所</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2026田中藝術節–愛閱田中・藝起嗨劇場委託專業服務採購案</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>700000</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>公開取得報價單或企劃書公告</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>115-081</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>活動執行</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>藝術節</t>
+        </is>
+      </c>
+      <c r="K142" t="n">
+        <v>8</v>
+      </c>
+      <c r="L142" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>外交部領事事務局</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>115年度推廣外交部領事事務局「LINE官方帳號」靜態貼圖廣告方案</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>630000</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>公開取得報價單或企劃書公告</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>T115027CB</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>宣導行銷</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>廣告、推廣</t>
+        </is>
+      </c>
+      <c r="K143" t="n">
+        <v>8</v>
+      </c>
+      <c r="L143" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
         <is>
           <t>勞動部勞動力發展署桃竹苗分署</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="C144" t="inlineStr">
         <is>
           <t>116年機關整合行銷勞務採購案</t>
         </is>
       </c>
-      <c r="D135" s="2" t="n">
+      <c r="D144" s="2" t="n">
         <v>1330000</v>
       </c>
-      <c r="E135" t="inlineStr">
+      <c r="E144" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
+      <c r="F144" t="inlineStr">
         <is>
           <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
         <is>
           <t>116Y020</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
+      <c r="I144" t="inlineStr">
         <is>
           <t>宣導行銷</t>
         </is>
       </c>
-      <c r="J135" t="inlineStr">
+      <c r="J144" t="inlineStr">
         <is>
           <t>整合行銷</t>
         </is>
       </c>
-      <c r="K135" t="n">
+      <c r="K144" t="n">
         <v>8</v>
       </c>
-      <c r="L135" s="3" t="inlineStr">
-        <is>
-          <t>開啟</t>
-        </is>
-      </c>
-      <c r="M135" t="inlineStr">
+      <c r="L144" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
         <is>
           <t>2026-10-15 08:34</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M135"/>
+  <autoFilter ref="A1:M144"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -9096,6 +9663,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L133" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L134" r:id="rId133"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L144" r:id="rId143"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9145,13 +9721,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5485</v>
+        <v>6032</v>
       </c>
       <c r="C2" t="n">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>430326370</v>
+        <v>466633370</v>
       </c>
     </row>
   </sheetData>
@@ -9181,7 +9757,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>產生時間：2026-10-21 08:35　資料庫共 134 筆</t>
+          <t>產生時間：2026-10-22 08:39　資料庫共 143 筆</t>
         </is>
       </c>
     </row>

--- a/data/標案資料庫.xlsx
+++ b/data/標案資料庫.xlsx
@@ -11129,7 +11129,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6603</v>
+        <v>6604</v>
       </c>
       <c r="C2" t="n">
         <v>165</v>
@@ -11165,7 +11165,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>產生時間：2026-10-23 08:36　資料庫共 165 筆</t>
+          <t>產生時間：2026-10-24 08:35　資料庫共 165 筆</t>
         </is>
       </c>
     </row>

--- a/data/標案資料庫.xlsx
+++ b/data/標案資料庫.xlsx
@@ -11165,7 +11165,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>產生時間：2026-10-24 08:35　資料庫共 165 筆</t>
+          <t>產生時間：2026-10-25 08:17　資料庫共 165 筆</t>
         </is>
       </c>
     </row>

--- a/data/標案資料庫.xlsx
+++ b/data/標案資料庫.xlsx
@@ -11165,7 +11165,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>產生時間：2026-10-25 08:17　資料庫共 165 筆</t>
+          <t>產生時間：2026-10-26 08:15　資料庫共 165 筆</t>
         </is>
       </c>
     </row>

--- a/data/標案資料庫.xlsx
+++ b/data/標案資料庫.xlsx
@@ -12,7 +12,7 @@
     <sheet name="說明" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'標案資料庫'!$A$1:$M$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'標案資料庫'!$A$1:$M$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M166"/>
+  <dimension ref="A1:M169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -524,30 +524,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>臺中市沙鹿區公所</t>
+          <t>監察院</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026沙鹿嘉年華-農產好味樂享宴暨節能宣導活動委託服務案</t>
+          <t>監察院國家人權委員會「數位隱私與人權治理國際論壇」委託專業服務案</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1040000</v>
+        <v>2520000</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -557,17 +557,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>115-HU-49</t>
+          <t>BB1151001</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>嘉年華、活動、宣導活動</t>
+          <t>國際論壇、論壇</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,32 +580,32 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-23 08:36</t>
+          <t>2026-10-27 09:27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>苗栗縣竹南鎮公所</t>
+          <t>財團法人蘭陽農業發展基金會</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>115年竹南鎮觀光形象宣傳廣告託播</t>
+          <t>2027宜蘭綠色博覽會－能源館委託專業服務案</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>287000</v>
+        <v>1480000</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -620,21 +620,21 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1151016-2</t>
+          <t>115101401</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>廣告託播、宣傳、形象</t>
+          <t>博覽會</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -643,37 +643,37 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-23 08:36</t>
+          <t>2026-10-27 09:27</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>財政部國庫署</t>
+          <t>國家發展委員會</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AI紅利全民共享普發現金政策溝通暨媒體宣導服務案</t>
+          <t>臺灣省政資料館116年展覽推廣協同研究委託服務案</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>15940000</v>
+        <v>1710821</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開招標公告</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -683,21 +683,21 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NTA11522</t>
+          <t>ndc115046</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>宣導行銷/政策溝通</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>宣導、媒體、政策溝通</t>
+          <t>展覽、推廣</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-23 08:36</t>
+          <t>2026-10-27 09:27</t>
         </is>
       </c>
     </row>
@@ -718,25 +718,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>臺南市政府觀光旅遊局</t>
+          <t>臺中市沙鹿區公所</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>115-116年台灣觀光100亮點臺南行銷活動規劃案</t>
+          <t>2026沙鹿嘉年華-農產好味樂享宴暨節能宣導活動委託服務案</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2400000</v>
+        <v>1040000</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1151412569</t>
+          <t>115-HU-49</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -756,11 +756,11 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>活動規劃、行銷</t>
+          <t>嘉年華、活動、宣導活動</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -781,25 +781,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>臺中市和平區公所</t>
+          <t>苗栗縣竹南鎮公所</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026和平區觀光季．梨山谷關原風歲末迎新暨珍愛節電資源宣導活動</t>
+          <t>115年竹南鎮觀光形象宣傳廣告託播</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2200000</v>
+        <v>287000</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -809,21 +809,21 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>115H26</t>
+          <t>1151016-2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>廣告託播、宣傳、形象</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -844,20 +844,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>國立傳統藝術中心</t>
+          <t>財政部國庫署</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>116年度臺灣戲曲中心推廣活動宣傳品項設計及印刷派送勞務採購案</t>
+          <t>AI紅利全民共享普發現金政策溝通暨媒體宣導服務案</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1872250</v>
+        <v>15940000</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -872,21 +872,21 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1152229</t>
+          <t>NTA11522</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>宣導行銷/政策溝通</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>活動、宣傳、推廣</t>
+          <t>宣導、媒體、政策溝通</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -907,25 +907,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>高雄市政府文化局</t>
+          <t>臺南市政府觀光旅遊局</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>「2026高雄漾藝術博覽會展板組裝及展場木作施作」勞務採購案</t>
+          <t>115-116年台灣觀光100亮點臺南行銷活動規劃案</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1049560</v>
+        <v>2400000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -935,21 +935,21 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>115251</t>
+          <t>1151412569</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>博覽會</t>
+          <t>活動規劃、行銷</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -970,25 +970,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>國立臺灣師範大學</t>
+          <t>臺中市和平區公所</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2027第十二屆國際數理奧林匹亞發展研討會住宿、餐飲、會議場地及交通服務</t>
+          <t>2026和平區觀光季．梨山谷關原風歲末迎新暨珍愛節電資源宣導活動</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>650000</v>
+        <v>2200000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -998,21 +998,21 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>NU211510190599</t>
+          <t>115H26</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>研討會</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -1033,25 +1033,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>高雄市政府青年局</t>
+          <t>國立傳統藝術中心</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>「青年堤畔漫遊推廣活動」委託專業服務採購案</t>
+          <t>116年度臺灣戲曲中心推廣活動宣傳品項設計及印刷派送勞務採購案</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1450000</v>
+        <v>1872250</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>KYB115023</t>
+          <t>1152229</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1071,11 +1071,11 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>活動、推廣</t>
+          <t>活動、宣傳、推廣</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -1096,25 +1096,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>花蓮縣政府</t>
+          <t>高雄市政府文化局</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>116年度加強公務和諧連繫－農特產品、伴手禮及紀念品行銷推廣採購案(開口契約)</t>
+          <t>「2026高雄漾藝術博覽會展板組裝及展場木作施作」勞務採購案</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>4393000</v>
+        <v>1049560</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1124,21 +1124,21 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>SK1150006298</t>
+          <t>115251</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>行銷推廣</t>
+          <t>博覽會</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -1159,20 +1159,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>臺灣銀行股份有限公司</t>
+          <t>國立臺灣師範大學</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>「臺灣銀行社群營運及行銷企劃」採購案</t>
+          <t>2027第十二屆國際數理奧林匹亞發展研討會住宿、餐飲、會議場地及交通服務</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1180000</v>
+        <v>650000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1187,21 +1187,21 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>133-115-B240</t>
+          <t>NU211510190599</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>行銷、社群</t>
+          <t>研討會</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
@@ -1222,20 +1222,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>臺中市政府文化局</t>
+          <t>高雄市政府青年局</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>「2027大墩文化中心書法藝術節」委託專業服務案</t>
+          <t>「青年堤畔漫遊推廣活動」委託專業服務採購案</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>500000</v>
+        <v>1450000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1250,17 +1250,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DCC11601</t>
+          <t>KYB115023</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>藝術節</t>
+          <t>活動、推廣</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1285,20 +1285,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>環境部</t>
+          <t>花蓮縣政府</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>全民環境永續運動推廣競賽專案工作計畫</t>
+          <t>116年度加強公務和諧連繫－農特產品、伴手禮及紀念品行銷推廣採購案(開口契約)</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>13730000</v>
+        <v>4393000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1313,17 +1313,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>115AA114</t>
+          <t>SK1150006298</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>競賽、推廣</t>
+          <t>行銷推廣</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1348,20 +1348,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>桃園市大溪區公所</t>
+          <t>臺灣銀行股份有限公司</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>116年桃園市大溪區元旦升旗典禮活動勞務採購</t>
+          <t>「臺灣銀行社群營運及行銷企劃」採購案</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>286600</v>
+        <v>1180000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1376,17 +1376,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>115102201</t>
+          <t>133-115-B240</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>活動、典禮</t>
+          <t>行銷、社群</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1411,25 +1411,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>教育部青年發展署</t>
+          <t>臺中市政府文化局</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>116年「青年志工行動競賽表揚暨培力交流活動」徵求承辦單位勞務採購案</t>
+          <t>「2027大墩文化中心書法藝術節」委託專業服務案</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>12000000</v>
+        <v>500000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>116201</t>
+          <t>DCC11601</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>活動、競賽</t>
+          <t>藝術節</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1474,20 +1474,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>環境部</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>115年屏東縣防暴社區環境營造及品牌推廣計畫</t>
+          <t>全民環境永續運動推廣競賽專案工作計畫</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>2000000</v>
+        <v>13730000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1502,17 +1502,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>B054-1151022-1B</t>
+          <t>115AA114</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>推廣、品牌</t>
+          <t>競賽、推廣</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1537,25 +1537,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>國立故宮博物院</t>
+          <t>桃園市大溪區公所</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>116年度數位影音製作案</t>
+          <t>116年桃園市大溪區元旦升旗典禮活動勞務採購</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>2750000</v>
+        <v>286600</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1565,17 +1565,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>NPM115088</t>
+          <t>115102201</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>影音製作</t>
+          <t>活動、典禮</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1600,20 +1600,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>監察院</t>
+          <t>教育部青年發展署</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>監察院國家人權委員會「國際人權輿情及重要議題觀測分析」專業服務案</t>
+          <t>116年「青年志工行動競賽表揚暨培力交流活動」徵求承辦單位勞務採購案</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1785000</v>
+        <v>12000000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1628,21 +1628,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>B1151001</t>
+          <t>116201</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>政策溝通</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>輿情</t>
+          <t>活動、競賽</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
@@ -1663,16 +1663,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>金門縣烈嶼鄉公所</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026光陰的旋律經典老歌活動委託專業服務</t>
+          <t>115年屏東縣防暴社區環境營造及品牌推廣計畫</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>2261000</v>
+        <v>2000000</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1691,21 +1691,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>115T09</t>
+          <t>B054-1151022-1B</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>推廣、品牌</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
@@ -1726,25 +1726,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>苗栗縣後龍鎮公所</t>
+          <t>國立故宮博物院</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>「苗栗縣後龍鎮115年度甘藷花生節活動」委託專業服務案</t>
+          <t>116年度數位影音製作案</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1430000</v>
+        <v>2750000</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1754,21 +1754,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>F1151029062</t>
+          <t>NPM115088</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>影音製作</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
@@ -1789,25 +1789,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>基隆市政府</t>
+          <t>監察院</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>多元休閒育樂暨戰鬥陀螺交流活動委託專業服務案</t>
+          <t>監察院國家人權委員會「國際人權輿情及重要議題觀測分析」專業服務案</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>950000</v>
+        <v>1785000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1817,21 +1817,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>115A06</t>
+          <t>B1151001</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>政策溝通</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>輿情</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
@@ -1852,25 +1852,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>國史館臺灣文獻館</t>
+          <t>金門縣烈嶼鄉公所</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>「統制‧狂飆‧生機：臺灣戰後初期經濟與二二八事件」展覽規劃設計施作及網頁、圖錄勞務採購</t>
+          <t>2026光陰的旋律經典老歌活動委託專業服務</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>1100000</v>
+        <v>2261000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>D-115-24</t>
+          <t>115T09</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>展覽</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1910,21 +1910,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>高雄市政府新聞局</t>
+          <t>苗栗縣後龍鎮公所</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>115年打造智慧城市網路媒體行銷案</t>
+          <t>「苗栗縣後龍鎮115年度甘藷花生節活動」委託專業服務案</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>300000</v>
+        <v>1430000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1943,21 +1943,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1151020B</t>
+          <t>F1151029062</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>媒體行銷</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
@@ -1966,28 +1966,28 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-22 08:39</t>
+          <t>2026-10-23 08:36</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>苗栗縣苗栗市公所</t>
+          <t>基隆市政府</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>115年度苗栗市親子蘿蔔節活動執行委託專業服務採購案</t>
+          <t>多元休閒育樂暨戰鬥陀螺交流活動委託專業服務案</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>1060000</v>
+        <v>950000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>B1605</t>
+          <t>115A06</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2016,11 +2016,11 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
@@ -2029,37 +2029,37 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-22 08:39</t>
+          <t>2026-10-23 08:36</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>臺東縣政府</t>
+          <t>國史館臺灣文獻館</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>台東紅烏龍產業培力暨跨域行銷推廣計畫委託專業服務案</t>
+          <t>「統制‧狂飆‧生機：臺灣戰後初期經濟與二二八事件」展覽規劃設計施作及網頁、圖錄勞務採購</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>10500000</v>
+        <v>1100000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2069,21 +2069,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>115810430549</t>
+          <t>D-115-24</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>行銷推廣</t>
+          <t>展覽</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-22 08:39</t>
+          <t>2026-10-23 08:36</t>
         </is>
       </c>
     </row>
@@ -2104,20 +2104,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>臺東縣政府</t>
+          <t>高雄市政府新聞局</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>臺東縣116年度元旦及國慶升旗典禮慶祝活動</t>
+          <t>115年打造智慧城市網路媒體行銷案</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1440000</v>
+        <v>300000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2132,17 +2132,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>115130230570</t>
+          <t>1151020B</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>活動、典禮</t>
+          <t>媒體行銷</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2167,25 +2167,25 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>海洋委員會海洋保育署</t>
+          <t>苗栗縣苗栗市公所</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2028國際海龜年會(ISTS46)籌辦及宣傳推廣計畫</t>
+          <t>115年度苗栗市親子蘿蔔節活動執行委託專業服務採購案</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>6000000</v>
+        <v>1060000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2195,17 +2195,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>115-C-106</t>
+          <t>B1605</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>宣傳推廣</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2230,16 +2230,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>內政部國家公園署</t>
+          <t>臺東縣政府</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>臺灣濕地日品牌推廣及濕地保育社會參與計畫</t>
+          <t>台東紅烏龍產業培力暨跨域行銷推廣計畫委託專業服務案</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>8430000</v>
+        <v>10500000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>115N-026</t>
+          <t>115810430549</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>推廣、品牌</t>
+          <t>行銷推廣</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2293,25 +2293,25 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>臺中市風景區管理所</t>
+          <t>臺東縣政府</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>大安港媽祖文化園區假日主題市集活動委託專業服務案</t>
+          <t>臺東縣116年度元旦及國慶升旗典禮慶祝活動</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0</v>
+        <v>1440000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>115102040</t>
+          <t>115130230570</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2331,11 +2331,11 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>活動、典禮</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
@@ -2356,16 +2356,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>新竹市政府</t>
+          <t>海洋委員會海洋保育署</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>新竹市政府2027年國外食品展佈展及行銷委託專業服務案</t>
+          <t>2028國際海龜年會(ISTS46)籌辦及宣傳推廣計畫</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>8000000</v>
+        <v>6000000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1150309</t>
+          <t>115-C-106</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2394,11 +2394,11 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>行銷</t>
+          <t>宣傳推廣</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
@@ -2419,25 +2419,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>彰化縣員林市公所</t>
+          <t>內政部國家公園署</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>「116年新春揮毫贈春聯活動」委託專業服務案</t>
+          <t>臺灣濕地日品牌推廣及濕地保育社會參與計畫</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>577000</v>
+        <v>8430000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2447,21 +2447,21 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>02115033</t>
+          <t>115N-026</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>推廣、品牌</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
@@ -2477,40 +2477,40 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>宜蘭縣政府</t>
+          <t>臺中市風景區管理所</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>「宜蘭縣115年國際移民嘉年華」活動規劃執行委託案</t>
+          <t>大安港媽祖文化園區假日主題市集活動委託專業服務案</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>400000</v>
+        <v>0</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>CVSL115019</t>
+          <t>115102040</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2520,11 +2520,11 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>嘉年華、活動規劃</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
@@ -2533,32 +2533,32 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-21 08:35</t>
+          <t>2026-10-22 08:39</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>桃園市政府工務局</t>
+          <t>新竹市政府</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>桃園市116年績優社工人員表揚典禮暨社工日系列活動</t>
+          <t>新竹市政府2027年國外食品展佈展及行銷委託專業服務案</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>4000000</v>
+        <v>8000000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2573,21 +2573,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1151019-2</t>
+          <t>1150309</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>系列活動、典禮</t>
+          <t>行銷</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
@@ -2596,32 +2596,32 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-21 08:35</t>
+          <t>2026-10-22 08:39</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>台灣中油股份有限公司天然氣事業部觀塘液化天然氣廠</t>
+          <t>彰化縣員林市公所</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>觀塘廠多媒體影片製作</t>
+          <t>「116年新春揮毫贈春聯活動」委託專業服務案</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>935101</v>
+        <v>577000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2636,21 +2636,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>LEA1540001</t>
+          <t>02115033</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>影片製作、媒體</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-21 08:35</t>
+          <t>2026-10-22 08:39</t>
         </is>
       </c>
     </row>
@@ -2671,49 +2671,49 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>勞動部勞動力發展署桃竹苗分署</t>
+          <t>宜蘭縣政府</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>「2027桃竹苗OpenHouse就業博覽會官方網站」勞務採購案</t>
+          <t>「宜蘭縣115年國際移民嘉年華」活動規劃執行委託案</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>3324999</v>
+        <v>400000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>116Y045</t>
+          <t>CVSL115019</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>博覽會</t>
+          <t>嘉年華、活動規劃</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
@@ -2734,25 +2734,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>農業部</t>
+          <t>桃園市政府工務局</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>116年度整體農業政策整合行銷案</t>
+          <t>桃園市116年績優社工人員表揚典禮暨社工日系列活動</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>25000000</v>
+        <v>4000000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>公開招標公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2762,21 +2762,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>11559T</t>
+          <t>1151019-2</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>整合行銷</t>
+          <t>系列活動、典禮</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
@@ -2797,20 +2797,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>新竹市政府</t>
+          <t>台灣中油股份有限公司天然氣事業部觀塘液化天然氣廠</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>115年新竹市志願服務表揚暨社區成果展委託專業服務案</t>
+          <t>觀塘廠多媒體影片製作</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>1312500</v>
+        <v>935101</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2825,21 +2825,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1150307</t>
+          <t>LEA1540001</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>成果展</t>
+          <t>影片製作、媒體</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
@@ -2860,20 +2860,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>宜蘭縣政府</t>
+          <t>勞動部勞動力發展署桃竹苗分署</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>宜蘭縣115年度原有住宅無障礙設施補助委託辦理推廣宣導評估案</t>
+          <t>「2027桃竹苗OpenHouse就業博覽會官方網站」勞務採購案</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1210000</v>
+        <v>3324999</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2883,26 +2883,26 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>CNSL115032</t>
+          <t>116Y045</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>宣導、推廣</t>
+          <t>博覽會</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
@@ -2923,25 +2923,25 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>南投縣草屯鎮公所</t>
+          <t>農業部</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026草屯聖誕煙火嘉年華委託專業服務勞務採購案</t>
+          <t>116年度整體農業政策整合行銷案</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>7000000</v>
+        <v>25000000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開招標公告</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>115FR122501</t>
+          <t>11559T</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>嘉年華</t>
+          <t>整合行銷</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2986,20 +2986,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>核能安全委員會</t>
+          <t>新竹市政府</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>116及117年度新聞媒體監測資料檢索系統勞務採購案</t>
+          <t>115年新竹市志願服務表揚暨社區成果展委託專業服務案</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>964800</v>
+        <v>1312500</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3014,21 +3014,21 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>NSC11510044L</t>
+          <t>1150307</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>政策溝通</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>媒體監測</t>
+          <t>成果展</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
@@ -3049,20 +3049,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>苗栗縣政府</t>
+          <t>宜蘭縣政府</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>「2027台灣燈會在苗栗－整體展演策劃、製作及執行」委託專業服務案</t>
+          <t>宜蘭縣115年度原有住宅無障礙設施補助委託辦理推廣宣導評估案</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>55500000</v>
+        <v>1210000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3072,26 +3072,26 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>115229</t>
+          <t>CNSL115032</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>燈會</t>
+          <t>宣導、推廣</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
@@ -3112,25 +3112,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>屏東縣長治鄉公所</t>
+          <t>南投縣草屯鎮公所</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2027年繁華義勇恩公文化祭暨祭祀慶典活動委託專業服務案</t>
+          <t>2026草屯聖誕煙火嘉年華委託專業服務勞務採購案</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>800000</v>
+        <v>7000000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1151015</t>
+          <t>115FR122501</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3150,11 +3150,11 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>嘉年華</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
@@ -3170,30 +3170,30 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>衛生福利部</t>
+          <t>核能安全委員會</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>116年度「社會工作專業人員表揚典禮暨宣導活動」</t>
+          <t>116及117年度新聞媒體監測資料檢索系統勞務採購案</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>2600000</v>
+        <v>964800</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3203,21 +3203,21 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>M1604017</t>
+          <t>NSC11510044L</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>政策溝通</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>活動、典禮、宣導活動</t>
+          <t>媒體監測</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
@@ -3226,37 +3226,37 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-20 09:04</t>
+          <t>2026-10-21 08:35</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>高雄市政府新聞局</t>
+          <t>苗栗縣政府</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>施政成果暨大型活動平面整合行銷案</t>
+          <t>「2027台灣燈會在苗栗－整體展演策劃、製作及執行」委託專業服務案</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>1100000</v>
+        <v>55500000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3266,21 +3266,21 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1151015B</t>
+          <t>115229</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>活動、整合行銷</t>
+          <t>燈會</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
@@ -3289,37 +3289,37 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-20 09:04</t>
+          <t>2026-10-21 08:35</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>高雄市政府工務局公園處</t>
+          <t>屏東縣長治鄉公所</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>115-116年度工務建設宣導活動案(開口契約)</t>
+          <t>2027年繁華義勇恩公文化祭暨祭祀慶典活動委託專業服務案</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>2445109</v>
+        <v>800000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3329,21 +3329,21 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>11504SB012</t>
+          <t>1151015</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-10-20 09:04</t>
+          <t>2026-10-21 08:35</t>
         </is>
       </c>
     </row>
@@ -3364,49 +3364,49 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>苗栗縣政府衛生局</t>
+          <t>衛生福利部</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>115年預防保健業務之戶外廣告行銷推廣</t>
+          <t>116年度「社會工作專業人員表揚典禮暨宣導活動」</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>580000</v>
+        <v>2600000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>11532</t>
+          <t>M1604017</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>行銷推廣、廣告</t>
+          <t>活動、典禮、宣導活動</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
@@ -3427,16 +3427,16 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>臺北市立美術館</t>
+          <t>高雄市政府新聞局</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>「當代藝術與技術論壇」錄影案</t>
+          <t>施政成果暨大型活動平面整合行銷案</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>220000</v>
+        <v>1100000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -3455,21 +3455,21 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>115RE0118</t>
+          <t>1151015B</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>論壇</t>
+          <t>活動、整合行銷</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
@@ -3490,20 +3490,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>桃園市政府客家事務局</t>
+          <t>高雄市政府工務局公園處</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>桃園市政府客家事務局115-116年桃園市客家文化館展覽活動等營運管理勞務採購案</t>
+          <t>115-116年度工務建設宣導活動案(開口契約)</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>5100000</v>
+        <v>2445109</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3518,21 +3518,21 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>115-022</t>
+          <t>11504SB012</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>活動、展覽</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
@@ -3553,16 +3553,16 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>南投縣政府</t>
+          <t>苗栗縣政府衛生局</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>115年度幸福南投短影音行銷宣傳採購案</t>
+          <t>115年預防保健業務之戶外廣告行銷推廣</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>1400000</v>
+        <v>580000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -3576,12 +3576,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>115-07-07-006G</t>
+          <t>11532</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3591,11 +3591,11 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>行銷宣傳</t>
+          <t>行銷推廣、廣告</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
@@ -3616,25 +3616,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>農業部林業及自然保育署花蓮分署</t>
+          <t>臺北市立美術館</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>林田山遊客中心佈展(含活動駐館)委託專業服務</t>
+          <t>「當代藝術與技術論壇」錄影案</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>5900000</v>
+        <v>220000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3644,21 +3644,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>115m011</t>
+          <t>115RE0118</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>論壇</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
@@ -3679,20 +3679,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>臺中市神岡區公所</t>
+          <t>桃園市政府客家事務局</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>【2026臺中市民野餐日(神岡區)雙場地活動】委託專業服務採購案</t>
+          <t>桃園市政府客家事務局115-116年桃園市客家文化館展覽活動等營運管理勞務採購案</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>1920000</v>
+        <v>5100000</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>115-LS37</t>
+          <t>115-022</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3717,11 +3717,11 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>活動、展覽</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
@@ -3742,25 +3742,25 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>臺中市政府客家事務委員會</t>
+          <t>南投縣政府</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2027臺中東勢新丁粄節-文宣暨會場佈置委託專業服務勞務採購案</t>
+          <t>115年度幸福南投短影音行銷宣傳採購案</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>1750000</v>
+        <v>1400000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1151102</t>
+          <t>115-07-07-006G</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3780,11 +3780,11 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>文宣</t>
+          <t>行銷宣傳</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
@@ -3800,25 +3800,25 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>國家人權博物館</t>
+          <t>農業部林業及自然保育署花蓮分署</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>「解嚴40週年國際論壇暨紀念專書籌劃」委託專業服務案</t>
+          <t>林田山遊客中心佈展(含活動駐館)委託專業服務</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>2200000</v>
+        <v>5900000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3833,21 +3833,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>11590Z</t>
+          <t>115m011</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>國際論壇、論壇</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
@@ -3856,47 +3856,47 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>南投縣政府</t>
+          <t>臺中市神岡區公所</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>「2026南投花卉嘉年華－草屯展區系列活動」勞務採購案</t>
+          <t>【2026臺中市民野餐日(神岡區)雙場地活動】委託專業服務採購案</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>1000000</v>
+        <v>1920000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1150602018G</t>
+          <t>115-LS37</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3906,11 +3906,11 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>嘉年華、系列活動</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
@@ -3919,35 +3919,37 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>臺南市政府農業局</t>
+          <t>臺中市政府客家事務委員會</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>日本地區臺南市農漁產推廣暨行銷活動策畫與執行委託專業服務案</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr"/>
+          <t>2027臺中東勢新丁粄節-文宣暨會場佈置委託專業服務勞務採購案</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>1750000</v>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3957,21 +3959,21 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>115AGR080</t>
+          <t>1151102</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>活動、行銷、推廣</t>
+          <t>文宣</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
@@ -3980,7 +3982,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-19 08:10</t>
+          <t>2026-10-20 09:04</t>
         </is>
       </c>
     </row>
@@ -3992,25 +3994,25 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>桃園市政府環境管理處</t>
+          <t>國家人權博物館</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>115年度職業安全衛生業務標竿學習宣導活動計畫</t>
+          <t>「解嚴40週年國際論壇暨紀念專書籌劃」委託專業服務案</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>1300000</v>
+        <v>2200000</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4020,21 +4022,21 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1150036916</t>
+          <t>11590Z</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>國際論壇、論壇</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
@@ -4055,49 +4057,49 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>南投縣政府社會及勞動局</t>
+          <t>南投縣政府</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>南投縣115年度國際身心障礙者日宣導活動</t>
+          <t>「2026南投花卉嘉年華－草屯展區系列活動」勞務採購案</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>2500000</v>
+        <v>1000000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>115-10-10-005-E</t>
+          <t>1150602018G</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>嘉年華、系列活動</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
@@ -4118,25 +4120,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>財團法人蘭陽農業發展基金會</t>
+          <t>臺南市政府農業局</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2027宜蘭綠色博覽會－海洋館委託專業服務案</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="n">
-        <v>7000000</v>
-      </c>
+          <t>日本地區臺南市農漁產推廣暨行銷活動策畫與執行委託專業服務案</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4146,21 +4146,21 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>115101305</t>
+          <t>115AGR080</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>博覽會</t>
+          <t>活動、行銷、推廣</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
@@ -4181,25 +4181,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>財團法人蘭陽農業發展基金會</t>
+          <t>桃園市政府環境管理處</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2027宜蘭綠色博覽會－森林館委託專業服務案</t>
+          <t>115年度職業安全衛生業務標竿學習宣導活動計畫</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>3950000</v>
+        <v>1300000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4209,21 +4209,21 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>115101301</t>
+          <t>1150036916</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>博覽會</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
@@ -4244,49 +4244,49 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>雲林縣政府</t>
+          <t>南投縣政府社會及勞動局</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>「2026雲林文創聯合徵選暨雲林設計獎」頒獎典禮委託規劃執行案</t>
+          <t>南投縣115年度國際身心障礙者日宣導活動</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>500000</v>
+        <v>2500000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1152H10116</t>
+          <t>115-10-10-005-E</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>頒獎典禮</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
@@ -4307,25 +4307,25 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>臺北市教師研習中心</t>
+          <t>財團法人蘭陽農業發展基金會</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>116年度優質學校頒獎典禮、杏壇芬芳獎表揚典禮、臺北教育111標竿學校頒獎典禮採購案</t>
+          <t>2027宜蘭綠色博覽會－海洋館委託專業服務案</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>869500</v>
+        <v>7000000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4335,21 +4335,21 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>11605</t>
+          <t>115101305</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>頒獎典禮</t>
+          <t>博覽會</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
@@ -4370,25 +4370,25 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>臺中市政府數位發展局</t>
+          <t>財團法人蘭陽農業發展基金會</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>台中通特店消費推廣暨抽獎活動案</t>
+          <t>2027宜蘭綠色博覽會－森林館委託專業服務案</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>950000</v>
+        <v>3950000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4398,21 +4398,21 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>115B-10</t>
+          <t>115101301</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>活動、推廣</t>
+          <t>博覽會</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
@@ -4433,35 +4433,35 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>桃園市政府客家事務局</t>
+          <t>雲林縣政府</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>「桃園市客家文化館開館系列活動」勞務採購案</t>
+          <t>「2026雲林文創聯合徵選暨雲林設計獎」頒獎典禮委託規劃執行案</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>5500000</v>
+        <v>500000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>115-021</t>
+          <t>1152H10116</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>系列活動</t>
+          <t>頒獎典禮</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -4496,25 +4496,25 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>嘉義市政府</t>
+          <t>臺北市教師研習中心</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>嘉義市政府116年家庭暴力暨性侵害防治中心宣導行銷計畫</t>
+          <t>116年度優質學校頒獎典禮、杏壇芬芳獎表揚典禮、臺北教育111標竿學校頒獎典禮採購案</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>1800000</v>
+        <v>869500</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4524,17 +4524,17 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>115266</t>
+          <t>11605</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>宣導、行銷</t>
+          <t>頒獎典禮</t>
         </is>
       </c>
       <c r="K65" t="n">
@@ -4559,16 +4559,16 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>國家科學及技術委員會南部科學園區管理局</t>
+          <t>臺中市政府數位發展局</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>國家科學及技術委員會116年度科學園區滿意度調查計畫</t>
+          <t>台中通特店消費推廣暨抽獎活動案</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>1236708</v>
+        <v>950000</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -4587,21 +4587,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>115660D01151</t>
+          <t>115B-10</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>政策溝通</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>滿意度調查</t>
+          <t>活動、推廣</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
@@ -4622,20 +4622,20 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>農業部林業及自然保育署阿里山林業鐵路及文化資產管理處</t>
+          <t>桃園市政府客家事務局</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>116-117年「阿里山林鐵行動學校」跨館際展覽委託專業服務案</t>
+          <t>「桃園市客家文化館開館系列活動」勞務採購案</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>2800000</v>
+        <v>5500000</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>116-EDU-001</t>
+          <t>115-021</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4660,11 +4660,11 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>展覽</t>
+          <t>系列活動</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
@@ -4685,25 +4685,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>新北市政府觀光旅遊局</t>
+          <t>嘉義市政府</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>115年新北市平日住宿及生日券獎助活動專案管理委託專業服務案</t>
+          <t>嘉義市政府116年家庭暴力暨性侵害防治中心宣導行銷計畫</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>700000</v>
+        <v>1800000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4713,21 +4713,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1152038719</t>
+          <t>115266</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>宣導、行銷</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
@@ -4748,20 +4748,20 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>中華郵政股份有限公司</t>
+          <t>國家科學及技術委員會南部科學園區管理局</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>「羊來了-生肖郵票特展」策、布展及開幕活動委託服務</t>
+          <t>國家科學及技術委員會116年度科學園區滿意度調查計畫</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>1480000</v>
+        <v>1236708</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4776,21 +4776,21 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>115-3-167</t>
+          <t>115660D01151</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>政策溝通</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>滿意度調查</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
@@ -4806,25 +4806,25 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>桃園市政府藝文設施管理中心</t>
+          <t>農業部林業及自然保育署阿里山林業鐵路及文化資產管理處</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>「2027桃園鐵玫瑰藝術節活動執行統籌及行銷」委託專業服務採購案</t>
+          <t>116-117年「阿里山林鐵行動學校」跨館際展覽委託專業服務案</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>9000000</v>
+        <v>2800000</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4834,26 +4834,26 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>115AFMC-017</t>
+          <t>116-EDU-001</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>活動執行、藝術節、行銷</t>
+          <t>展覽</t>
         </is>
       </c>
       <c r="K70" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
@@ -4862,32 +4862,32 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>屏東縣獅子鄉公所</t>
+          <t>新北市政府觀光旅遊局</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>屏東縣獅子鄉115年度慶祝重陽節聯合表揚暨族語文化推廣與文化健康站成果展活動勞務採購案</t>
+          <t>115年新北市平日住宿及生日券獎助活動專案管理委託專業服務案</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>1162700</v>
+        <v>700000</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4897,26 +4897,26 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1151001AA</t>
+          <t>1152038719</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>成果展、活動、推廣</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
@@ -4925,37 +4925,37 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>勞動部勞動力發展署雲嘉南分署</t>
+          <t>中華郵政股份有限公司</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>116年度社群平台整合行銷委託計畫</t>
+          <t>「羊來了-生肖郵票特展」策、布展及開幕活動委託服務</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>2000000</v>
+        <v>1480000</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4965,21 +4965,21 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>yctrb1150129</t>
+          <t>115-3-167</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>整合行銷、社群平台</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2026-10-16 09:31</t>
+          <t>2026-10-19 08:10</t>
         </is>
       </c>
     </row>
@@ -5000,25 +5000,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>內政部</t>
+          <t>桃園市政府藝文設施管理中心</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>116年第84屆兵役節慶祝大會暨頒獎典禮委外服務案</t>
+          <t>「2027桃園鐵玫瑰藝術節活動執行統籌及行銷」委託專業服務採購案</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>1230000</v>
+        <v>9000000</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5028,21 +5028,21 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>115YJ-ST15</t>
+          <t>115AFMC-017</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>國際會議論壇/活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>大會、頒獎典禮</t>
+          <t>活動執行、藝術節、行銷</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
@@ -5063,49 +5063,49 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>桃園市八德區公所</t>
+          <t>屏東縣獅子鄉公所</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>116年度桃園市元旦升旗典禮活動規劃與執行</t>
+          <t>屏東縣獅子鄉115年度慶祝重陽節聯合表揚暨族語文化推廣與文化健康站成果展活動勞務採購案</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>1600000</v>
+        <v>1162700</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>BB1151015</t>
+          <t>1151001AA</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>活動規劃、典禮</t>
+          <t>成果展、活動、推廣</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
@@ -5126,25 +5126,25 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>國立臺中教育大學</t>
+          <t>勞動部勞動力發展署雲嘉南分署</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>數位內容充實與推廣總計畫成果紀錄影片製作採購案</t>
+          <t>116年度社群平台整合行銷委託計畫</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>465000</v>
+        <v>2000000</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>115-C063</t>
+          <t>yctrb1150129</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5164,11 +5164,11 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>影片製作、推廣</t>
+          <t>整合行銷、社群平台</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
@@ -5189,49 +5189,49 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>文化部</t>
+          <t>內政部</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>文化部「蒙藏文化情境展示及體驗活動」展場設計製作布卸展及活動執行藝文採購案</t>
+          <t>116年第84屆兵役節慶祝大會暨頒獎典禮委外服務案</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>3350000</v>
+        <v>1230000</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>11510159</t>
+          <t>115YJ-ST15</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>國際會議論壇/活動執行</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>大會、頒獎典禮</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
@@ -5252,25 +5252,25 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>國立雲林科技大學</t>
+          <t>桃園市八德區公所</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026研發成果展場地佈置案</t>
+          <t>116年度桃園市元旦升旗典禮活動規劃與執行</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>840000</v>
+        <v>1600000</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>HTL115040</t>
+          <t>BB1151015</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5290,11 +5290,11 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>成果展</t>
+          <t>活動規劃、典禮</t>
         </is>
       </c>
       <c r="K77" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
@@ -5315,16 +5315,16 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>桃園市政府觀光旅遊局</t>
+          <t>國立臺中教育大學</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>116年桃園觀光旅遊局輿情蒐集及通報服務勞務採購案</t>
+          <t>數位內容充實與推廣總計畫成果紀錄影片製作採購案</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>247008</v>
+        <v>465000</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -5343,21 +5343,21 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>1151015-AA1</t>
+          <t>115-C063</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>政策溝通</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>輿情</t>
+          <t>影片製作、推廣</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
@@ -5378,25 +5378,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>臺中市立圖書館</t>
+          <t>文化部</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026臺中市立圖書館羅布森圖書館展覽委託專業服務採購案</t>
+          <t>文化部「蒙藏文化情境展示及體驗活動」展場設計製作布卸展及活動執行藝文採購案</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>1120000</v>
+        <v>3350000</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>115058</t>
+          <t>11510159</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5416,11 +5416,11 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>展覽</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="K79" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
@@ -5441,20 +5441,20 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>國立雲林科技大學</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>115年客家記憶共創計畫-客家文化中心古契約展覽策劃執行</t>
+          <t>2026研發成果展場地佈置案</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>850000</v>
+        <v>840000</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>A132-1151015-1</t>
+          <t>HTL115040</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5479,11 +5479,11 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>展覽</t>
+          <t>成果展</t>
         </is>
       </c>
       <c r="K80" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
@@ -5499,21 +5499,21 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>廣亞學校財團法人育達科技大學</t>
+          <t>桃園市政府觀光旅遊局</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>研究發展處創新創業輔導暨育成中心115年青年創業工作坊專案管理計畫青年遴選活動頒獎典禮暨成果展評選採購</t>
+          <t>116年桃園觀光旅遊局輿情蒐集及通報服務勞務採購案</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>350000</v>
+        <v>247008</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -5532,21 +5532,21 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>115J-04</t>
+          <t>1151015-AA1</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>政策溝通</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>頒獎典禮、成果展、活動、工作坊</t>
+          <t>輿情</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
@@ -5555,32 +5555,32 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>苗栗縣政府衛生局</t>
+          <t>臺中市立圖書館</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>115年衛生教育之媒體廣告行銷推廣</t>
+          <t>2026臺中市立圖書館羅布森圖書館展覽委託專業服務採購案</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>770000</v>
+        <v>1120000</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5595,21 +5595,21 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>11535</t>
+          <t>115058</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>行銷推廣、廣告、媒體</t>
+          <t>展覽</t>
         </is>
       </c>
       <c r="K82" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
@@ -5618,37 +5618,37 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>新竹市政府</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>116年新竹市政府城市行銷處社群網站管理</t>
+          <t>115年客家記憶共創計畫-客家文化中心古契約展覽策劃執行</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>1900000</v>
+        <v>850000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5658,21 +5658,21 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1150300</t>
+          <t>A132-1151015-1</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>城市行銷、社群網站</t>
+          <t>展覽</t>
         </is>
       </c>
       <c r="K83" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2026-10-15 08:34</t>
+          <t>2026-10-16 09:31</t>
         </is>
       </c>
     </row>
@@ -5693,16 +5693,16 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>高雄市政府地政局</t>
+          <t>廣亞學校財團法人育達科技大學</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>115年度不動產防詐暨交易安全宣導活動委外服務案</t>
+          <t>研究發展處創新創業輔導暨育成中心115年青年創業工作坊專案管理計畫青年遴選活動頒獎典禮暨成果展評選採購</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>400000</v>
+        <v>350000</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -5721,21 +5721,21 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>115019</t>
+          <t>115J-04</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>頒獎典禮、成果展、活動、工作坊</t>
         </is>
       </c>
       <c r="K84" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
@@ -5756,25 +5756,25 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>桃園市政府環境保護局</t>
+          <t>苗栗縣政府衛生局</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>116年社群網路環境教育推廣維運計畫</t>
+          <t>115年衛生教育之媒體廣告行銷推廣</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>3800000</v>
+        <v>770000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1150085608</t>
+          <t>11535</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5794,11 +5794,11 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>推廣、社群</t>
+          <t>行銷推廣、廣告、媒體</t>
         </is>
       </c>
       <c r="K85" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
@@ -5819,25 +5819,25 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>嘉義縣表演藝術中心</t>
+          <t>新竹市政府</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>嘉義縣表演藝術中心115年表演節目整合傳播委託專業服務案</t>
+          <t>116年新竹市政府城市行銷處社群網站管理</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>800000</v>
+        <v>1900000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>1150002654</t>
+          <t>1150300</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5857,11 +5857,11 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>整合傳播</t>
+          <t>城市行銷、社群網站</t>
         </is>
       </c>
       <c r="K86" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
@@ -5877,25 +5877,25 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>南投縣水里鄉公所</t>
+          <t>高雄市政府地政局</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>「2026水里觀光行銷暨農特產品推廣系列活動—煙火設計及施放勞務採購案」</t>
+          <t>115年度不動產防詐暨交易安全宣導活動委外服務案</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>1000000</v>
+        <v>400000</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>115SHTS07</t>
+          <t>115019</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5920,11 +5920,11 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>系列活動、觀光行銷、推廣</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="L87" s="3" t="inlineStr">
         <is>
@@ -5940,30 +5940,30 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>國立臺灣大學</t>
+          <t>桃園市政府環境保護局</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2027年臺大杜鵑花節學系博覽會場佈</t>
+          <t>116年社群網路環境教育推廣維運計畫</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>1250000</v>
+        <v>3800000</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5973,21 +5973,21 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1150963</t>
+          <t>1150085608</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>博覽會</t>
+          <t>推廣、社群</t>
         </is>
       </c>
       <c r="K88" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
@@ -6003,25 +6003,25 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>高雄市政府運動發展局</t>
+          <t>嘉義縣表演藝術中心</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>企業22年甲級排球聯賽高雄台電女子排球隊主場賽事行銷活動案</t>
+          <t>嘉義縣表演藝術中心115年表演節目整合傳播委託專業服務案</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>590000</v>
+        <v>800000</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -6036,17 +6036,17 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>115-B-76</t>
+          <t>1150002654</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>活動、行銷</t>
+          <t>整合傳播</t>
         </is>
       </c>
       <c r="K89" t="n">
@@ -6071,25 +6071,25 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>南投縣水里鄉公所</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>115年度管路灌溉成果推廣活動</t>
+          <t>「2026水里觀光行銷暨農特產品推廣系列活動—煙火設計及施放勞務採購案」</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>4000000</v>
+        <v>1000000</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>TY115B030</t>
+          <t>115SHTS07</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6109,11 +6109,11 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>活動、推廣</t>
+          <t>系列活動、觀光行銷、推廣</t>
         </is>
       </c>
       <c r="K90" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
@@ -6134,49 +6134,49 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>臺北市政府工務局</t>
+          <t>國立臺灣大學</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>116年全國大專院校運動會開閉幕典禮活動</t>
+          <t>2027年臺大杜鵑花節學系博覽會場佈</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>10000000</v>
+        <v>1250000</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>1150826S0096</t>
+          <t>1150963</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>活動、典禮</t>
+          <t>博覽會</t>
         </is>
       </c>
       <c r="K91" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L91" s="3" t="inlineStr">
         <is>
@@ -6197,20 +6197,20 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>臺中市政府環境保護局</t>
+          <t>高雄市政府運動發展局</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>115年度環保英雄歲末嘉年華活動採購案</t>
+          <t>企業22年甲級排球聯賽高雄台電女子排球隊主場賽事行銷活動案</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>1105000</v>
+        <v>590000</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>N1151013101</t>
+          <t>115-B-76</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>嘉年華</t>
+          <t>活動、行銷</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -6260,20 +6260,20 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>新北市政府環境保護局</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>116年度資源回收推動及形象改造計畫</t>
+          <t>115年度管路灌溉成果推廣活動</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>9670000</v>
+        <v>4000000</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6288,17 +6288,17 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>115-177</t>
+          <t>TY115B030</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>形象改造</t>
+          <t>活動、推廣</t>
         </is>
       </c>
       <c r="K93" t="n">
@@ -6323,20 +6323,20 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>原住民族委員會原住民族文化發展中心</t>
+          <t>臺北市政府工務局</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>116年公益彩券回饋金計畫-文化觀光行銷專業人才勞務採購案</t>
+          <t>116年全國大專院校運動會開閉幕典禮活動</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>4681825</v>
+        <v>10000000</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6346,22 +6346,22 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1150006860</t>
+          <t>1150826S0096</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>觀光行銷</t>
+          <t>活動、典禮</t>
         </is>
       </c>
       <c r="K94" t="n">
@@ -6386,16 +6386,16 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>勞動部</t>
+          <t>臺中市政府環境保護局</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>115年度「勞工自願提繳退休金影片製作案」</t>
+          <t>115年度環保英雄歲末嘉年華活動採購案</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>997920</v>
+        <v>1105000</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -6414,17 +6414,17 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>03-11509091</t>
+          <t>N1151013101</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>影片製作</t>
+          <t>嘉年華</t>
         </is>
       </c>
       <c r="K95" t="n">
@@ -6449,49 +6449,49 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>桃園市政府捷運工程局</t>
+          <t>新北市政府環境保護局</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>桃園市八德區德和路一段第2階段通車活動委託服務案</t>
+          <t>116年度資源回收推動及形象改造計畫</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>1000000</v>
+        <v>9670000</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1151006</t>
+          <t>115-177</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>形象改造</t>
         </is>
       </c>
       <c r="K96" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
@@ -6507,30 +6507,30 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>中華郵政股份有限公司</t>
+          <t>原住民族委員會原住民族文化發展中心</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>115年度郵政形象廣告電視託播</t>
+          <t>116年公益彩券回饋金計畫-文化觀光行銷專業人才勞務採購案</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>6000000</v>
+        <v>4681825</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>公開招標公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>115-5-294</t>
+          <t>1150006860</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6550,11 +6550,11 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>電視託播、形象廣告</t>
+          <t>觀光行銷</t>
         </is>
       </c>
       <c r="K97" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L97" s="3" t="inlineStr">
         <is>
@@ -6570,30 +6570,30 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>臺銀人壽保險股份有限公司</t>
+          <t>勞動部</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>115年壽險行銷研討會-理財激勵專案</t>
+          <t>115年度「勞工自願提繳退休金影片製作案」</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>8330000</v>
+        <v>997920</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -6603,21 +6603,21 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>115-005-106-CL-1-798</t>
+          <t>03-11509091</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>研討會</t>
+          <t>影片製作</t>
         </is>
       </c>
       <c r="K98" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L98" s="3" t="inlineStr">
         <is>
@@ -6633,23 +6633,25 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>國立臺南大學</t>
+          <t>桃園市政府捷運工程局</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>幼兒美感教育社群與國際交流影音紀錄</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr"/>
+          <t>桃園市八德區德和路一段第2階段通車活動委託服務案</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>1000000</v>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -6659,26 +6661,26 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>1151065-TL</t>
+          <t>1151006</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>國際會議論壇/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>國際交流、社群</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K99" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L99" s="3" t="inlineStr">
         <is>
@@ -6699,25 +6701,25 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>臺東縣鹿野鄉公所</t>
+          <t>中華郵政股份有限公司</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026鹿野馬拉松系列活動賽事勞務採購案</t>
+          <t>115年度郵政形象廣告電視託播</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>1460000</v>
+        <v>6000000</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>公開招標公告</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6727,21 +6729,21 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>1150929</t>
+          <t>115-5-294</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>系列活動</t>
+          <t>電視託播、形象廣告</t>
         </is>
       </c>
       <c r="K100" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
@@ -6762,25 +6764,25 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>臺中市大里區公所</t>
+          <t>臺銀人壽保險股份有限公司</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>115年大里區運動會暨里鄰長健行活動規劃執行委託專業服務採購</t>
+          <t>115年壽險行銷研討會-理財激勵專案</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>400000</v>
+        <v>8330000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6790,21 +6792,21 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>115dali032</t>
+          <t>115-005-106-CL-1-798</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>活動規劃</t>
+          <t>研討會</t>
         </is>
       </c>
       <c r="K101" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L101" s="3" t="inlineStr">
         <is>
@@ -6825,20 +6827,18 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>桃園市復興區公所</t>
+          <t>國立臺南大學</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>桃園市復興區115年度甜柿推廣活動好柿發聲勞務採購案</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="n">
-        <v>766500</v>
-      </c>
+          <t>幼兒美感教育社群與國際交流影音紀錄</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6853,21 +6853,21 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>115D52</t>
+          <t>1151065-TL</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>國際會議論壇/宣導行銷</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>活動、推廣</t>
+          <t>國際交流、社群</t>
         </is>
       </c>
       <c r="K102" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L102" s="3" t="inlineStr">
         <is>
@@ -6888,16 +6888,16 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>南投縣政府</t>
+          <t>臺東縣鹿野鄉公所</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>115年度南投拍片好所在影視音協拍多元媒體宣傳採購案</t>
+          <t>2026鹿野馬拉松系列活動賽事勞務採購案</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>1100000</v>
+        <v>1460000</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -6916,17 +6916,17 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>1150707005G</t>
+          <t>1150929</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>媒體宣傳</t>
+          <t>系列活動</t>
         </is>
       </c>
       <c r="K103" t="n">
@@ -6951,35 +6951,35 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>農業部林業及自然保育署阿里山林業鐵路及文化資產管理處</t>
+          <t>臺中市大里區公所</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>阿里山林鐵服務中心小葉子館之展覽、賣店、服務設施規劃暨製作案</t>
+          <t>115年大里區運動會暨里鄰長健行活動規劃執行委託專業服務採購</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>2500000</v>
+        <v>400000</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>115-ALI-001</t>
+          <t>115dali032</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6989,11 +6989,11 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>展覽</t>
+          <t>活動規劃</t>
         </is>
       </c>
       <c r="K104" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L104" s="3" t="inlineStr">
         <is>
@@ -7014,16 +7014,16 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>苗栗縣政府</t>
+          <t>桃園市復興區公所</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>苗栗縣政府115年度短影音攝製暨電視宣傳委託專業服務案</t>
+          <t>桃園市復興區115年度甜柿推廣活動好柿發聲勞務採購案</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>650000</v>
+        <v>766500</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -7042,21 +7042,21 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>115147f</t>
+          <t>115D52</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>宣傳</t>
+          <t>活動、推廣</t>
         </is>
       </c>
       <c r="K105" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L105" s="3" t="inlineStr">
         <is>
@@ -7072,17 +7072,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>花蓮縣豐濱鄉公所</t>
+          <t>南投縣政府</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>115年「點亮豐濱！族語詩歌高聲唱耶誕嘉年華暨文化健康站成果展」勞務採購案</t>
+          <t>115年度南投拍片好所在影視音協拍多元媒體宣傳採購案</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
@@ -7105,21 +7105,21 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>FB1151218</t>
+          <t>1150707005G</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>嘉年華、成果展</t>
+          <t>媒體宣傳</t>
         </is>
       </c>
       <c r="K106" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L106" s="3" t="inlineStr">
         <is>
@@ -7135,21 +7135,21 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>臺中市政府研究發展考核委員會</t>
+          <t>農業部林業及自然保育署阿里山林業鐵路及文化資產管理處</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>「115年度臺中市經濟發展與城市行銷推廣案」委託專業服務案</t>
+          <t>阿里山林鐵服務中心小葉子館之展覽、賣店、服務設施規劃暨製作案</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>2520000</v>
+        <v>2500000</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -7163,26 +7163,26 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>115RCP16</t>
+          <t>115-ALI-001</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>行銷推廣、城市行銷</t>
+          <t>展覽</t>
         </is>
       </c>
       <c r="K107" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L107" s="3" t="inlineStr">
         <is>
@@ -7198,25 +7198,25 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>高雄市政府經濟發展局</t>
+          <t>苗栗縣政府</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>「2027高雄過好年聯合記者會」委託專業服務案</t>
+          <t>苗栗縣政府115年度短影音攝製暨電視宣傳委託專業服務案</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>500000</v>
+        <v>650000</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -7231,21 +7231,21 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>115090</t>
+          <t>115147f</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>記者會</t>
+          <t>宣傳</t>
         </is>
       </c>
       <c r="K108" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L108" s="3" t="inlineStr">
         <is>
@@ -7266,20 +7266,20 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>內政部</t>
+          <t>花蓮縣豐濱鄉公所</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>115年度合作社制度宣導短片託播案</t>
+          <t>115年「點亮豐濱！族語詩歌高聲唱耶誕嘉年華暨文化健康站成果展」勞務採購案</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>800000</v>
+        <v>1100000</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -7289,26 +7289,26 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>115HT-NH090806</t>
+          <t>FB1151218</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>宣導短片</t>
+          <t>嘉年華、成果展</t>
         </is>
       </c>
       <c r="K109" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L109" s="3" t="inlineStr">
         <is>
@@ -7329,25 +7329,25 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>花蓮縣議會</t>
+          <t>臺中市政府研究發展考核委員會</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>花蓮縣議會「第21屆議員宣誓就職典禮暨正副議長選舉」委託專業服務案</t>
+          <t>「115年度臺中市經濟發展與城市行銷推廣案」委託專業服務案</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>360000</v>
+        <v>2520000</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -7357,21 +7357,21 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>115GA31</t>
+          <t>115RCP16</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>典禮</t>
+          <t>行銷推廣、城市行銷</t>
         </is>
       </c>
       <c r="K110" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="L110" s="3" t="inlineStr">
         <is>
@@ -7387,30 +7387,30 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>南投縣水里鄉公所</t>
+          <t>高雄市政府經濟發展局</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>「2026水里觀光行銷暨農特產推廣系列活動」勞務採購案</t>
+          <t>「2027高雄過好年聯合記者會」委託專業服務案</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>4300000</v>
+        <v>500000</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -7420,21 +7420,21 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>115SHTS06</t>
+          <t>115090</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>系列活動、觀光行銷、推廣</t>
+          <t>記者會</t>
         </is>
       </c>
       <c r="K111" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="L111" s="3" t="inlineStr">
         <is>
@@ -7450,21 +7450,21 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>花蓮縣政府</t>
+          <t>內政部</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>115年花蓮縣長青大學結業典禮暨成果展活動</t>
+          <t>115年度合作社制度宣導短片託播案</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>1150000</v>
+        <v>800000</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -7478,26 +7478,26 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>SC1150020901</t>
+          <t>115HT-NH090806</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>成果展、活動、典禮</t>
+          <t>宣導短片</t>
         </is>
       </c>
       <c r="K112" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L112" s="3" t="inlineStr">
         <is>
@@ -7513,25 +7513,25 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>臺南市政府經濟發展局</t>
+          <t>花蓮縣議會</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>「116年永康迎春嘉年華」活動規劃執行服務</t>
+          <t>花蓮縣議會「第21屆議員宣誓就職典禮暨正副議長選舉」委託專業服務案</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>600000</v>
+        <v>360000</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>115ECON71S1</t>
+          <t>115GA31</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7556,11 +7556,11 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>嘉年華、活動規劃</t>
+          <t>典禮</t>
         </is>
       </c>
       <c r="K113" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L113" s="3" t="inlineStr">
         <is>
@@ -7581,20 +7581,20 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>臺北表演藝術中心</t>
+          <t>南投縣水里鄉公所</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>第三屆臺北戲劇獎頒獎典禮暨系列活動製作執行勞務採購案</t>
+          <t>「2026水里觀光行銷暨農特產推廣系列活動」勞務採購案</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>15000000</v>
+        <v>4300000</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -7609,21 +7609,21 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>TPACRD1150141</t>
+          <t>115SHTS06</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>頒獎典禮、系列活動</t>
+          <t>系列活動、觀光行銷、推廣</t>
         </is>
       </c>
       <c r="K114" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L114" s="3" t="inlineStr">
         <is>
@@ -7644,20 +7644,20 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>屏東縣獅子鄉公所</t>
+          <t>花蓮縣政府</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>屏東縣獅子鄉115年度慶祝重陽節聯合表揚暨族語文化推廣與文化健康站成果展活動勞務採購案</t>
+          <t>115年花蓮縣長青大學結業典禮暨成果展活動</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>1162700</v>
+        <v>1150000</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -7672,17 +7672,17 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>1151001AA</t>
+          <t>SC1150020901</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>成果展、活動、推廣</t>
+          <t>成果展、活動、典禮</t>
         </is>
       </c>
       <c r="K115" t="n">
@@ -7707,20 +7707,20 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>宜蘭縣政府</t>
+          <t>臺南市政府經濟發展局</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>「宜蘭縣115年國際移民嘉年華」活動規劃執行委託案</t>
+          <t>「116年永康迎春嘉年華」活動規劃執行服務</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>400000</v>
+        <v>600000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>CVSL115019</t>
+          <t>115ECON71S1</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7770,25 +7770,25 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>財政部高雄國稅局</t>
+          <t>臺北表演藝術中心</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>115年度結合統一發票推行暨「來稅局找碴-觀察力培養計畫」租稅宣導活動委外服務案</t>
+          <t>第三屆臺北戲劇獎頒獎典禮暨系列活動製作執行勞務採購案</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>445000</v>
+        <v>15000000</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -7798,21 +7798,21 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>1150042</t>
+          <t>TPACRD1150141</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>頒獎典禮、系列活動</t>
         </is>
       </c>
       <c r="K117" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L117" s="3" t="inlineStr">
         <is>
@@ -7833,20 +7833,20 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>國立臺中教育大學</t>
+          <t>屏東縣獅子鄉公所</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>115年原住民族教育論壇暨原住民族教育資源中心成果交流會</t>
+          <t>屏東縣獅子鄉115年度慶祝重陽節聯合表揚暨族語文化推廣與文化健康站成果展活動勞務採購案</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>1450000</v>
+        <v>1162700</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -7861,21 +7861,21 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>115-C062</t>
+          <t>1151001AA</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>論壇</t>
+          <t>成果展、活動、推廣</t>
         </is>
       </c>
       <c r="K118" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L118" s="3" t="inlineStr">
         <is>
@@ -7896,20 +7896,20 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>衛生福利部疾病管制署</t>
+          <t>宜蘭縣政府</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>「115年度防疫績優獎頒獎典禮專業服務」採購案</t>
+          <t>「宜蘭縣115年國際移民嘉年華」活動規劃執行委託案</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>950000</v>
+        <v>400000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>LA115028</t>
+          <t>CVSL115019</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7934,11 +7934,11 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>頒獎典禮</t>
+          <t>嘉年華、活動規劃</t>
         </is>
       </c>
       <c r="K119" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L119" s="3" t="inlineStr">
         <is>
@@ -7959,20 +7959,20 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>花蓮縣政府</t>
+          <t>財政部高雄國稅局</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>115年花蓮縣精品咖啡行銷推廣計畫</t>
+          <t>115年度結合統一發票推行暨「來稅局找碴-觀察力培養計畫」租稅宣導活動委外服務案</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>1100000</v>
+        <v>445000</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -7987,21 +7987,21 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>AG1150018061</t>
+          <t>1150042</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>行銷推廣</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K120" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L120" s="3" t="inlineStr">
         <is>
@@ -8022,25 +8022,25 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>社團法人花蓮縣基督教會花蓮靈糧堂宣教協會</t>
+          <t>國立臺中教育大學</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026花蓮幸福聖誕城行銷宣傳及城市聯合宣傳規劃案</t>
+          <t>115年原住民族教育論壇暨原住民族教育資源中心成果交流會</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>6789600</v>
+        <v>1450000</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -8050,21 +8050,21 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-2HLLC</t>
+          <t>115-C062</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>行銷宣傳</t>
+          <t>論壇</t>
         </is>
       </c>
       <c r="K121" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L121" s="3" t="inlineStr">
         <is>
@@ -8085,25 +8085,25 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>社團法人花蓮縣基督教會花蓮靈糧堂宣教協會</t>
+          <t>衛生福利部疾病管制署</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026花蓮幸福聖誕城活動執行案</t>
+          <t>「115年度防疫績優獎頒獎典禮專業服務」採購案</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>9950000</v>
+        <v>950000</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-1HLLC</t>
+          <t>LA115028</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>頒獎典禮</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -8148,20 +8148,20 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>桃園市平鎮區公所</t>
+          <t>花蓮縣政府</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>116年桃園市平鎮區元旦升旗典禮活動</t>
+          <t>115年花蓮縣精品咖啡行銷推廣計畫</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>450000</v>
+        <v>1100000</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -8176,17 +8176,17 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>1151005A01</t>
+          <t>AG1150018061</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>活動、典禮</t>
+          <t>行銷推廣</t>
         </is>
       </c>
       <c r="K123" t="n">
@@ -8211,45 +8211,45 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>彰化縣田中鎮公所</t>
+          <t>社團法人花蓮縣基督教會花蓮靈糧堂宣教協會</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026田中藝術節–愛閱田中・藝起嗨劇場委託專業服務採購案</t>
+          <t>2026花蓮幸福聖誕城行銷宣傳及城市聯合宣傳規劃案</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>700000</v>
+        <v>6789600</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>115-081</t>
+          <t>2026-2HLLC</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>藝術節</t>
+          <t>行銷宣傳</t>
         </is>
       </c>
       <c r="K124" t="n">
@@ -8274,16 +8274,16 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>社團法人花蓮縣基督教會花蓮靈糧堂宣教協會</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>116年屏東縣政府社會處網路媒體行銷維運案</t>
+          <t>2026花蓮幸福聖誕城活動執行案</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>2000000</v>
+        <v>9950000</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -8302,17 +8302,17 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>A058-1151007-2</t>
+          <t>2026-1HLLC</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>媒體行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="K125" t="n">
@@ -8337,20 +8337,20 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>南投縣政府</t>
+          <t>桃園市平鎮區公所</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>115年縣政成果及重大活動影音攝製行銷案</t>
+          <t>116年桃園市平鎮區元旦升旗典禮活動</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>1400000</v>
+        <v>450000</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -8365,17 +8365,17 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>115-07-06-011E</t>
+          <t>1151005A01</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>活動、行銷</t>
+          <t>活動、典禮</t>
         </is>
       </c>
       <c r="K126" t="n">
@@ -8400,16 +8400,16 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>苗栗縣政府</t>
+          <t>彰化縣田中鎮公所</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>「2027台灣燈會在苗栗」廣播錄製暨執行委託專業服務案</t>
+          <t>2026田中藝術節–愛閱田中・藝起嗨劇場委託專業服務採購案</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>500000</v>
+        <v>700000</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -8423,12 +8423,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>115141f</t>
+          <t>115-081</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8438,11 +8438,11 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>燈會</t>
+          <t>藝術節</t>
         </is>
       </c>
       <c r="K127" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L127" s="3" t="inlineStr">
         <is>
@@ -8463,25 +8463,25 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>臺南市政府經濟發展局</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>「2027新化年貨大街」活動委託服務案</t>
+          <t>116年屏東縣政府社會處網路媒體行銷維運案</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>1100000</v>
+        <v>2000000</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -8491,21 +8491,21 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>115ECON72S1</t>
+          <t>A058-1151007-2</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>媒體行銷</t>
         </is>
       </c>
       <c r="K128" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L128" s="3" t="inlineStr">
         <is>
@@ -8521,30 +8521,30 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>花蓮縣政府</t>
+          <t>南投縣政府</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026花蓮星潮原聲系列活動規劃執行案</t>
+          <t>115年縣政成果及重大活動影音攝製行銷案</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>40000000</v>
+        <v>1400000</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -8554,21 +8554,21 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>AB1150007224</t>
+          <t>115-07-06-011E</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>系列活動、活動規劃</t>
+          <t>活動、行銷</t>
         </is>
       </c>
       <c r="K129" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L129" s="3" t="inlineStr">
         <is>
@@ -8584,21 +8584,21 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>南投縣政府</t>
+          <t>苗栗縣政府</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>「2026南投花卉嘉年華－草屯展區系列活動」勞務採購案</t>
+          <t>「2027台灣燈會在苗栗」廣播錄製暨執行委託專業服務案</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>1150602018G</t>
+          <t>115141f</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8627,11 +8627,11 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>嘉年華、系列活動</t>
+          <t>燈會</t>
         </is>
       </c>
       <c r="K130" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L130" s="3" t="inlineStr">
         <is>
@@ -8647,25 +8647,25 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>內政部</t>
+          <t>臺南市政府經濟發展局</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>116年第84屆兵役節慶祝大會暨頒獎典禮委外服務案</t>
+          <t>「2027新化年貨大街」活動委託服務案</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>1230000</v>
+        <v>1100000</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -8680,21 +8680,21 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>115YJ-ST15</t>
+          <t>115ECON72S1</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>國際會議論壇/活動執行</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>大會、頒獎典禮</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K131" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="L131" s="3" t="inlineStr">
         <is>
@@ -8715,25 +8715,25 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>國立臺灣美術館</t>
+          <t>花蓮縣政府</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">國家珍藏作品之線上藝廊推廣影片製作採購案 </t>
+          <t>2026花蓮星潮原聲系列活動規劃執行案</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>600000</v>
+        <v>40000000</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -8743,21 +8743,21 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>115118</t>
+          <t>AB1150007224</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>影片製作、推廣</t>
+          <t>系列活動、活動規劃</t>
         </is>
       </c>
       <c r="K132" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L132" s="3" t="inlineStr">
         <is>
@@ -8778,25 +8778,25 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>苗栗縣苗栗市公所</t>
+          <t>南投縣政府</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>苗栗市2026冬迎璀璨歲末藝文嘉年華</t>
+          <t>「2026南投花卉嘉年華－草屯展區系列活動」勞務採購案</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>2440000</v>
+        <v>1000000</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>C548</t>
+          <t>1150602018G</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8816,11 +8816,11 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>嘉年華</t>
+          <t>嘉年華、系列活動</t>
         </is>
       </c>
       <c r="K133" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L133" s="3" t="inlineStr">
         <is>
@@ -8841,20 +8841,20 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>苗栗縣苗栗市公所</t>
+          <t>內政部</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>115年度苗栗市親子蘿蔔節活動執行委託專業服務採購案</t>
+          <t>116年第84屆兵役節慶祝大會暨頒獎典禮委外服務案</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>1000000</v>
+        <v>1230000</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -8869,21 +8869,21 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>B1600</t>
+          <t>115YJ-ST15</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>國際會議論壇/活動執行</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>大會、頒獎典禮</t>
         </is>
       </c>
       <c r="K134" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L134" s="3" t="inlineStr">
         <is>
@@ -8904,25 +8904,25 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>桃園市政府工務局</t>
+          <t>國立臺灣美術館</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>115年桃園市食農教育執行成果展委託專業服務案</t>
+          <t xml:space="preserve">國家珍藏作品之線上藝廊推廣影片製作採購案 </t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>2000000</v>
+        <v>600000</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -8932,21 +8932,21 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>1151005-3</t>
+          <t>115118</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>成果展</t>
+          <t>影片製作、推廣</t>
         </is>
       </c>
       <c r="K135" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L135" s="3" t="inlineStr">
         <is>
@@ -8967,25 +8967,25 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>新竹縣尖石鄉公所</t>
+          <t>苗栗縣苗栗市公所</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>新竹縣尖石鄉115年尖石鄉鄉長盃第二屆傳統路跑嘉年華暨傳統擲矛、傳統狩獵活動勞務採購案</t>
+          <t>苗栗市2026冬迎璀璨歲末藝文嘉年華</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>950000</v>
+        <v>2440000</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>1159226</t>
+          <t>C548</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -9030,25 +9030,25 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>嘉義縣文化觀光局</t>
+          <t>苗栗縣苗栗市公所</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>「116年度嘉義縣觀光旅遊數位整合行銷」委託專業服務案</t>
+          <t>115年度苗栗市親子蘿蔔節活動執行委託專業服務採購案</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -9058,17 +9058,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>1150011120</t>
+          <t>B1600</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>整合行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -9093,49 +9093,49 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>台灣中油股份有限公司探採事業部</t>
+          <t>桃園市政府工務局</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>碳封存監測資料彙整分析及社會溝通顧問服務</t>
+          <t>115年桃園市食農教育執行成果展委託專業服務案</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>1490000</v>
+        <v>2000000</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>BEA1500013</t>
+          <t>1151005-3</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>政策溝通</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>社會溝通</t>
+          <t>成果展</t>
         </is>
       </c>
       <c r="K138" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L138" s="3" t="inlineStr">
         <is>
@@ -9156,16 +9156,16 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>中央選舉委員會</t>
+          <t>新竹縣尖石鄉公所</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>115年地方公職人員選舉及公民投票選務滿意度民意調查採購案</t>
+          <t>新竹縣尖石鄉115年尖石鄉鄉長盃第二屆傳統路跑嘉年華暨傳統擲矛、傳統狩獵活動勞務採購案</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>500000</v>
+        <v>950000</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -9184,21 +9184,21 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>1150909</t>
+          <t>1159226</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>政策溝通</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>民意調查</t>
+          <t>嘉年華</t>
         </is>
       </c>
       <c r="K139" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L139" s="3" t="inlineStr">
         <is>
@@ -9219,25 +9219,25 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>桃園市政府捷運工程局</t>
+          <t>嘉義縣文化觀光局</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>桃園市八德區德和路一段第2階段通車活動委託服務案</t>
+          <t>「116年度嘉義縣觀光旅遊數位整合行銷」委託專業服務案</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -9247,21 +9247,21 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>1151006</t>
+          <t>1150011120</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>整合行銷</t>
         </is>
       </c>
       <c r="K140" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L140" s="3" t="inlineStr">
         <is>
@@ -9277,54 +9277,54 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>國防部</t>
+          <t>台灣中油股份有限公司探採事業部</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>國軍招募宣傳電視廣告託播</t>
+          <t>碳封存監測資料彙整分析及社會溝通顧問服務</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>2000000</v>
+        <v>1490000</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>公開招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>CC15003L050</t>
+          <t>BEA1500013</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>政策溝通</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>廣告託播、宣傳</t>
+          <t>社會溝通</t>
         </is>
       </c>
       <c r="K141" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L141" s="3" t="inlineStr">
         <is>
@@ -9340,30 +9340,30 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>衛生福利部社會及家庭署</t>
+          <t>中央選舉委員會</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>116年度強化社會安全網績優人員及團體獎項品牌識別系統專業服務案</t>
+          <t>115年地方公職人員選舉及公民投票選務滿意度民意調查採購案</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>2550000</v>
+        <v>500000</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -9373,21 +9373,21 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>C116001</t>
+          <t>1150909</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>政策溝通</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>品牌識別</t>
+          <t>民意調查</t>
         </is>
       </c>
       <c r="K142" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L142" s="3" t="inlineStr">
         <is>
@@ -9403,30 +9403,30 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>臺北市政府觀光傳播局</t>
+          <t>桃園市政府捷運工程局</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>116年度臺北開齋節暨穆斯林友善城市推廣活動案</t>
+          <t>桃園市八德區德和路一段第2階段通車活動委託服務案</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>4000000</v>
+        <v>1000000</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -9436,21 +9436,21 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>1150075</t>
+          <t>1151006</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>活動、推廣</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K143" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L143" s="3" t="inlineStr">
         <is>
@@ -9471,25 +9471,25 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>國立歷史博物館</t>
+          <t>國防部</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>常設展手語導覽影片製作案</t>
+          <t>國軍招募宣傳電視廣告託播</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>950000</v>
+        <v>2000000</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>公開招標公告</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>115046</t>
+          <t>CC15003L050</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9509,11 +9509,11 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>影片製作</t>
+          <t>廣告託播、宣傳</t>
         </is>
       </c>
       <c r="K144" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L144" s="3" t="inlineStr">
         <is>
@@ -9534,20 +9534,20 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>內政部國土管理署</t>
+          <t>衛生福利部社會及家庭署</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>116年度住宅政策推廣影音及多媒體製作案</t>
+          <t>116年度強化社會安全網績優人員及團體獎項品牌識別系統專業服務案</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>9950000</v>
+        <v>2550000</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>115A-066</t>
+          <t>C116001</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9572,7 +9572,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>推廣、媒體</t>
+          <t>品牌識別</t>
         </is>
       </c>
       <c r="K145" t="n">
@@ -9597,16 +9597,16 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>高雄市政府勞工局訓練就業中心</t>
+          <t>臺北市政府觀光傳播局</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>「116年度鳳山、岡山就業服務站現場徵才活動」委託服務案</t>
+          <t>116年度臺北開齋節暨穆斯林友善城市推廣活動案</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>2892100</v>
+        <v>4000000</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -9625,21 +9625,21 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>116F002</t>
+          <t>1150075</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>活動、推廣</t>
         </is>
       </c>
       <c r="K146" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L146" s="3" t="inlineStr">
         <is>
@@ -9660,20 +9660,20 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>新北市政府勞工局</t>
+          <t>國立歷史博物館</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>新北市政府116年度外國人文化與休閒活動計畫-越南、印尼活動委託專業服務採購案</t>
+          <t>常設展手語導覽影片製作案</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>1300000</v>
+        <v>950000</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -9683,26 +9683,26 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>TPLAB115013</t>
+          <t>115046</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>影片製作</t>
         </is>
       </c>
       <c r="K147" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L147" s="3" t="inlineStr">
         <is>
@@ -9718,30 +9718,30 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>臺中市石岡區公所</t>
+          <t>內政部國土管理署</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>115年石岡童樂會暨水資源宣導活動</t>
+          <t>116年度住宅政策推廣影音及多媒體製作案</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>800000</v>
+        <v>9950000</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -9751,21 +9751,21 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>115SK20</t>
+          <t>115A-066</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>推廣、媒體</t>
         </is>
       </c>
       <c r="K148" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L148" s="3" t="inlineStr">
         <is>
@@ -9781,30 +9781,30 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>臺中市石岡區公所</t>
+          <t>高雄市政府勞工局訓練就業中心</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026臺中市民野餐日（石岡區）暨觀光活化水資源宣導活動</t>
+          <t>「116年度鳳山、岡山就業服務站現場徵才活動」委託服務案</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>920000</v>
+        <v>2892100</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -9814,21 +9814,21 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>115SK19</t>
+          <t>116F002</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K149" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L149" s="3" t="inlineStr">
         <is>
@@ -9844,40 +9844,40 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>新竹縣芎林鄉公所</t>
+          <t>新北市政府勞工局</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2027芎林路跑嘉年華活動計畫委託專業服務案</t>
+          <t>新北市政府116年度外國人文化與休閒活動計畫-越南、印尼活動委託專業服務採購案</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>2400000</v>
+        <v>1300000</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>1160001P</t>
+          <t>TPLAB115013</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9887,11 +9887,11 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>嘉年華、活動</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K150" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L150" s="3" t="inlineStr">
         <is>
@@ -9912,25 +9912,25 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>海洋委員會</t>
+          <t>臺中市石岡區公所</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>海洋博覽會整體規劃暨先期策略研析委託專業服務案</t>
+          <t>115年石岡童樂會暨水資源宣導活動</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>3000000</v>
+        <v>800000</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -9940,21 +9940,21 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>OAC115044</t>
+          <t>115SK20</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>博覽會</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K151" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L151" s="3" t="inlineStr">
         <is>
@@ -9975,25 +9975,25 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>花蓮縣政府</t>
+          <t>臺中市石岡區公所</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>115年花蓮宜居城市行銷採購案(開口契約)</t>
+          <t>2026臺中市民野餐日（石岡區）暨觀光活化水資源宣導活動</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>9450000</v>
+        <v>920000</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -10003,21 +10003,21 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>SK1150005862</t>
+          <t>115SK19</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>城市行銷</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K152" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L152" s="3" t="inlineStr">
         <is>
@@ -10038,25 +10038,25 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>花蓮縣政府</t>
+          <t>新竹縣芎林鄉公所</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>115年花蓮縣社區照顧關懷據點及社區長照站成果展</t>
+          <t>2027芎林路跑嘉年華活動計畫委託專業服務案</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>1250000</v>
+        <v>2400000</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>SC1150020073</t>
+          <t>1160001P</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -10076,11 +10076,11 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>成果展</t>
+          <t>嘉年華、活動</t>
         </is>
       </c>
       <c r="K153" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L153" s="3" t="inlineStr">
         <is>
@@ -10101,25 +10101,25 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>桃園市政府文化局</t>
+          <t>海洋委員會</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026桃園仙草花節系列活動-民歌演唱會委託專業服務案</t>
+          <t>海洋博覽會整體規劃暨先期策略研析委託專業服務案</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>500000</v>
+        <v>3000000</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -10129,21 +10129,21 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>TYC115-39</t>
+          <t>OAC115044</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>系列活動</t>
+          <t>博覽會</t>
         </is>
       </c>
       <c r="K154" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L154" s="3" t="inlineStr">
         <is>
@@ -10164,20 +10164,20 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>宜蘭縣政府</t>
+          <t>花蓮縣政府</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>宜蘭縣115年度原有住宅無障礙設施補助委託辦理推廣宣導評估案</t>
+          <t>115年花蓮宜居城市行銷採購案(開口契約)</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>1210000</v>
+        <v>9450000</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>CNSL115032</t>
+          <t>SK1150005862</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -10202,7 +10202,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>宣導、推廣</t>
+          <t>城市行銷</t>
         </is>
       </c>
       <c r="K155" t="n">
@@ -10227,25 +10227,25 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>財團法人嘉義市文化基金會</t>
+          <t>花蓮縣政府</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026嘉義市管樂節晚會舞台暨表演節目規畫執行委託服務案</t>
+          <t>115年花蓮縣社區照顧關懷據點及社區長照站成果展</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>15000000</v>
+        <v>1250000</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -10255,7 +10255,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>115A001</t>
+          <t>SC1150020073</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10265,11 +10265,11 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>晚會</t>
+          <t>成果展</t>
         </is>
       </c>
       <c r="K156" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L156" s="3" t="inlineStr">
         <is>
@@ -10290,25 +10290,25 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>新竹市政府</t>
+          <t>桃園市政府文化局</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>「2026客家藝文活動」委託專業服務案</t>
+          <t>2026桃園仙草花節系列活動-民歌演唱會委託專業服務案</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>2400000</v>
+        <v>500000</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標公告</t>
+          <t>公開取得報價單或企劃書公告</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>1150292</t>
+          <t>TYC115-39</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10328,11 +10328,11 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>系列活動</t>
         </is>
       </c>
       <c r="K157" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L157" s="3" t="inlineStr">
         <is>
@@ -10348,25 +10348,25 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>新北市政府觀光旅遊局</t>
+          <t>宜蘭縣政府</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>116年度跨媒體整合傳播採購案</t>
+          <t>宜蘭縣115年度原有住宅無障礙設施補助委託辦理推廣宣導評估案</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>7350000</v>
+        <v>1210000</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>1151911877</t>
+          <t>CNSL115032</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10391,11 +10391,11 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>整合傳播、跨媒體</t>
+          <t>宣導、推廣</t>
         </is>
       </c>
       <c r="K158" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L158" s="3" t="inlineStr">
         <is>
@@ -10411,25 +10411,25 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>司法院</t>
+          <t>財團法人嘉義市文化基金會</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>司法院115年司法博物館主題活動規劃執行採購案</t>
+          <t>2026嘉義市管樂節晚會舞台暨表演節目規畫執行委託服務案</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>3400000</v>
+        <v>15000000</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>1151400844</t>
+          <t>115A001</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10454,11 +10454,11 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>活動規劃、主題活動</t>
+          <t>晚會</t>
         </is>
       </c>
       <c r="K159" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L159" s="3" t="inlineStr">
         <is>
@@ -10474,54 +10474,54 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>彰化縣伸港鄉公所</t>
+          <t>新竹市政府</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2027年伸港飛揚-元旦升旗健行齊步走暨節能減碳宣導活動委託服務案</t>
+          <t>「2026客家藝文活動」委託專業服務案</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>1152300</v>
+        <v>2400000</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>1152006</t>
+          <t>1150292</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>活動執行/宣導行銷</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>活動、宣導活動</t>
+          <t>活動</t>
         </is>
       </c>
       <c r="K160" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L160" s="3" t="inlineStr">
         <is>
@@ -10542,25 +10542,25 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>臺東縣政府</t>
+          <t>新北市政府觀光旅遊局</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>興隆國小--臺東縣115年度環境變遷與藍碳發展論壇暨體驗學習活動</t>
+          <t>116年度跨媒體整合傳播採購案</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>420000</v>
+        <v>7350000</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -10570,21 +10570,21 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>115310130545</t>
+          <t>1151911877</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>宣導行銷</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>論壇</t>
+          <t>整合傳播、跨媒體</t>
         </is>
       </c>
       <c r="K161" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L161" s="3" t="inlineStr">
         <is>
@@ -10605,20 +10605,20 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>桃園市政府文化局</t>
+          <t>司法院</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026桃園社造博覽會規劃執行案</t>
+          <t>司法院115年司法博物館主題活動規劃執行採購案</t>
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>2000000</v>
+        <v>3400000</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -10633,21 +10633,21 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>1150276</t>
+          <t>1151400844</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>國際會議論壇</t>
+          <t>活動執行</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>博覽會</t>
+          <t>活動規劃、主題活動</t>
         </is>
       </c>
       <c r="K162" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L162" s="3" t="inlineStr">
         <is>
@@ -10668,20 +10668,20 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>新北市政府水利局</t>
+          <t>彰化縣伸港鄉公所</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>新北市治水、清水、親水水環境治理成果影片製作案</t>
+          <t>2027年伸港飛揚-元旦升旗健行齊步走暨節能減碳宣導活動委託服務案</t>
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>1200000</v>
+        <v>1152300</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -10691,26 +10691,26 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>1150930A</t>
+          <t>1152006</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>活動執行/宣導行銷</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>影片製作</t>
+          <t>活動、宣導活動</t>
         </is>
       </c>
       <c r="K163" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L163" s="3" t="inlineStr">
         <is>
@@ -10731,16 +10731,16 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>彰化縣田中鎮公所</t>
+          <t>臺東縣政府</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026田中藝術節–愛閱田中・藝起嗨劇場委託專業服務採購案</t>
+          <t>興隆國小--臺東縣115年度環境變遷與藍碳發展論壇暨體驗學習活動</t>
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>700000</v>
+        <v>420000</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -10759,21 +10759,21 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>115-081</t>
+          <t>115310130545</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>活動執行</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>藝術節</t>
+          <t>論壇</t>
         </is>
       </c>
       <c r="K164" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L164" s="3" t="inlineStr">
         <is>
@@ -10794,25 +10794,25 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>外交部領事事務局</t>
+          <t>桃園市政府文化局</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>115年度推廣外交部領事事務局「LINE官方帳號」靜態貼圖廣告方案</t>
+          <t>2026桃園社造博覽會規劃執行案</t>
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>630000</v>
+        <v>2000000</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書公告</t>
+          <t>經公開評選或公開徵求之限制性招標公告</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -10822,21 +10822,21 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>T115027CB</t>
+          <t>1150276</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>宣導行銷</t>
+          <t>國際會議論壇</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>廣告、推廣</t>
+          <t>博覽會</t>
         </is>
       </c>
       <c r="K165" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L165" s="3" t="inlineStr">
         <is>
@@ -10857,20 +10857,20 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>勞動部勞動力發展署桃竹苗分署</t>
+          <t>新北市政府水利局</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>116年機關整合行銷勞務採購案</t>
+          <t>新北市治水、清水、親水水環境治理成果影片製作案</t>
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>1330000</v>
+        <v>1200000</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -10885,7 +10885,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>116Y020</t>
+          <t>1150930A</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10895,7 +10895,7 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>整合行銷</t>
+          <t>影片製作</t>
         </is>
       </c>
       <c r="K166" t="n">
@@ -10912,8 +10912,197 @@
         </is>
       </c>
     </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>彰化縣田中鎮公所</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2026田中藝術節–愛閱田中・藝起嗨劇場委託專業服務採購案</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="n">
+        <v>700000</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>公開取得報價單或企劃書公告</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>115-081</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>活動執行</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>藝術節</t>
+        </is>
+      </c>
+      <c r="K167" t="n">
+        <v>8</v>
+      </c>
+      <c r="L167" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>外交部領事事務局</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>115年度推廣外交部領事事務局「LINE官方帳號」靜態貼圖廣告方案</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>630000</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>公開取得報價單或企劃書公告</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>T115027CB</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>宣導行銷</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>廣告、推廣</t>
+        </is>
+      </c>
+      <c r="K168" t="n">
+        <v>8</v>
+      </c>
+      <c r="L168" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>勞動部勞動力發展署桃竹苗分署</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>116年機關整合行銷勞務採購案</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="n">
+        <v>1330000</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>公開取得報價單或企劃書公告</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>116Y020</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>宣導行銷</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>整合行銷</t>
+        </is>
+      </c>
+      <c r="K169" t="n">
+        <v>8</v>
+      </c>
+      <c r="L169" s="3" t="inlineStr">
+        <is>
+          <t>開啟</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:34</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M166"/>
+  <autoFilter ref="A1:M169"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -11080,6 +11269,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L164" r:id="rId163"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L165" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L169" r:id="rId168"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11129,13 +11321,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6604</v>
+        <v>6724</v>
       </c>
       <c r="C2" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>537887780</v>
+        <v>543598601</v>
       </c>
     </row>
   </sheetData>
@@ -11165,7 +11357,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>產生時間：2026-10-26 08:15　資料庫共 165 筆</t>
+          <t>產生時間：2026-10-27 09:27　資料庫共 168 筆</t>
         </is>
       </c>
     </row>

--- a/data/標案資料庫.xlsx
+++ b/data/標案資料庫.xlsx
@@ -12765,7 +12765,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>產生時間：2026-10-29 17:18　資料庫共 190 筆</t>
+          <t>產生時間：2026-10-29 18:47　資料庫共 190 筆</t>
         </is>
       </c>
     </row>
